--- a/datasets_test.xlsx
+++ b/datasets_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2023 cytoSR\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBEF9535-9D0F-4806-865F-0A461BA1FD4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF14631-5C60-41F5-8BAC-820DFB05C316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20625" yWindow="2475" windowWidth="14130" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20970" yWindow="2820" windowWidth="14130" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="232">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -94,284 +94,773 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>SimuBeads3D-128-31-0-0-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SimuBeads3D-128-31-05-1-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SimuBeads3D-128-31-05-1-03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SimuBeads3D-128-31-05-1-01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SimuMix3D-382-101-05-1-1-560</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SimuMix3D-382-101-05-1-1-642</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SimuMix3D-128-31-0-0-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SimuMix3D-128-31-05-1-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SimuMix3D-128-31-05-1-03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SimuMix3D-128-31-05-1-01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SimuMix3D-256-31-0-0-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SimuMix3D-256-31-05-1-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SimuMix3D-256-31-05-1-03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SimuMix3D-256-31-05-1-01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Microtubule-3d-1024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Microtubule2-3d-1024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nuclear-pore-complex-1024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nuclear-pore-complex2-1024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Microtubules2-9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ratio</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scale_factor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>path_lr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>path_hr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>path_txt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\SimuBeads3D_128\raw_psf_31_gauss_0_poiss_0_sf_1_ratio_1</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\SimuBeads3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_1</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\SimuBeads3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.3</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\SimuBeads3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.1</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\SimuBeads3D_128\gt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\SimuBeads3D_128\test.txt</t>
+  </si>
+  <si>
+    <t>path_psf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\SimuBeads3D_128\PSF_31.tif</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\SimuMix3D_128\raw_psf_31_gauss_0_poiss_0_sf_1_ratio_1</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\SimuMix3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_1</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\SimuMix3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.3</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\SimuMix3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.1</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\SimuMix3D_128\gt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\SimuMix3D_128\test.txt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\SimuMix3D_128\PSF_31.tif</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\SimuMix3D_128\PSF_31.tif</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\SimuMix3D_256\raw_psf_31_gauss_0_poiss_0_sf_1_ratio_1</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\SimuMix3D_256\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_1</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\SimuMix3D_256\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.3</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\SimuMix3D_256\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.1</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\SimuMix3D_256\gt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\SimuMix3D_256\test.txt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\SimuMix3D_256\PSF_31.tif</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\SimuMix3D_382\raw_psf_101_gauss_0.5_poiss_1_sf_1_ratio_1_lambda_560</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\SimuMix3D_382\raw_psf_101_gauss_0.5_poiss_1_sf_1_ratio_1_lambda_642</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\SimuMix3D_382\gt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\SimuMix3D_382\test.txt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\SimuMix3D_382\raw_psf_101_gauss_0.5_poiss_1_sf_1_ratio_1_lambda_560\PSF.tif</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\SimuMix3D_382\raw_psf_101_gauss_0.5_poiss_1_sf_1_ratio_1_lambda_642\PSF.tif</t>
+  </si>
+  <si>
+    <t>I:\Datasets\ZeroShotDeconvNet\3D time-lapsing data_LLSM_Mitosis_H2B\642\raw</t>
+  </si>
+  <si>
+    <t>I:\Datasets\ZeroShotDeconvNet\3D time-lapsing data_LLSM_Mitosis_Mito\560\raw</t>
+  </si>
+  <si>
+    <t>I:\Datasets\ZeroShotDeconvNet\3D time-lapsing data_LLSM_Mitosis_Mito\560\raw.txt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\ZeroShotDeconvNet\3D time-lapsing data_LLSM_Mitosis_H2B\642\raw.txt</t>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\ZeroShotDeconvNet\3D time-lapsing data_LLSM_Mitosis_H2B\642\raw\PSF_odd.tif</t>
+  </si>
+  <si>
+    <t>I:\Datasets\ZeroShotDeconvNet\3D time-lapsing data_LLSM_Mitosis_Mito\560\raw\PSF_odd.tif</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Microtubule\raw_1024x1024</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Microtubule\gt_1024x1024</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Microtubule\test_1024x1024.txt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\test.txt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\test.txt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Microtubule2\raw_1024x1024</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Microtubule2\gt_1024x1024</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Microtubule2\test_1024x1024.txt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex\raw_1024x1024</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex\gt_1024x1024</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex\test_1024x1024.txt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex2\raw_1024x1024</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex2\gt_1024x1024</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex2\test_1024x1024.txt</t>
+  </si>
+  <si>
+    <t>train_mode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>su</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>F-actin-nonlinear-9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SimuBeads3D-128-31-0-0-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SimuBeads3D-128-31-05-1-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SimuBeads3D-128-31-05-1-03</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SimuBeads3D-128-31-05-1-01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SimuMix3D-382-101-05-1-1-560</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SimuMix3D-382-101-05-1-1-642</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SimuMix3D-128-31-0-0-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SimuMix3D-128-31-05-1-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SimuMix3D-128-31-05-1-03</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SimuMix3D-128-31-05-1-01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SimuMix3D-256-31-0-0-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SimuMix3D-256-31-05-1-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SimuMix3D-256-31-05-1-03</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SimuMix3D-256-31-05-1-01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Microtubule-3d-1024</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Microtubule2-3d-1024</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Nuclear-pore-complex-1024</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Nuclear-pore-complex2-1024</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Microtubules2-9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ratio</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>scale_factor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>path_lr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>path_hr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>path_txt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuBeads3D_128\raw_psf_31_gauss_0_poiss_0_sf_1_ratio_1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuBeads3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuBeads3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.3</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuBeads3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.1</t>
+  </si>
+  <si>
+    <t>F-actin-nonlinear-8</t>
+  </si>
+  <si>
+    <t>F-actin-nonlinear-7</t>
+  </si>
+  <si>
+    <t>F-actin-nonlinear-6</t>
+  </si>
+  <si>
+    <t>F-actin-nonlinear-5</t>
+  </si>
+  <si>
+    <t>F-actin-nonlinear-4</t>
+  </si>
+  <si>
+    <t>F-actin-nonlinear-3</t>
+  </si>
+  <si>
+    <t>F-actin-nonlinear-2</t>
+  </si>
+  <si>
+    <t>F-actin-nonlinear-1</t>
+  </si>
+  <si>
+    <t>Microtubules2-8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Microtubules2-7</t>
+  </si>
+  <si>
+    <t>Microtubules2-6</t>
+  </si>
+  <si>
+    <t>Microtubules2-5</t>
+  </si>
+  <si>
+    <t>Microtubules2-4</t>
+  </si>
+  <si>
+    <t>Microtubules2-3</t>
+  </si>
+  <si>
+    <t>Microtubules2-2</t>
+  </si>
+  <si>
+    <t>Microtubules2-1</t>
+  </si>
+  <si>
+    <t>CCPs-9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_9_sf_1\raw</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_9_sf_1\gt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\test.txt</t>
+  </si>
+  <si>
+    <t>CCPs-8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCPs-7</t>
+  </si>
+  <si>
+    <t>CCPs-6</t>
+  </si>
+  <si>
+    <t>CCPs-5</t>
+  </si>
+  <si>
+    <t>CCPs-4</t>
+  </si>
+  <si>
+    <t>CCPs-3</t>
+  </si>
+  <si>
+    <t>CCPs-2</t>
+  </si>
+  <si>
+    <t>CCPs-1</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_8_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_7_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_6_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_5_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_4_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_3_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_2_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_1_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_8_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_7_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_6_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_5_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_4_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_3_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_2_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_1_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_9_sf_1\raw</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_9_sf_1\gt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_8_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_7_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_6_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_5_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_4_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_3_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_2_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_1_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_8_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_7_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_6_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_5_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_4_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_3_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_2_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_1_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_9_sf_1\raw</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_9_sf_1\gt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_8_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_7_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_6_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_5_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_4_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_3_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_2_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_1_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_8_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_7_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_6_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_5_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_4_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_3_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_2_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_1_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-actin-12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-actin-11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-actin-10</t>
+  </si>
+  <si>
+    <t>F-actin-9</t>
+  </si>
+  <si>
+    <t>F-actin-8</t>
+  </si>
+  <si>
+    <t>F-actin-7</t>
+  </si>
+  <si>
+    <t>F-actin-6</t>
+  </si>
+  <si>
+    <t>F-actin-5</t>
+  </si>
+  <si>
+    <t>F-actin-4</t>
+  </si>
+  <si>
+    <t>F-actin-3</t>
+  </si>
+  <si>
+    <t>F-actin-2</t>
+  </si>
+  <si>
+    <t>F-actin-1</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\test.txt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_12_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_11_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_10_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_9_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_8_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_7_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_6_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_5_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_4_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_3_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_2_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_1_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_12_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_11_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_10_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_9_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_8_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_7_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_6_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_5_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_4_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_3_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_2_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_1_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ER-6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ER-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ER-4</t>
+  </si>
+  <si>
+    <t>ER-3</t>
+  </si>
+  <si>
+    <t>ER-2</t>
+  </si>
+  <si>
+    <t>ER-1</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\test.txt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_6_sf_1\gt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_5_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_4_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_3_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_2_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_1_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>I:\Datasets\RLN\SimuBeads3D_128\gt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuBeads3D_128\test.txt</t>
-  </si>
-  <si>
-    <t>path_psf</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuBeads3D_128\PSF_31.tif</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_128\raw_psf_31_gauss_0_poiss_0_sf_1_ratio_1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.3</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_128\gt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_128\test.txt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_128\PSF_31.tif</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_128\PSF_31.tif</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_256\raw_psf_31_gauss_0_poiss_0_sf_1_ratio_1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_256\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_256\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.3</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_256\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_256\gt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_256\test.txt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_256\PSF_31.tif</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_382\raw_psf_101_gauss_0.5_poiss_1_sf_1_ratio_1_lambda_560</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_382\raw_psf_101_gauss_0.5_poiss_1_sf_1_ratio_1_lambda_642</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_382\gt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_382\test.txt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_382\raw_psf_101_gauss_0.5_poiss_1_sf_1_ratio_1_lambda_560\PSF.tif</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_382\raw_psf_101_gauss_0.5_poiss_1_sf_1_ratio_1_lambda_642\PSF.tif</t>
-  </si>
-  <si>
-    <t>I:\Datasets\ZeroShotDeconvNet\3D time-lapsing data_LLSM_Mitosis_H2B\642\raw</t>
-  </si>
-  <si>
-    <t>I:\Datasets\ZeroShotDeconvNet\3D time-lapsing data_LLSM_Mitosis_Mito\560\raw</t>
-  </si>
-  <si>
-    <t>I:\Datasets\ZeroShotDeconvNet\3D time-lapsing data_LLSM_Mitosis_Mito\560\raw.txt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\ZeroShotDeconvNet\3D time-lapsing data_LLSM_Mitosis_H2B\642\raw.txt</t>
-  </si>
-  <si>
-    <t>None</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\ZeroShotDeconvNet\3D time-lapsing data_LLSM_Mitosis_H2B\642\raw\PSF_odd.tif</t>
-  </si>
-  <si>
-    <t>I:\Datasets\ZeroShotDeconvNet\3D time-lapsing data_LLSM_Mitosis_Mito\560\raw\PSF_odd.tif</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Microtubule\raw_1024x1024</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Microtubule\gt_1024x1024</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Microtubule\test_1024x1024.txt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\raw_noise_9</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\gt_sf_1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\test.txt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\raw_noise_9</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\gt_sf_1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\test.txt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Microtubule2\raw_1024x1024</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Microtubule2\gt_1024x1024</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Microtubule2\test_1024x1024.txt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex\raw_1024x1024</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex\gt_1024x1024</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex\test_1024x1024.txt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex2\raw_1024x1024</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex2\gt_1024x1024</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex2\test_1024x1024.txt</t>
-  </si>
-  <si>
-    <t>train_mode</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ss</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>su</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>enable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_6_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_5_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_4_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_3_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_2_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_1_sf_1\raw</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -422,7 +911,267 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="27">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -709,18 +1458,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="4" customWidth="1"/>
-    <col min="4" max="4" width="3.125" customWidth="1"/>
-    <col min="5" max="5" width="3.375" customWidth="1"/>
-    <col min="6" max="6" width="5" customWidth="1"/>
-    <col min="7" max="7" width="12.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="36.75" customWidth="1"/>
+    <col min="2" max="2" width="2.5" customWidth="1"/>
+    <col min="3" max="3" width="3.375" customWidth="1"/>
+    <col min="4" max="4" width="2.25" customWidth="1"/>
+    <col min="5" max="5" width="2.375" customWidth="1"/>
+    <col min="6" max="6" width="4.25" customWidth="1"/>
+    <col min="7" max="8" width="9.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
@@ -728,19 +1477,19 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C1" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D1" t="s">
         <v>6</v>
       </c>
       <c r="E1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
@@ -752,27 +1501,27 @@
         <v>13</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D2">
         <v>2</v>
@@ -793,27 +1542,27 @@
         <v>15</v>
       </c>
       <c r="J2" t="s">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="K2" t="s">
-        <v>81</v>
+        <v>158</v>
       </c>
       <c r="L2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="M2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -834,30 +1583,30 @@
         <v>15</v>
       </c>
       <c r="J3" t="s">
-        <v>83</v>
+        <v>159</v>
       </c>
       <c r="K3" t="s">
-        <v>84</v>
+        <v>167</v>
       </c>
       <c r="L3" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="M3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -866,39 +1615,39 @@
         <v>1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J4" t="s">
-        <v>41</v>
+        <v>160</v>
       </c>
       <c r="K4" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
       <c r="L4" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="M4" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -907,121 +1656,121 @@
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>42</v>
+        <v>161</v>
       </c>
       <c r="K5" t="s">
-        <v>45</v>
+        <v>169</v>
       </c>
       <c r="L5" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="M5" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>43</v>
+        <v>162</v>
       </c>
       <c r="K6" t="s">
-        <v>45</v>
+        <v>170</v>
       </c>
       <c r="L6" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="M6" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J7" t="s">
-        <v>44</v>
+        <v>163</v>
       </c>
       <c r="K7" t="s">
-        <v>45</v>
+        <v>171</v>
       </c>
       <c r="L7" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="M7" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1030,39 +1779,39 @@
         <v>1</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J8" t="s">
-        <v>49</v>
+        <v>164</v>
       </c>
       <c r="K8" t="s">
-        <v>53</v>
+        <v>172</v>
       </c>
       <c r="L8" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="M8" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1071,121 +1820,121 @@
         <v>1</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J9" t="s">
-        <v>50</v>
+        <v>165</v>
       </c>
       <c r="K9" t="s">
-        <v>53</v>
+        <v>173</v>
       </c>
       <c r="L9" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="M9" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>102</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J10" t="s">
-        <v>51</v>
+        <v>166</v>
       </c>
       <c r="K10" t="s">
-        <v>53</v>
+        <v>174</v>
       </c>
       <c r="L10" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="M10" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J11" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="K11" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="L11" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="M11" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1194,39 +1943,39 @@
         <v>1</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J12" t="s">
-        <v>57</v>
+        <v>141</v>
       </c>
       <c r="K12" t="s">
-        <v>61</v>
+        <v>149</v>
       </c>
       <c r="L12" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="M12" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -1235,121 +1984,121 @@
         <v>1</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J13" t="s">
-        <v>58</v>
+        <v>142</v>
       </c>
       <c r="K13" t="s">
-        <v>61</v>
+        <v>150</v>
       </c>
       <c r="L13" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="M13" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>105</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J14" t="s">
-        <v>59</v>
+        <v>143</v>
       </c>
       <c r="K14" t="s">
-        <v>61</v>
+        <v>151</v>
       </c>
       <c r="L14" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="M14" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="F15">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J15" t="s">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="K15" t="s">
-        <v>61</v>
+        <v>152</v>
       </c>
       <c r="L15" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="M15" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -1358,39 +2107,39 @@
         <v>1</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J16" t="s">
-        <v>64</v>
+        <v>145</v>
       </c>
       <c r="K16" t="s">
-        <v>66</v>
+        <v>153</v>
       </c>
       <c r="L16" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="M16" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1399,39 +2148,39 @@
         <v>1</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J17" t="s">
-        <v>65</v>
+        <v>146</v>
       </c>
       <c r="K17" t="s">
-        <v>66</v>
+        <v>154</v>
       </c>
       <c r="L17" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="M17" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1440,39 +2189,39 @@
         <v>1</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J18" t="s">
-        <v>77</v>
+        <v>147</v>
       </c>
       <c r="K18" t="s">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="L18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -1481,39 +2230,39 @@
         <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J19" t="s">
-        <v>86</v>
+        <v>148</v>
       </c>
       <c r="K19" t="s">
-        <v>87</v>
+        <v>156</v>
       </c>
       <c r="L19" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="M19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>111</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -1522,39 +2271,39 @@
         <v>1</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J20" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="K20" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="L20" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="M20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -1563,39 +2312,39 @@
         <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J21" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="K21" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="L21" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="M21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>7</v>
+        <v>116</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -1604,39 +2353,39 @@
         <v>1</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J22" t="s">
-        <v>70</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>74</v>
+        <v>124</v>
+      </c>
+      <c r="K22" t="s">
+        <v>132</v>
       </c>
       <c r="L22" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="M22" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>8</v>
+        <v>117</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -1645,39 +2394,39 @@
         <v>1</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J23" t="s">
-        <v>71</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>74</v>
+        <v>125</v>
+      </c>
+      <c r="K23" t="s">
+        <v>133</v>
       </c>
       <c r="L23" t="s">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="M23" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>11</v>
+        <v>118</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -1686,71 +2435,1964 @@
         <v>1</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J24" t="s">
-        <v>70</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>74</v>
+        <v>126</v>
+      </c>
+      <c r="K24" t="s">
+        <v>134</v>
       </c>
       <c r="L24" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="M24" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>119</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" t="s">
+        <v>127</v>
+      </c>
+      <c r="K25" t="s">
+        <v>135</v>
+      </c>
+      <c r="L25" t="s">
+        <v>114</v>
+      </c>
+      <c r="M25" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>120</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26">
+        <v>2</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J26" t="s">
+        <v>128</v>
+      </c>
+      <c r="K26" t="s">
+        <v>136</v>
+      </c>
+      <c r="L26" t="s">
+        <v>114</v>
+      </c>
+      <c r="M26" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>121</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
+        <v>92</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J27" t="s">
+        <v>129</v>
+      </c>
+      <c r="K27" t="s">
+        <v>137</v>
+      </c>
+      <c r="L27" t="s">
+        <v>114</v>
+      </c>
+      <c r="M27" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>122</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28">
+        <v>2</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J28" t="s">
+        <v>130</v>
+      </c>
+      <c r="K28" t="s">
+        <v>138</v>
+      </c>
+      <c r="L28" t="s">
+        <v>114</v>
+      </c>
+      <c r="M28" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>175</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>92</v>
+      </c>
+      <c r="D29">
+        <v>2</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J29" t="s">
+        <v>200</v>
+      </c>
+      <c r="K29" t="s">
+        <v>188</v>
+      </c>
+      <c r="L29" t="s">
+        <v>187</v>
+      </c>
+      <c r="M29" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>176</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
+        <v>92</v>
+      </c>
+      <c r="D30">
+        <v>2</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J30" t="s">
+        <v>201</v>
+      </c>
+      <c r="K30" t="s">
+        <v>189</v>
+      </c>
+      <c r="L30" t="s">
+        <v>187</v>
+      </c>
+      <c r="M30" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>177</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
+        <v>92</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J31" t="s">
+        <v>202</v>
+      </c>
+      <c r="K31" t="s">
+        <v>190</v>
+      </c>
+      <c r="L31" t="s">
+        <v>187</v>
+      </c>
+      <c r="M31" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>178</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>92</v>
+      </c>
+      <c r="D32">
+        <v>2</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J32" t="s">
+        <v>203</v>
+      </c>
+      <c r="K32" t="s">
+        <v>191</v>
+      </c>
+      <c r="L32" t="s">
+        <v>187</v>
+      </c>
+      <c r="M32" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>179</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
+        <v>92</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J33" t="s">
+        <v>204</v>
+      </c>
+      <c r="K33" t="s">
+        <v>192</v>
+      </c>
+      <c r="L33" t="s">
+        <v>187</v>
+      </c>
+      <c r="M33" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>180</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
+        <v>92</v>
+      </c>
+      <c r="D34">
+        <v>2</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J34" t="s">
+        <v>205</v>
+      </c>
+      <c r="K34" t="s">
+        <v>193</v>
+      </c>
+      <c r="L34" t="s">
+        <v>187</v>
+      </c>
+      <c r="M34" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>181</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35" t="s">
+        <v>92</v>
+      </c>
+      <c r="D35">
+        <v>2</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J35" t="s">
+        <v>206</v>
+      </c>
+      <c r="K35" t="s">
+        <v>194</v>
+      </c>
+      <c r="L35" t="s">
+        <v>187</v>
+      </c>
+      <c r="M35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>182</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
+        <v>92</v>
+      </c>
+      <c r="D36">
+        <v>2</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J36" t="s">
+        <v>207</v>
+      </c>
+      <c r="K36" t="s">
+        <v>195</v>
+      </c>
+      <c r="L36" t="s">
+        <v>187</v>
+      </c>
+      <c r="M36" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>183</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
+        <v>92</v>
+      </c>
+      <c r="D37">
+        <v>2</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J37" t="s">
+        <v>208</v>
+      </c>
+      <c r="K37" t="s">
+        <v>196</v>
+      </c>
+      <c r="L37" t="s">
+        <v>187</v>
+      </c>
+      <c r="M37" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>184</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>92</v>
+      </c>
+      <c r="D38">
+        <v>2</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J38" t="s">
+        <v>209</v>
+      </c>
+      <c r="K38" t="s">
+        <v>197</v>
+      </c>
+      <c r="L38" t="s">
+        <v>187</v>
+      </c>
+      <c r="M38" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>185</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s">
+        <v>92</v>
+      </c>
+      <c r="D39">
+        <v>2</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J39" t="s">
+        <v>210</v>
+      </c>
+      <c r="K39" t="s">
+        <v>198</v>
+      </c>
+      <c r="L39" t="s">
+        <v>187</v>
+      </c>
+      <c r="M39" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>186</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
+        <v>92</v>
+      </c>
+      <c r="D40">
+        <v>2</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J40" t="s">
+        <v>211</v>
+      </c>
+      <c r="K40" t="s">
+        <v>199</v>
+      </c>
+      <c r="L40" t="s">
+        <v>187</v>
+      </c>
+      <c r="M40" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>212</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41" t="s">
+        <v>92</v>
+      </c>
+      <c r="D41">
+        <v>2</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J41" t="s">
+        <v>226</v>
+      </c>
+      <c r="K41" t="s">
+        <v>219</v>
+      </c>
+      <c r="L41" t="s">
+        <v>218</v>
+      </c>
+      <c r="M41" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>213</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42" t="s">
+        <v>92</v>
+      </c>
+      <c r="D42">
+        <v>2</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J42" t="s">
+        <v>227</v>
+      </c>
+      <c r="K42" t="s">
+        <v>220</v>
+      </c>
+      <c r="L42" t="s">
+        <v>218</v>
+      </c>
+      <c r="M42" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>214</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
+        <v>92</v>
+      </c>
+      <c r="D43">
+        <v>2</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J43" t="s">
+        <v>228</v>
+      </c>
+      <c r="K43" t="s">
+        <v>221</v>
+      </c>
+      <c r="L43" t="s">
+        <v>218</v>
+      </c>
+      <c r="M43" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>215</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
+        <v>92</v>
+      </c>
+      <c r="D44">
+        <v>2</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J44" t="s">
+        <v>229</v>
+      </c>
+      <c r="K44" t="s">
+        <v>222</v>
+      </c>
+      <c r="L44" t="s">
+        <v>218</v>
+      </c>
+      <c r="M44" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>216</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45" t="s">
+        <v>92</v>
+      </c>
+      <c r="D45">
+        <v>2</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J45" t="s">
+        <v>230</v>
+      </c>
+      <c r="K45" t="s">
+        <v>223</v>
+      </c>
+      <c r="L45" t="s">
+        <v>218</v>
+      </c>
+      <c r="M45" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>217</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46" t="s">
+        <v>92</v>
+      </c>
+      <c r="D46">
+        <v>2</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J46" t="s">
+        <v>231</v>
+      </c>
+      <c r="K46" t="s">
+        <v>224</v>
+      </c>
+      <c r="L46" t="s">
+        <v>218</v>
+      </c>
+      <c r="M46" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>16</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
+        <v>92</v>
+      </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J47" t="s">
+        <v>40</v>
+      </c>
+      <c r="K47" t="s">
+        <v>225</v>
+      </c>
+      <c r="L47" t="s">
+        <v>45</v>
+      </c>
+      <c r="M47" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48">
+        <v>1</v>
+      </c>
+      <c r="C48" t="s">
+        <v>92</v>
+      </c>
+      <c r="D48">
+        <v>3</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J48" t="s">
+        <v>41</v>
+      </c>
+      <c r="K48" t="s">
+        <v>44</v>
+      </c>
+      <c r="L48" t="s">
+        <v>45</v>
+      </c>
+      <c r="M48" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>18</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49" t="s">
+        <v>92</v>
+      </c>
+      <c r="D49">
+        <v>3</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
+      </c>
+      <c r="F49">
+        <v>0.3</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J49" t="s">
+        <v>42</v>
+      </c>
+      <c r="K49" t="s">
+        <v>44</v>
+      </c>
+      <c r="L49" t="s">
+        <v>45</v>
+      </c>
+      <c r="M49" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>19</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s">
+        <v>92</v>
+      </c>
+      <c r="D50">
+        <v>3</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+      <c r="F50">
+        <v>0.1</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J50" t="s">
+        <v>43</v>
+      </c>
+      <c r="K50" t="s">
+        <v>44</v>
+      </c>
+      <c r="L50" t="s">
+        <v>45</v>
+      </c>
+      <c r="M50" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>22</v>
+      </c>
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51" t="s">
+        <v>92</v>
+      </c>
+      <c r="D51">
+        <v>3</v>
+      </c>
+      <c r="E51">
+        <v>1</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J51" t="s">
+        <v>48</v>
+      </c>
+      <c r="K51" t="s">
+        <v>52</v>
+      </c>
+      <c r="L51" t="s">
+        <v>53</v>
+      </c>
+      <c r="M51" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>23</v>
+      </c>
+      <c r="B52">
+        <v>1</v>
+      </c>
+      <c r="C52" t="s">
+        <v>92</v>
+      </c>
+      <c r="D52">
+        <v>3</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J52" t="s">
+        <v>49</v>
+      </c>
+      <c r="K52" t="s">
+        <v>52</v>
+      </c>
+      <c r="L52" t="s">
+        <v>53</v>
+      </c>
+      <c r="M52" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>24</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53" t="s">
+        <v>92</v>
+      </c>
+      <c r="D53">
+        <v>3</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+      <c r="F53">
+        <v>0.3</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J53" t="s">
+        <v>50</v>
+      </c>
+      <c r="K53" t="s">
+        <v>52</v>
+      </c>
+      <c r="L53" t="s">
+        <v>53</v>
+      </c>
+      <c r="M53" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>25</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54" t="s">
+        <v>92</v>
+      </c>
+      <c r="D54">
+        <v>3</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+      <c r="F54">
+        <v>0.1</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J54" t="s">
+        <v>51</v>
+      </c>
+      <c r="K54" t="s">
+        <v>52</v>
+      </c>
+      <c r="L54" t="s">
+        <v>53</v>
+      </c>
+      <c r="M54" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>26</v>
+      </c>
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="C55" t="s">
+        <v>92</v>
+      </c>
+      <c r="D55">
+        <v>3</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J55" t="s">
+        <v>56</v>
+      </c>
+      <c r="K55" t="s">
+        <v>60</v>
+      </c>
+      <c r="L55" t="s">
+        <v>61</v>
+      </c>
+      <c r="M55" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>27</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="C56" t="s">
+        <v>92</v>
+      </c>
+      <c r="D56">
+        <v>3</v>
+      </c>
+      <c r="E56">
+        <v>1</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J56" t="s">
+        <v>57</v>
+      </c>
+      <c r="K56" t="s">
+        <v>60</v>
+      </c>
+      <c r="L56" t="s">
+        <v>61</v>
+      </c>
+      <c r="M56" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>28</v>
+      </c>
+      <c r="B57">
+        <v>1</v>
+      </c>
+      <c r="C57" t="s">
+        <v>92</v>
+      </c>
+      <c r="D57">
+        <v>3</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
+      </c>
+      <c r="F57">
+        <v>0.3</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J57" t="s">
+        <v>58</v>
+      </c>
+      <c r="K57" t="s">
+        <v>60</v>
+      </c>
+      <c r="L57" t="s">
+        <v>61</v>
+      </c>
+      <c r="M57" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>29</v>
+      </c>
+      <c r="B58">
+        <v>1</v>
+      </c>
+      <c r="C58" t="s">
+        <v>92</v>
+      </c>
+      <c r="D58">
+        <v>3</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+      <c r="F58">
+        <v>0.1</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J58" t="s">
+        <v>59</v>
+      </c>
+      <c r="K58" t="s">
+        <v>60</v>
+      </c>
+      <c r="L58" t="s">
+        <v>61</v>
+      </c>
+      <c r="M58" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>20</v>
+      </c>
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59" t="s">
+        <v>92</v>
+      </c>
+      <c r="D59">
+        <v>3</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J59" t="s">
+        <v>63</v>
+      </c>
+      <c r="K59" t="s">
+        <v>65</v>
+      </c>
+      <c r="L59" t="s">
+        <v>66</v>
+      </c>
+      <c r="M59" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>21</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60" t="s">
+        <v>92</v>
+      </c>
+      <c r="D60">
+        <v>3</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J60" t="s">
+        <v>64</v>
+      </c>
+      <c r="K60" t="s">
+        <v>65</v>
+      </c>
+      <c r="L60" t="s">
+        <v>66</v>
+      </c>
+      <c r="M60" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>30</v>
+      </c>
+      <c r="B61">
+        <v>0</v>
+      </c>
+      <c r="C61" t="s">
+        <v>92</v>
+      </c>
+      <c r="D61">
+        <v>3</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J61" t="s">
+        <v>76</v>
+      </c>
+      <c r="K61" t="s">
+        <v>77</v>
+      </c>
+      <c r="L61" t="s">
+        <v>78</v>
+      </c>
+      <c r="M61" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>31</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62" t="s">
+        <v>92</v>
+      </c>
+      <c r="D62">
+        <v>3</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J62" t="s">
+        <v>81</v>
+      </c>
+      <c r="K62" t="s">
+        <v>82</v>
+      </c>
+      <c r="L62" t="s">
+        <v>83</v>
+      </c>
+      <c r="M62" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>32</v>
+      </c>
+      <c r="B63">
+        <v>0</v>
+      </c>
+      <c r="C63" t="s">
+        <v>92</v>
+      </c>
+      <c r="D63">
+        <v>3</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+      <c r="F63">
+        <v>1</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J63" t="s">
+        <v>84</v>
+      </c>
+      <c r="K63" t="s">
+        <v>85</v>
+      </c>
+      <c r="L63" t="s">
+        <v>86</v>
+      </c>
+      <c r="M63" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>33</v>
+      </c>
+      <c r="B64">
+        <v>1</v>
+      </c>
+      <c r="C64" t="s">
+        <v>92</v>
+      </c>
+      <c r="D64">
+        <v>3</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J64" t="s">
+        <v>87</v>
+      </c>
+      <c r="K64" t="s">
+        <v>88</v>
+      </c>
+      <c r="L64" t="s">
+        <v>89</v>
+      </c>
+      <c r="M64" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>7</v>
+      </c>
+      <c r="B65">
+        <v>1</v>
+      </c>
+      <c r="C65" t="s">
+        <v>92</v>
+      </c>
+      <c r="D65">
+        <v>3</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J65" t="s">
+        <v>69</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L65" t="s">
+        <v>72</v>
+      </c>
+      <c r="M65" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>8</v>
+      </c>
+      <c r="B66">
+        <v>1</v>
+      </c>
+      <c r="C66" t="s">
+        <v>92</v>
+      </c>
+      <c r="D66">
+        <v>3</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+      <c r="F66">
+        <v>1</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J66" t="s">
+        <v>70</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L66" t="s">
+        <v>71</v>
+      </c>
+      <c r="M66" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>11</v>
+      </c>
+      <c r="B67">
+        <v>1</v>
+      </c>
+      <c r="C67" t="s">
+        <v>91</v>
+      </c>
+      <c r="D67">
+        <v>3</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J67" t="s">
+        <v>69</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L67" t="s">
+        <v>72</v>
+      </c>
+      <c r="M67" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
         <v>12</v>
       </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25" t="s">
-        <v>96</v>
-      </c>
-      <c r="D25">
+      <c r="B68">
+        <v>1</v>
+      </c>
+      <c r="C68" t="s">
+        <v>91</v>
+      </c>
+      <c r="D68">
         <v>3</v>
       </c>
-      <c r="E25">
-        <v>1</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25" s="1" t="s">
+      <c r="E68">
+        <v>1</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="H68" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="I68" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="J25" t="s">
+      <c r="J68" t="s">
+        <v>70</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L68" t="s">
         <v>71</v>
       </c>
-      <c r="K25" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="L25" t="s">
-        <v>72</v>
-      </c>
-      <c r="M25" t="s">
-        <v>76</v>
+      <c r="M68" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B1:B1048576">
+  <conditionalFormatting sqref="B1 B11 B47:B1048576">
+    <cfRule type="cellIs" dxfId="26" priority="29" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2">
+    <cfRule type="cellIs" dxfId="25" priority="26" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3">
+    <cfRule type="cellIs" dxfId="24" priority="25" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4">
+    <cfRule type="cellIs" dxfId="23" priority="24" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5">
+    <cfRule type="cellIs" dxfId="22" priority="23" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="cellIs" dxfId="21" priority="22" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7">
+    <cfRule type="cellIs" dxfId="20" priority="21" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8">
+    <cfRule type="cellIs" dxfId="19" priority="20" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B9">
+    <cfRule type="cellIs" dxfId="18" priority="19" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10">
+    <cfRule type="cellIs" dxfId="17" priority="18" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12">
+    <cfRule type="cellIs" dxfId="16" priority="17" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="cellIs" dxfId="15" priority="16" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="cellIs" dxfId="14" priority="15" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B15">
+    <cfRule type="cellIs" dxfId="13" priority="14" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16">
+    <cfRule type="cellIs" dxfId="12" priority="13" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17">
+    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B18">
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19:B20">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B29:B46">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>

--- a/datasets_test.xlsx
+++ b/datasets_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2023 cytoSR\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF14631-5C60-41F5-8BAC-820DFB05C316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC626084-DC95-40B2-BEC5-117850A3D9F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20970" yWindow="2820" windowWidth="14130" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6765" yWindow="3660" windowWidth="29715" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="233">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -861,6 +861,10 @@
   </si>
   <si>
     <t>I:\Datasets\BioSR\ER\noise_1_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pixel_size</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1458,7 +1462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:N68"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.75" customWidth="1"/>
@@ -1472,7 +1476,7 @@
     <col min="13" max="13" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1512,8 +1516,11 @@
       <c r="M1" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N1" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>94</v>
       </c>
@@ -1553,8 +1560,11 @@
       <c r="M2" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N2">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>95</v>
       </c>
@@ -1594,8 +1604,11 @@
       <c r="M3" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N3">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>96</v>
       </c>
@@ -1635,8 +1648,11 @@
       <c r="M4" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N4">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>97</v>
       </c>
@@ -1676,8 +1692,11 @@
       <c r="M5" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N5">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>98</v>
       </c>
@@ -1717,8 +1736,11 @@
       <c r="M6" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N6">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>99</v>
       </c>
@@ -1758,8 +1780,11 @@
       <c r="M7" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>100</v>
       </c>
@@ -1799,8 +1824,11 @@
       <c r="M8" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>101</v>
       </c>
@@ -1840,8 +1868,11 @@
       <c r="M9" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>102</v>
       </c>
@@ -1881,8 +1912,11 @@
       <c r="M10" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -1922,8 +1956,11 @@
       <c r="M11" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>103</v>
       </c>
@@ -1963,8 +2000,11 @@
       <c r="M12" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>104</v>
       </c>
@@ -2004,8 +2044,11 @@
       <c r="M13" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>105</v>
       </c>
@@ -2045,8 +2088,11 @@
       <c r="M14" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>106</v>
       </c>
@@ -2086,8 +2132,11 @@
       <c r="M15" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>107</v>
       </c>
@@ -2127,8 +2176,11 @@
       <c r="M16" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N16">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>108</v>
       </c>
@@ -2168,8 +2220,11 @@
       <c r="M17" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N17">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>109</v>
       </c>
@@ -2209,8 +2264,11 @@
       <c r="M18" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N18">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>110</v>
       </c>
@@ -2250,8 +2308,11 @@
       <c r="M19" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N19">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>111</v>
       </c>
@@ -2291,8 +2352,11 @@
       <c r="M20" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N20">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>115</v>
       </c>
@@ -2332,8 +2396,11 @@
       <c r="M21" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N21">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>116</v>
       </c>
@@ -2373,8 +2440,11 @@
       <c r="M22" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N22">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>117</v>
       </c>
@@ -2414,8 +2484,11 @@
       <c r="M23" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N23">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>118</v>
       </c>
@@ -2455,8 +2528,11 @@
       <c r="M24" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N24">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>119</v>
       </c>
@@ -2496,8 +2572,11 @@
       <c r="M25" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N25">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>120</v>
       </c>
@@ -2537,8 +2616,11 @@
       <c r="M26" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N26">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>121</v>
       </c>
@@ -2578,8 +2660,11 @@
       <c r="M27" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N27">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>122</v>
       </c>
@@ -2619,8 +2704,11 @@
       <c r="M28" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N28">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>175</v>
       </c>
@@ -2660,8 +2748,11 @@
       <c r="M29" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N29">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>176</v>
       </c>
@@ -2701,8 +2792,11 @@
       <c r="M30" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N30">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>177</v>
       </c>
@@ -2742,8 +2836,11 @@
       <c r="M31" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N31">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>178</v>
       </c>
@@ -2783,8 +2880,11 @@
       <c r="M32" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N32">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>179</v>
       </c>
@@ -2824,8 +2924,11 @@
       <c r="M33" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N33">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>180</v>
       </c>
@@ -2865,8 +2968,11 @@
       <c r="M34" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N34">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>181</v>
       </c>
@@ -2906,8 +3012,11 @@
       <c r="M35" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N35">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>182</v>
       </c>
@@ -2947,8 +3056,11 @@
       <c r="M36" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N36">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>183</v>
       </c>
@@ -2988,8 +3100,11 @@
       <c r="M37" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N37">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>184</v>
       </c>
@@ -3029,8 +3144,11 @@
       <c r="M38" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N38">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>185</v>
       </c>
@@ -3070,8 +3188,11 @@
       <c r="M39" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N39">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>186</v>
       </c>
@@ -3111,8 +3232,11 @@
       <c r="M40" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N40">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>212</v>
       </c>
@@ -3152,8 +3276,11 @@
       <c r="M41" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N41">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>213</v>
       </c>
@@ -3193,8 +3320,11 @@
       <c r="M42" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N42">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>214</v>
       </c>
@@ -3234,8 +3364,11 @@
       <c r="M43" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N43">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>215</v>
       </c>
@@ -3275,8 +3408,11 @@
       <c r="M44" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N44">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>216</v>
       </c>
@@ -3316,8 +3452,11 @@
       <c r="M45" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N45">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>217</v>
       </c>
@@ -3357,8 +3496,11 @@
       <c r="M46" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N46">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>16</v>
       </c>
@@ -3398,8 +3540,11 @@
       <c r="M47" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N47">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>17</v>
       </c>
@@ -3439,8 +3584,11 @@
       <c r="M48" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N48">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -3480,8 +3628,11 @@
       <c r="M49" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N49">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>19</v>
       </c>
@@ -3521,8 +3672,11 @@
       <c r="M50" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N50">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>22</v>
       </c>
@@ -3562,8 +3716,11 @@
       <c r="M51" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N51">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>23</v>
       </c>
@@ -3603,8 +3760,11 @@
       <c r="M52" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N52">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>24</v>
       </c>
@@ -3644,8 +3804,11 @@
       <c r="M53" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N53">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>25</v>
       </c>
@@ -3685,8 +3848,11 @@
       <c r="M54" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N54">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>26</v>
       </c>
@@ -3726,8 +3892,11 @@
       <c r="M55" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N55">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>27</v>
       </c>
@@ -3767,8 +3936,11 @@
       <c r="M56" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N56">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>28</v>
       </c>
@@ -3808,8 +3980,11 @@
       <c r="M57" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N57">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>29</v>
       </c>
@@ -3849,8 +4024,11 @@
       <c r="M58" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N58">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>20</v>
       </c>
@@ -3890,8 +4068,11 @@
       <c r="M59" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N59">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>21</v>
       </c>
@@ -3931,8 +4112,11 @@
       <c r="M60" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N60">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>30</v>
       </c>
@@ -3972,8 +4156,11 @@
       <c r="M61" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N61">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>31</v>
       </c>
@@ -4013,8 +4200,11 @@
       <c r="M62" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N62">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>32</v>
       </c>
@@ -4054,8 +4244,11 @@
       <c r="M63" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N63">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>33</v>
       </c>
@@ -4095,8 +4288,11 @@
       <c r="M64" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N64">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>7</v>
       </c>
@@ -4136,8 +4332,11 @@
       <c r="M65" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N65">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>8</v>
       </c>
@@ -4177,8 +4376,11 @@
       <c r="M66" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N66">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>11</v>
       </c>
@@ -4218,8 +4420,11 @@
       <c r="M67" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N67">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>12</v>
       </c>
@@ -4258,6 +4463,9 @@
       </c>
       <c r="M68" t="s">
         <v>75</v>
+      </c>
+      <c r="N68">
+        <v>62.6</v>
       </c>
     </row>
   </sheetData>

--- a/datasets_test.xlsx
+++ b/datasets_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2023 cytoSR\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC626084-DC95-40B2-BEC5-117850A3D9F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB357AC7-B559-4747-B4BB-4EC632E15D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6765" yWindow="3660" windowWidth="29715" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5655" yWindow="1620" windowWidth="29715" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="232">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -58,14 +58,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ZeroShotDeconvNet-simutrain-642</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ZeroShotDeconvNet-simutrain-560</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>(3,31,31)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -74,14 +66,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ZeroShotDeconvNet-ss-642</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ZeroShotDeconvNet-ss-560</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ker_std_init</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -865,6 +849,18 @@
   </si>
   <si>
     <t>pixel_size</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>slice_space</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZeroShotDeconvNet-mitosis-642</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZeroShotDeconvNet-mitosis-560</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1462,7 +1458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N68"/>
+  <dimension ref="A1:O66"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.75" customWidth="1"/>
@@ -1476,24 +1472,24 @@
     <col min="13" max="13" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D1" t="s">
         <v>6</v>
       </c>
       <c r="E1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
@@ -1502,33 +1498,36 @@
         <v>3</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D2">
         <v>2</v>
@@ -1540,39 +1539,42 @@
         <v>1</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="K2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="L2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="M2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N2">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1584,39 +1586,42 @@
         <v>1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="K3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="L3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="M3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N3">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -1628,39 +1633,42 @@
         <v>1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J4" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="K4" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="L4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="M4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N4">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -1672,39 +1680,42 @@
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="K5" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="L5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="M5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N5">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -1716,39 +1727,42 @@
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J6" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="K6" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="L6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="M6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N6">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -1760,39 +1774,42 @@
         <v>1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J7" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="K7" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="L7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="M7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N7">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -1804,39 +1821,42 @@
         <v>1</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J8" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K8" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="L8" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="M8" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N8">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -1848,39 +1868,42 @@
         <v>1</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J9" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="K9" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="L9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="M9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N9">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D10">
         <v>2</v>
@@ -1892,39 +1915,42 @@
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J10" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="K10" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="L10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="M10" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N10">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -1936,39 +1962,42 @@
         <v>1</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J11" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="K11" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="L11" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="M11" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N11">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -1980,39 +2009,42 @@
         <v>1</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J12" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="K12" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L12" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="M12" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N12">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -2024,39 +2056,42 @@
         <v>1</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J13" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="K13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="L13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="M13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N13">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -2068,39 +2103,42 @@
         <v>1</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J14" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="K14" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="L14" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="M14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N14">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D15">
         <v>2</v>
@@ -2112,39 +2150,42 @@
         <v>1</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J15" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="K15" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L15" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="M15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N15">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -2156,39 +2197,42 @@
         <v>1</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J16" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="K16" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="L16" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="M16" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N16">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -2200,39 +2244,42 @@
         <v>1</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J17" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="K17" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L17" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="M17" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N17">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -2244,39 +2291,42 @@
         <v>1</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J18" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="K18" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L18" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="M18" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N18">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D19">
         <v>2</v>
@@ -2288,39 +2338,42 @@
         <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J19" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="K19" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="L19" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="M19" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N19">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D20">
         <v>2</v>
@@ -2332,39 +2385,42 @@
         <v>1</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J20" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="K20" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="L20" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="M20" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N20">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D21">
         <v>2</v>
@@ -2376,39 +2432,42 @@
         <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J21" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="K21" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="L21" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="M21" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N21">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D22">
         <v>2</v>
@@ -2420,39 +2479,42 @@
         <v>1</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J22" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="K22" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="L22" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="M22" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N22">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D23">
         <v>2</v>
@@ -2464,39 +2526,42 @@
         <v>1</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J23" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="K23" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="L23" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="M23" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N23">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -2508,39 +2573,42 @@
         <v>1</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J24" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="K24" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L24" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="M24" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N24">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D25">
         <v>2</v>
@@ -2552,39 +2620,42 @@
         <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J25" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="K25" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L25" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="M25" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N25">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D26">
         <v>2</v>
@@ -2596,39 +2667,42 @@
         <v>1</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J26" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="K26" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L26" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="M26" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N26">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -2640,39 +2714,42 @@
         <v>1</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J27" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="K27" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="L27" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="M27" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N27">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D28">
         <v>2</v>
@@ -2684,39 +2761,42 @@
         <v>1</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J28" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="K28" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="L28" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="M28" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N28">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D29">
         <v>2</v>
@@ -2728,39 +2808,42 @@
         <v>1</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J29" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="K29" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="L29" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="M29" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N29">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D30">
         <v>2</v>
@@ -2772,39 +2855,42 @@
         <v>1</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J30" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="K30" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="L30" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="M30" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N30">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D31">
         <v>2</v>
@@ -2816,39 +2902,42 @@
         <v>1</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J31" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="K31" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="L31" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="M31" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N31">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D32">
         <v>2</v>
@@ -2860,39 +2949,42 @@
         <v>1</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J32" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="K32" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L32" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="M32" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N32">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B33">
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -2904,39 +2996,42 @@
         <v>1</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J33" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="K33" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="L33" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="M33" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N33">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B34">
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D34">
         <v>2</v>
@@ -2948,39 +3043,42 @@
         <v>1</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J34" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="K34" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="L34" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="M34" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N34">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D35">
         <v>2</v>
@@ -2992,39 +3090,42 @@
         <v>1</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J35" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="K35" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="L35" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="M35" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N35">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B36">
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D36">
         <v>2</v>
@@ -3036,83 +3137,89 @@
         <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J36" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="K36" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L36" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="M36" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N36">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
+        <v>179</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
+        <v>88</v>
+      </c>
+      <c r="D37">
+        <v>2</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J37" t="s">
+        <v>204</v>
+      </c>
+      <c r="K37" t="s">
+        <v>192</v>
+      </c>
+      <c r="L37" t="s">
         <v>183</v>
       </c>
-      <c r="B37">
-        <v>1</v>
-      </c>
-      <c r="C37" t="s">
-        <v>92</v>
-      </c>
-      <c r="D37">
-        <v>2</v>
-      </c>
-      <c r="E37">
-        <v>1</v>
-      </c>
-      <c r="F37">
-        <v>1</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J37" t="s">
-        <v>208</v>
-      </c>
-      <c r="K37" t="s">
-        <v>196</v>
-      </c>
-      <c r="L37" t="s">
-        <v>187</v>
-      </c>
       <c r="M37" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N37">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B38">
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D38">
         <v>2</v>
@@ -3124,39 +3231,42 @@
         <v>1</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J38" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="K38" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="L38" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="M38" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N38">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B39">
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D39">
         <v>2</v>
@@ -3168,39 +3278,42 @@
         <v>1</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J39" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="K39" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="L39" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="M39" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N39">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D40">
         <v>2</v>
@@ -3212,39 +3325,42 @@
         <v>1</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J40" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="K40" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="L40" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="M40" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N40">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B41">
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D41">
         <v>2</v>
@@ -3256,39 +3372,42 @@
         <v>1</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J41" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="K41" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="L41" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="M41" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N41">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D42">
         <v>2</v>
@@ -3300,83 +3419,89 @@
         <v>1</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J42" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="K42" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="L42" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="M42" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N42">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
+        <v>210</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
+        <v>88</v>
+      </c>
+      <c r="D43">
+        <v>2</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J43" t="s">
+        <v>224</v>
+      </c>
+      <c r="K43" t="s">
+        <v>217</v>
+      </c>
+      <c r="L43" t="s">
         <v>214</v>
       </c>
-      <c r="B43">
-        <v>1</v>
-      </c>
-      <c r="C43" t="s">
-        <v>92</v>
-      </c>
-      <c r="D43">
-        <v>2</v>
-      </c>
-      <c r="E43">
-        <v>1</v>
-      </c>
-      <c r="F43">
-        <v>1</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J43" t="s">
-        <v>228</v>
-      </c>
-      <c r="K43" t="s">
-        <v>221</v>
-      </c>
-      <c r="L43" t="s">
-        <v>218</v>
-      </c>
       <c r="M43" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N43">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B44">
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D44">
         <v>2</v>
@@ -3388,39 +3513,42 @@
         <v>1</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J44" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="K44" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="L44" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="M44" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N44">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B45">
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -3432,39 +3560,42 @@
         <v>1</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J45" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="K45" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="L45" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="M45" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N45">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B46">
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D46">
         <v>2</v>
@@ -3476,39 +3607,42 @@
         <v>1</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J46" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="K46" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="L46" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="M46" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N46">
         <v>62.6</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B47">
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D47">
         <v>3</v>
@@ -3526,33 +3660,36 @@
         <v>4</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J47" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="K47" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="L47" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="M47" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="N47">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="O47">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B48">
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D48">
         <v>3</v>
@@ -3570,33 +3707,36 @@
         <v>4</v>
       </c>
       <c r="I48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J48" t="s">
+        <v>37</v>
+      </c>
+      <c r="K48" t="s">
+        <v>40</v>
+      </c>
+      <c r="L48" t="s">
+        <v>41</v>
+      </c>
+      <c r="M48" t="s">
+        <v>43</v>
+      </c>
+      <c r="N48">
+        <v>25</v>
+      </c>
+      <c r="O48">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
         <v>14</v>
       </c>
-      <c r="J48" t="s">
-        <v>41</v>
-      </c>
-      <c r="K48" t="s">
-        <v>44</v>
-      </c>
-      <c r="L48" t="s">
-        <v>45</v>
-      </c>
-      <c r="M48" t="s">
-        <v>47</v>
-      </c>
-      <c r="N48">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>18</v>
-      </c>
       <c r="B49">
         <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D49">
         <v>3</v>
@@ -3614,33 +3754,36 @@
         <v>4</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J49" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="K49" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="L49" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="M49" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="N49">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="O49">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B50">
         <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D50">
         <v>3</v>
@@ -3658,33 +3801,36 @@
         <v>4</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J50" t="s">
+        <v>39</v>
+      </c>
+      <c r="K50" t="s">
+        <v>40</v>
+      </c>
+      <c r="L50" t="s">
+        <v>41</v>
+      </c>
+      <c r="M50" t="s">
         <v>43</v>
       </c>
-      <c r="K50" t="s">
-        <v>44</v>
-      </c>
-      <c r="L50" t="s">
-        <v>45</v>
-      </c>
-      <c r="M50" t="s">
-        <v>47</v>
-      </c>
       <c r="N50">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="O50">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B51">
         <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D51">
         <v>3</v>
@@ -3702,33 +3848,36 @@
         <v>4</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J51" t="s">
+        <v>44</v>
+      </c>
+      <c r="K51" t="s">
         <v>48</v>
       </c>
-      <c r="K51" t="s">
-        <v>52</v>
-      </c>
       <c r="L51" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M51" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="N51">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="O51">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B52">
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D52">
         <v>3</v>
@@ -3746,33 +3895,36 @@
         <v>4</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J52" t="s">
+        <v>45</v>
+      </c>
+      <c r="K52" t="s">
+        <v>48</v>
+      </c>
+      <c r="L52" t="s">
         <v>49</v>
       </c>
-      <c r="K52" t="s">
-        <v>52</v>
-      </c>
-      <c r="L52" t="s">
-        <v>53</v>
-      </c>
       <c r="M52" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="N52">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="O52">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B53">
         <v>1</v>
       </c>
       <c r="C53" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D53">
         <v>3</v>
@@ -3790,33 +3942,36 @@
         <v>4</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J53" t="s">
+        <v>46</v>
+      </c>
+      <c r="K53" t="s">
+        <v>48</v>
+      </c>
+      <c r="L53" t="s">
+        <v>49</v>
+      </c>
+      <c r="M53" t="s">
         <v>50</v>
       </c>
-      <c r="K53" t="s">
-        <v>52</v>
-      </c>
-      <c r="L53" t="s">
-        <v>53</v>
-      </c>
-      <c r="M53" t="s">
-        <v>54</v>
-      </c>
       <c r="N53">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="O53">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B54">
         <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D54">
         <v>3</v>
@@ -3834,33 +3989,36 @@
         <v>4</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J54" t="s">
+        <v>47</v>
+      </c>
+      <c r="K54" t="s">
+        <v>48</v>
+      </c>
+      <c r="L54" t="s">
+        <v>49</v>
+      </c>
+      <c r="M54" t="s">
         <v>51</v>
       </c>
-      <c r="K54" t="s">
-        <v>52</v>
-      </c>
-      <c r="L54" t="s">
-        <v>53</v>
-      </c>
-      <c r="M54" t="s">
-        <v>55</v>
-      </c>
       <c r="N54">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="O54">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B55">
         <v>1</v>
       </c>
       <c r="C55" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D55">
         <v>3</v>
@@ -3878,33 +4036,36 @@
         <v>4</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J55" t="s">
+        <v>52</v>
+      </c>
+      <c r="K55" t="s">
         <v>56</v>
       </c>
-      <c r="K55" t="s">
-        <v>60</v>
-      </c>
       <c r="L55" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="M55" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="N55">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="O55">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B56">
         <v>1</v>
       </c>
       <c r="C56" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D56">
         <v>3</v>
@@ -3922,33 +4083,36 @@
         <v>4</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J56" t="s">
+        <v>53</v>
+      </c>
+      <c r="K56" t="s">
+        <v>56</v>
+      </c>
+      <c r="L56" t="s">
         <v>57</v>
       </c>
-      <c r="K56" t="s">
-        <v>60</v>
-      </c>
-      <c r="L56" t="s">
-        <v>61</v>
-      </c>
       <c r="M56" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="N56">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="O56">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B57">
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D57">
         <v>3</v>
@@ -3966,33 +4130,36 @@
         <v>4</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J57" t="s">
+        <v>54</v>
+      </c>
+      <c r="K57" t="s">
+        <v>56</v>
+      </c>
+      <c r="L57" t="s">
+        <v>57</v>
+      </c>
+      <c r="M57" t="s">
         <v>58</v>
       </c>
-      <c r="K57" t="s">
-        <v>60</v>
-      </c>
-      <c r="L57" t="s">
-        <v>61</v>
-      </c>
-      <c r="M57" t="s">
-        <v>62</v>
-      </c>
       <c r="N57">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="O57">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B58">
         <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D58">
         <v>3</v>
@@ -4010,33 +4177,36 @@
         <v>4</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J58" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="K58" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="L58" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="M58" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="N58">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="O58">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B59">
         <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D59">
         <v>3</v>
@@ -4054,33 +4224,36 @@
         <v>5</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J59" t="s">
+        <v>59</v>
+      </c>
+      <c r="K59" t="s">
+        <v>61</v>
+      </c>
+      <c r="L59" t="s">
+        <v>62</v>
+      </c>
+      <c r="M59" t="s">
         <v>63</v>
       </c>
-      <c r="K59" t="s">
-        <v>65</v>
-      </c>
-      <c r="L59" t="s">
-        <v>66</v>
-      </c>
-      <c r="M59" t="s">
-        <v>67</v>
-      </c>
       <c r="N59">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="O59">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B60">
         <v>1</v>
       </c>
       <c r="C60" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D60">
         <v>3</v>
@@ -4098,33 +4271,36 @@
         <v>5</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J60" t="s">
+        <v>60</v>
+      </c>
+      <c r="K60" t="s">
+        <v>61</v>
+      </c>
+      <c r="L60" t="s">
+        <v>62</v>
+      </c>
+      <c r="M60" t="s">
         <v>64</v>
       </c>
-      <c r="K60" t="s">
-        <v>65</v>
-      </c>
-      <c r="L60" t="s">
-        <v>66</v>
-      </c>
-      <c r="M60" t="s">
-        <v>68</v>
-      </c>
       <c r="N60">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="O60">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B61">
         <v>0</v>
       </c>
       <c r="C61" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D61">
         <v>3</v>
@@ -4136,39 +4312,42 @@
         <v>1</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J61" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="K61" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="L61" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="M61" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N61">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="O61">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B62">
         <v>1</v>
       </c>
       <c r="C62" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D62">
         <v>3</v>
@@ -4180,39 +4359,42 @@
         <v>1</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J62" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="K62" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="L62" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="M62" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N62">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="O62">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B63">
         <v>0</v>
       </c>
       <c r="C63" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D63">
         <v>3</v>
@@ -4224,39 +4406,42 @@
         <v>1</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J63" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K63" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="L63" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M63" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N63">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="O63">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B64">
         <v>1</v>
       </c>
       <c r="C64" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D64">
         <v>3</v>
@@ -4268,39 +4453,42 @@
         <v>1</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J64" t="s">
+        <v>83</v>
+      </c>
+      <c r="K64" t="s">
+        <v>84</v>
+      </c>
+      <c r="L64" t="s">
+        <v>85</v>
+      </c>
+      <c r="M64" t="s">
+        <v>69</v>
+      </c>
+      <c r="N64">
+        <v>25</v>
+      </c>
+      <c r="O64">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>230</v>
+      </c>
+      <c r="B65">
+        <v>1</v>
+      </c>
+      <c r="C65" t="s">
         <v>87</v>
-      </c>
-      <c r="K64" t="s">
-        <v>88</v>
-      </c>
-      <c r="L64" t="s">
-        <v>89</v>
-      </c>
-      <c r="M64" t="s">
-        <v>73</v>
-      </c>
-      <c r="N64">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>7</v>
-      </c>
-      <c r="B65">
-        <v>1</v>
-      </c>
-      <c r="C65" t="s">
-        <v>92</v>
       </c>
       <c r="D65">
         <v>3</v>
@@ -4318,33 +4506,36 @@
         <v>5</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J65" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="L65" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="M65" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="N65">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
+        <v>92.6</v>
+      </c>
+      <c r="O65">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>8</v>
+        <v>231</v>
       </c>
       <c r="B66">
         <v>1</v>
       </c>
       <c r="C66" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D66">
         <v>3</v>
@@ -4362,110 +4553,25 @@
         <v>5</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J66" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="L66" t="s">
+        <v>67</v>
+      </c>
+      <c r="M66" t="s">
         <v>71</v>
       </c>
-      <c r="M66" t="s">
-        <v>75</v>
-      </c>
       <c r="N66">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>11</v>
-      </c>
-      <c r="B67">
-        <v>1</v>
-      </c>
-      <c r="C67" t="s">
-        <v>91</v>
-      </c>
-      <c r="D67">
-        <v>3</v>
-      </c>
-      <c r="E67">
-        <v>1</v>
-      </c>
-      <c r="F67">
-        <v>1</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J67" t="s">
-        <v>69</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L67" t="s">
-        <v>72</v>
-      </c>
-      <c r="M67" t="s">
-        <v>74</v>
-      </c>
-      <c r="N67">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>12</v>
-      </c>
-      <c r="B68">
-        <v>1</v>
-      </c>
-      <c r="C68" t="s">
-        <v>91</v>
-      </c>
-      <c r="D68">
-        <v>3</v>
-      </c>
-      <c r="E68">
-        <v>1</v>
-      </c>
-      <c r="F68">
-        <v>1</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J68" t="s">
-        <v>70</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L68" t="s">
-        <v>71</v>
-      </c>
-      <c r="M68" t="s">
-        <v>75</v>
-      </c>
-      <c r="N68">
-        <v>62.6</v>
+        <v>92.6</v>
+      </c>
+      <c r="O66">
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/datasets_test.xlsx
+++ b/datasets_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2023 cytoSR\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB357AC7-B559-4747-B4BB-4EC632E15D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4F72F5-7F3A-4EBA-AF58-ED4CE3B430C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5655" yWindow="1620" windowWidth="29715" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3675,10 +3675,10 @@
         <v>43</v>
       </c>
       <c r="N47">
-        <v>25</v>
+        <v>162.5</v>
       </c>
       <c r="O47">
-        <v>160</v>
+        <v>162.5</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.2">
@@ -3722,10 +3722,10 @@
         <v>43</v>
       </c>
       <c r="N48">
-        <v>25</v>
+        <v>162.5</v>
       </c>
       <c r="O48">
-        <v>160</v>
+        <v>162.5</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.2">
@@ -3769,10 +3769,10 @@
         <v>43</v>
       </c>
       <c r="N49">
-        <v>25</v>
+        <v>162.5</v>
       </c>
       <c r="O49">
-        <v>160</v>
+        <v>162.5</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.2">
@@ -3816,10 +3816,10 @@
         <v>43</v>
       </c>
       <c r="N50">
-        <v>25</v>
+        <v>162.5</v>
       </c>
       <c r="O50">
-        <v>160</v>
+        <v>162.5</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.2">
@@ -3863,10 +3863,10 @@
         <v>50</v>
       </c>
       <c r="N51">
-        <v>25</v>
+        <v>162.5</v>
       </c>
       <c r="O51">
-        <v>160</v>
+        <v>162.5</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.2">
@@ -3910,10 +3910,10 @@
         <v>50</v>
       </c>
       <c r="N52">
-        <v>25</v>
+        <v>162.5</v>
       </c>
       <c r="O52">
-        <v>160</v>
+        <v>162.5</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.2">
@@ -3957,10 +3957,10 @@
         <v>50</v>
       </c>
       <c r="N53">
-        <v>25</v>
+        <v>162.5</v>
       </c>
       <c r="O53">
-        <v>160</v>
+        <v>162.5</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.2">
@@ -4004,10 +4004,10 @@
         <v>51</v>
       </c>
       <c r="N54">
-        <v>25</v>
+        <v>162.5</v>
       </c>
       <c r="O54">
-        <v>160</v>
+        <v>162.5</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.2">
@@ -4051,10 +4051,10 @@
         <v>58</v>
       </c>
       <c r="N55">
-        <v>25</v>
+        <v>162.5</v>
       </c>
       <c r="O55">
-        <v>160</v>
+        <v>162.5</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.2">
@@ -4098,10 +4098,10 @@
         <v>58</v>
       </c>
       <c r="N56">
-        <v>25</v>
+        <v>162.5</v>
       </c>
       <c r="O56">
-        <v>160</v>
+        <v>162.5</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.2">
@@ -4145,10 +4145,10 @@
         <v>58</v>
       </c>
       <c r="N57">
-        <v>25</v>
+        <v>162.5</v>
       </c>
       <c r="O57">
-        <v>160</v>
+        <v>162.5</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.2">
@@ -4192,10 +4192,10 @@
         <v>58</v>
       </c>
       <c r="N58">
-        <v>25</v>
+        <v>162.5</v>
       </c>
       <c r="O58">
-        <v>160</v>
+        <v>162.5</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.2">
@@ -4239,10 +4239,10 @@
         <v>63</v>
       </c>
       <c r="N59">
-        <v>25</v>
+        <v>92.6</v>
       </c>
       <c r="O59">
-        <v>160</v>
+        <v>200</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.2">
@@ -4286,10 +4286,10 @@
         <v>64</v>
       </c>
       <c r="N60">
-        <v>25</v>
+        <v>92.6</v>
       </c>
       <c r="O60">
-        <v>160</v>
+        <v>200</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.2">

--- a/datasets_test.xlsx
+++ b/datasets_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2023 cytoSR\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4F72F5-7F3A-4EBA-AF58-ED4CE3B430C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87AFAA80-50D6-4FAD-A677-3DC39B49B028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5655" yWindow="1620" windowWidth="29715" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2970" yWindow="4395" windowWidth="29715" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="236">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -862,6 +862,19 @@
   <si>
     <t>ZeroShotDeconvNet-mitosis-560</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SirDNA-1024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\raw_1024x1024</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\gt_1024x1024</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\test_1024x1024.txt</t>
   </si>
 </sst>
 </file>
@@ -1458,7 +1471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O66"/>
+  <dimension ref="A1:O67"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.75" customWidth="1"/>
@@ -4572,6 +4585,53 @@
       </c>
       <c r="O66">
         <v>200</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A67" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B67">
+        <v>1</v>
+      </c>
+      <c r="C67" t="s">
+        <v>88</v>
+      </c>
+      <c r="D67">
+        <v>3</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J67" t="s">
+        <v>233</v>
+      </c>
+      <c r="K67" t="s">
+        <v>234</v>
+      </c>
+      <c r="L67" t="s">
+        <v>235</v>
+      </c>
+      <c r="M67" t="s">
+        <v>69</v>
+      </c>
+      <c r="N67">
+        <v>25</v>
+      </c>
+      <c r="O67">
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/datasets_test.xlsx
+++ b/datasets_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2023 cytoSR\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87AFAA80-50D6-4FAD-A677-3DC39B49B028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55655E2F-6FDB-4A5E-8571-CCDE213A964B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2970" yWindow="4395" windowWidth="29715" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20235" yWindow="1740" windowWidth="16785" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="290">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -868,13 +868,200 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\raw_1024x1024</t>
-  </si>
-  <si>
     <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\gt_1024x1024</t>
   </si>
   <si>
     <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\test_1024x1024.txt</t>
+  </si>
+  <si>
+    <t>SirDNA-1024-live-cell-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\raw_live\test_cell1.txt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\raw_live\test_cell2.txt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\raw_live\test_cell3.txt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\raw_live\test_cell4.txt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\raw_live\test_cell5.txt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\raw_live\test_cell6.txt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\raw_live\test_cell7.txt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\raw_live\test_cell8.txt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\raw_live\test_cell9.txt</t>
+  </si>
+  <si>
+    <t>SirDNA-1024-live-cell-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SirDNA-1024-live-cell-3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SirDNA-1024-live-cell-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SirDNA-1024-live-cell-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SirDNA-1024-live-cell-6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SirDNA-1024-live-cell-7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SirDNA-1024-live-cell-8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SirDNA-1024-live-cell-9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\raw_live\cell1_rescale_filter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\raw_live\cell2_rescale_filter</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\raw_live\cell3_rescale_filter</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\raw_live\cell4_rescale_filter</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\raw_live\cell5_rescale_filter</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\raw_live\cell6_rescale_filter</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\raw_live\cell7_rescale_filter</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\raw_live\cell8_rescale_filter</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\raw_live\cell9_rescale_filter</t>
+  </si>
+  <si>
+    <t>SirDNA-1024-train</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\train_1024x1024_0_1.txt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\raw_1024x1024_filter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>su</t>
+  </si>
+  <si>
+    <t>biotisr-ccps-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biotisr-ccps-2</t>
+  </si>
+  <si>
+    <t>biotisr-ccps-3</t>
+  </si>
+  <si>
+    <t>biotisr-factin-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biotisr-factin-2</t>
+  </si>
+  <si>
+    <t>biotisr-factin-3</t>
+  </si>
+  <si>
+    <t>biotisr-factin-nonlinear-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biotisr-factin-nonlinear-2</t>
+  </si>
+  <si>
+    <t>biotisr-factin-nonlinear-3</t>
+  </si>
+  <si>
+    <t>biotisr-mt-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biotisr-mt-2</t>
+  </si>
+  <si>
+    <t>biotisr-mt-3</t>
+  </si>
+  <si>
+    <t>biotisr-mito-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biotisr-mito-2</t>
+  </si>
+  <si>
+    <t>biotisr-mito-3</t>
+  </si>
+  <si>
+    <t>(31,31)</t>
+  </si>
+  <si>
+    <t>deepbacs-ecoli</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deepbacs-saureus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sim-actin-3d</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vmsim3-mito</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vmsim5-mito</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vmsim488-patch-512</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vmsim568-patch-512</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vmsim647-patch-512</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -924,7 +1111,27 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="29">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1471,7 +1678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O67"/>
+  <dimension ref="A1:O100"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.75" customWidth="1"/>
@@ -4616,13 +4823,13 @@
         <v>10</v>
       </c>
       <c r="J67" t="s">
+        <v>264</v>
+      </c>
+      <c r="K67" t="s">
         <v>233</v>
       </c>
-      <c r="K67" t="s">
+      <c r="L67" t="s">
         <v>234</v>
-      </c>
-      <c r="L67" t="s">
-        <v>235</v>
       </c>
       <c r="M67" t="s">
         <v>69</v>
@@ -4634,139 +4841,1493 @@
         <v>160</v>
       </c>
     </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A68" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
+      </c>
+      <c r="C68" t="s">
+        <v>88</v>
+      </c>
+      <c r="D68">
+        <v>3</v>
+      </c>
+      <c r="E68">
+        <v>1</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J68" t="s">
+        <v>264</v>
+      </c>
+      <c r="K68" t="s">
+        <v>233</v>
+      </c>
+      <c r="L68" t="s">
+        <v>263</v>
+      </c>
+      <c r="M68" t="s">
+        <v>69</v>
+      </c>
+      <c r="N68">
+        <v>25</v>
+      </c>
+      <c r="O68">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>235</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
+      </c>
+      <c r="C69" t="s">
+        <v>88</v>
+      </c>
+      <c r="D69">
+        <v>3</v>
+      </c>
+      <c r="E69">
+        <v>1</v>
+      </c>
+      <c r="F69">
+        <v>1</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J69" t="s">
+        <v>253</v>
+      </c>
+      <c r="K69" t="s">
+        <v>253</v>
+      </c>
+      <c r="L69" t="s">
+        <v>236</v>
+      </c>
+      <c r="M69" t="s">
+        <v>69</v>
+      </c>
+      <c r="N69">
+        <v>25</v>
+      </c>
+      <c r="O69">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>245</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
+      </c>
+      <c r="C70" t="s">
+        <v>88</v>
+      </c>
+      <c r="D70">
+        <v>3</v>
+      </c>
+      <c r="E70">
+        <v>1</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J70" t="s">
+        <v>254</v>
+      </c>
+      <c r="K70" t="s">
+        <v>254</v>
+      </c>
+      <c r="L70" t="s">
+        <v>237</v>
+      </c>
+      <c r="M70" t="s">
+        <v>69</v>
+      </c>
+      <c r="N70">
+        <v>25</v>
+      </c>
+      <c r="O70">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>246</v>
+      </c>
+      <c r="B71">
+        <v>1</v>
+      </c>
+      <c r="C71" t="s">
+        <v>88</v>
+      </c>
+      <c r="D71">
+        <v>3</v>
+      </c>
+      <c r="E71">
+        <v>1</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J71" t="s">
+        <v>255</v>
+      </c>
+      <c r="K71" t="s">
+        <v>255</v>
+      </c>
+      <c r="L71" t="s">
+        <v>238</v>
+      </c>
+      <c r="M71" t="s">
+        <v>69</v>
+      </c>
+      <c r="N71">
+        <v>25</v>
+      </c>
+      <c r="O71">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>247</v>
+      </c>
+      <c r="B72">
+        <v>1</v>
+      </c>
+      <c r="C72" t="s">
+        <v>88</v>
+      </c>
+      <c r="D72">
+        <v>3</v>
+      </c>
+      <c r="E72">
+        <v>1</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J72" t="s">
+        <v>256</v>
+      </c>
+      <c r="K72" t="s">
+        <v>256</v>
+      </c>
+      <c r="L72" t="s">
+        <v>239</v>
+      </c>
+      <c r="M72" t="s">
+        <v>69</v>
+      </c>
+      <c r="N72">
+        <v>25</v>
+      </c>
+      <c r="O72">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>248</v>
+      </c>
+      <c r="B73">
+        <v>1</v>
+      </c>
+      <c r="C73" t="s">
+        <v>88</v>
+      </c>
+      <c r="D73">
+        <v>3</v>
+      </c>
+      <c r="E73">
+        <v>1</v>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J73" t="s">
+        <v>257</v>
+      </c>
+      <c r="K73" t="s">
+        <v>257</v>
+      </c>
+      <c r="L73" t="s">
+        <v>240</v>
+      </c>
+      <c r="M73" t="s">
+        <v>69</v>
+      </c>
+      <c r="N73">
+        <v>25</v>
+      </c>
+      <c r="O73">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>249</v>
+      </c>
+      <c r="B74">
+        <v>1</v>
+      </c>
+      <c r="C74" t="s">
+        <v>88</v>
+      </c>
+      <c r="D74">
+        <v>3</v>
+      </c>
+      <c r="E74">
+        <v>1</v>
+      </c>
+      <c r="F74">
+        <v>1</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J74" t="s">
+        <v>258</v>
+      </c>
+      <c r="K74" t="s">
+        <v>258</v>
+      </c>
+      <c r="L74" t="s">
+        <v>241</v>
+      </c>
+      <c r="M74" t="s">
+        <v>69</v>
+      </c>
+      <c r="N74">
+        <v>25</v>
+      </c>
+      <c r="O74">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>250</v>
+      </c>
+      <c r="B75">
+        <v>1</v>
+      </c>
+      <c r="C75" t="s">
+        <v>88</v>
+      </c>
+      <c r="D75">
+        <v>3</v>
+      </c>
+      <c r="E75">
+        <v>1</v>
+      </c>
+      <c r="F75">
+        <v>1</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J75" t="s">
+        <v>259</v>
+      </c>
+      <c r="K75" t="s">
+        <v>259</v>
+      </c>
+      <c r="L75" t="s">
+        <v>242</v>
+      </c>
+      <c r="M75" t="s">
+        <v>69</v>
+      </c>
+      <c r="N75">
+        <v>25</v>
+      </c>
+      <c r="O75">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>251</v>
+      </c>
+      <c r="B76">
+        <v>1</v>
+      </c>
+      <c r="C76" t="s">
+        <v>88</v>
+      </c>
+      <c r="D76">
+        <v>3</v>
+      </c>
+      <c r="E76">
+        <v>1</v>
+      </c>
+      <c r="F76">
+        <v>1</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J76" t="s">
+        <v>260</v>
+      </c>
+      <c r="K76" t="s">
+        <v>260</v>
+      </c>
+      <c r="L76" t="s">
+        <v>243</v>
+      </c>
+      <c r="M76" t="s">
+        <v>69</v>
+      </c>
+      <c r="N76">
+        <v>25</v>
+      </c>
+      <c r="O76">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>252</v>
+      </c>
+      <c r="B77">
+        <v>1</v>
+      </c>
+      <c r="C77" t="s">
+        <v>88</v>
+      </c>
+      <c r="D77">
+        <v>3</v>
+      </c>
+      <c r="E77">
+        <v>1</v>
+      </c>
+      <c r="F77">
+        <v>1</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J77" t="s">
+        <v>261</v>
+      </c>
+      <c r="K77" t="s">
+        <v>261</v>
+      </c>
+      <c r="L77" t="s">
+        <v>244</v>
+      </c>
+      <c r="M77" t="s">
+        <v>69</v>
+      </c>
+      <c r="N77">
+        <v>25</v>
+      </c>
+      <c r="O77">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>266</v>
+      </c>
+      <c r="B78">
+        <v>1</v>
+      </c>
+      <c r="C78" t="s">
+        <v>265</v>
+      </c>
+      <c r="D78">
+        <v>2</v>
+      </c>
+      <c r="E78">
+        <v>1</v>
+      </c>
+      <c r="F78">
+        <v>1</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M78" t="s">
+        <v>69</v>
+      </c>
+      <c r="N78">
+        <v>60.4</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>267</v>
+      </c>
+      <c r="B79">
+        <v>1</v>
+      </c>
+      <c r="C79" t="s">
+        <v>265</v>
+      </c>
+      <c r="D79">
+        <v>2</v>
+      </c>
+      <c r="E79">
+        <v>1</v>
+      </c>
+      <c r="F79">
+        <v>1</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M79" t="s">
+        <v>69</v>
+      </c>
+      <c r="N79">
+        <v>60.4</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>268</v>
+      </c>
+      <c r="B80">
+        <v>1</v>
+      </c>
+      <c r="C80" t="s">
+        <v>265</v>
+      </c>
+      <c r="D80">
+        <v>2</v>
+      </c>
+      <c r="E80">
+        <v>1</v>
+      </c>
+      <c r="F80">
+        <v>1</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M80" t="s">
+        <v>69</v>
+      </c>
+      <c r="N80">
+        <v>60.4</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>269</v>
+      </c>
+      <c r="B81">
+        <v>1</v>
+      </c>
+      <c r="C81" t="s">
+        <v>265</v>
+      </c>
+      <c r="D81">
+        <v>2</v>
+      </c>
+      <c r="E81">
+        <v>1</v>
+      </c>
+      <c r="F81">
+        <v>1</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M81" t="s">
+        <v>69</v>
+      </c>
+      <c r="N81">
+        <v>60.4</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>270</v>
+      </c>
+      <c r="B82">
+        <v>1</v>
+      </c>
+      <c r="C82" t="s">
+        <v>265</v>
+      </c>
+      <c r="D82">
+        <v>2</v>
+      </c>
+      <c r="E82">
+        <v>1</v>
+      </c>
+      <c r="F82">
+        <v>1</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M82" t="s">
+        <v>69</v>
+      </c>
+      <c r="N82">
+        <v>60.4</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>271</v>
+      </c>
+      <c r="B83">
+        <v>1</v>
+      </c>
+      <c r="C83" t="s">
+        <v>265</v>
+      </c>
+      <c r="D83">
+        <v>2</v>
+      </c>
+      <c r="E83">
+        <v>1</v>
+      </c>
+      <c r="F83">
+        <v>1</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M83" t="s">
+        <v>69</v>
+      </c>
+      <c r="N83">
+        <v>60.4</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>272</v>
+      </c>
+      <c r="B84">
+        <v>1</v>
+      </c>
+      <c r="C84" t="s">
+        <v>265</v>
+      </c>
+      <c r="D84">
+        <v>2</v>
+      </c>
+      <c r="E84">
+        <v>1</v>
+      </c>
+      <c r="F84">
+        <v>1</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M84" t="s">
+        <v>69</v>
+      </c>
+      <c r="N84">
+        <v>60.4</v>
+      </c>
+      <c r="O84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>273</v>
+      </c>
+      <c r="B85">
+        <v>1</v>
+      </c>
+      <c r="C85" t="s">
+        <v>265</v>
+      </c>
+      <c r="D85">
+        <v>2</v>
+      </c>
+      <c r="E85">
+        <v>1</v>
+      </c>
+      <c r="F85">
+        <v>1</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M85" t="s">
+        <v>69</v>
+      </c>
+      <c r="N85">
+        <v>60.4</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>274</v>
+      </c>
+      <c r="B86">
+        <v>1</v>
+      </c>
+      <c r="C86" t="s">
+        <v>265</v>
+      </c>
+      <c r="D86">
+        <v>2</v>
+      </c>
+      <c r="E86">
+        <v>1</v>
+      </c>
+      <c r="F86">
+        <v>1</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M86" t="s">
+        <v>69</v>
+      </c>
+      <c r="N86">
+        <v>60.4</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>275</v>
+      </c>
+      <c r="B87">
+        <v>1</v>
+      </c>
+      <c r="C87" t="s">
+        <v>265</v>
+      </c>
+      <c r="D87">
+        <v>2</v>
+      </c>
+      <c r="E87">
+        <v>1</v>
+      </c>
+      <c r="F87">
+        <v>1</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M87" t="s">
+        <v>69</v>
+      </c>
+      <c r="N87">
+        <v>60.4</v>
+      </c>
+      <c r="O87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>276</v>
+      </c>
+      <c r="B88">
+        <v>1</v>
+      </c>
+      <c r="C88" t="s">
+        <v>265</v>
+      </c>
+      <c r="D88">
+        <v>2</v>
+      </c>
+      <c r="E88">
+        <v>1</v>
+      </c>
+      <c r="F88">
+        <v>1</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M88" t="s">
+        <v>69</v>
+      </c>
+      <c r="N88">
+        <v>60.4</v>
+      </c>
+      <c r="O88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>277</v>
+      </c>
+      <c r="B89">
+        <v>1</v>
+      </c>
+      <c r="C89" t="s">
+        <v>265</v>
+      </c>
+      <c r="D89">
+        <v>2</v>
+      </c>
+      <c r="E89">
+        <v>1</v>
+      </c>
+      <c r="F89">
+        <v>1</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M89" t="s">
+        <v>69</v>
+      </c>
+      <c r="N89">
+        <v>60.4</v>
+      </c>
+      <c r="O89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>278</v>
+      </c>
+      <c r="B90">
+        <v>1</v>
+      </c>
+      <c r="C90" t="s">
+        <v>265</v>
+      </c>
+      <c r="D90">
+        <v>2</v>
+      </c>
+      <c r="E90">
+        <v>1</v>
+      </c>
+      <c r="F90">
+        <v>1</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M90" t="s">
+        <v>69</v>
+      </c>
+      <c r="N90">
+        <v>60.4</v>
+      </c>
+      <c r="O90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>279</v>
+      </c>
+      <c r="B91">
+        <v>1</v>
+      </c>
+      <c r="C91" t="s">
+        <v>265</v>
+      </c>
+      <c r="D91">
+        <v>2</v>
+      </c>
+      <c r="E91">
+        <v>1</v>
+      </c>
+      <c r="F91">
+        <v>1</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M91" t="s">
+        <v>69</v>
+      </c>
+      <c r="N91">
+        <v>60.4</v>
+      </c>
+      <c r="O91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>280</v>
+      </c>
+      <c r="B92">
+        <v>1</v>
+      </c>
+      <c r="C92" t="s">
+        <v>265</v>
+      </c>
+      <c r="D92">
+        <v>2</v>
+      </c>
+      <c r="E92">
+        <v>1</v>
+      </c>
+      <c r="F92">
+        <v>1</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M92" t="s">
+        <v>69</v>
+      </c>
+      <c r="N92">
+        <v>60.4</v>
+      </c>
+      <c r="O92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>282</v>
+      </c>
+      <c r="B93">
+        <v>1</v>
+      </c>
+      <c r="C93" t="s">
+        <v>265</v>
+      </c>
+      <c r="D93">
+        <v>2</v>
+      </c>
+      <c r="E93">
+        <v>1</v>
+      </c>
+      <c r="F93">
+        <v>1</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M93" t="s">
+        <v>69</v>
+      </c>
+      <c r="N93">
+        <v>40</v>
+      </c>
+      <c r="O93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>283</v>
+      </c>
+      <c r="B94">
+        <v>1</v>
+      </c>
+      <c r="C94" t="s">
+        <v>265</v>
+      </c>
+      <c r="D94">
+        <v>2</v>
+      </c>
+      <c r="E94">
+        <v>1</v>
+      </c>
+      <c r="F94">
+        <v>1</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M94" t="s">
+        <v>69</v>
+      </c>
+      <c r="N94">
+        <v>40</v>
+      </c>
+      <c r="O94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>284</v>
+      </c>
+      <c r="B95">
+        <v>1</v>
+      </c>
+      <c r="C95" t="s">
+        <v>265</v>
+      </c>
+      <c r="D95">
+        <v>2</v>
+      </c>
+      <c r="E95">
+        <v>1</v>
+      </c>
+      <c r="F95">
+        <v>1</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M95" t="s">
+        <v>69</v>
+      </c>
+      <c r="N95">
+        <v>40</v>
+      </c>
+      <c r="O95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>285</v>
+      </c>
+      <c r="B96">
+        <v>1</v>
+      </c>
+      <c r="C96" t="s">
+        <v>265</v>
+      </c>
+      <c r="D96">
+        <v>2</v>
+      </c>
+      <c r="E96">
+        <v>1</v>
+      </c>
+      <c r="F96">
+        <v>1</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M96" t="s">
+        <v>69</v>
+      </c>
+      <c r="N96">
+        <v>80</v>
+      </c>
+      <c r="O96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>286</v>
+      </c>
+      <c r="B97">
+        <v>1</v>
+      </c>
+      <c r="C97" t="s">
+        <v>265</v>
+      </c>
+      <c r="D97">
+        <v>2</v>
+      </c>
+      <c r="E97">
+        <v>1</v>
+      </c>
+      <c r="F97">
+        <v>1</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M97" t="s">
+        <v>69</v>
+      </c>
+      <c r="N97">
+        <v>80</v>
+      </c>
+      <c r="O97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>287</v>
+      </c>
+      <c r="B98">
+        <v>1</v>
+      </c>
+      <c r="C98" t="s">
+        <v>265</v>
+      </c>
+      <c r="D98">
+        <v>2</v>
+      </c>
+      <c r="E98">
+        <v>1</v>
+      </c>
+      <c r="F98">
+        <v>1</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M98" t="s">
+        <v>69</v>
+      </c>
+      <c r="N98">
+        <v>80</v>
+      </c>
+      <c r="O98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>288</v>
+      </c>
+      <c r="B99">
+        <v>1</v>
+      </c>
+      <c r="C99" t="s">
+        <v>265</v>
+      </c>
+      <c r="D99">
+        <v>2</v>
+      </c>
+      <c r="E99">
+        <v>1</v>
+      </c>
+      <c r="F99">
+        <v>1</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M99" t="s">
+        <v>69</v>
+      </c>
+      <c r="N99">
+        <v>80</v>
+      </c>
+      <c r="O99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>289</v>
+      </c>
+      <c r="B100">
+        <v>1</v>
+      </c>
+      <c r="C100" t="s">
+        <v>265</v>
+      </c>
+      <c r="D100">
+        <v>2</v>
+      </c>
+      <c r="E100">
+        <v>1</v>
+      </c>
+      <c r="F100">
+        <v>1</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M100" t="s">
+        <v>69</v>
+      </c>
+      <c r="N100">
+        <v>80</v>
+      </c>
+      <c r="O100">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B1 B11 B47:B1048576">
-    <cfRule type="cellIs" dxfId="26" priority="29" operator="equal">
+  <conditionalFormatting sqref="B1 B11 B47:B67 B78:B1048576">
+    <cfRule type="cellIs" dxfId="28" priority="31" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
+    <cfRule type="cellIs" dxfId="27" priority="28" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3">
+    <cfRule type="cellIs" dxfId="26" priority="27" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4">
     <cfRule type="cellIs" dxfId="25" priority="26" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B3">
+  <conditionalFormatting sqref="B5">
     <cfRule type="cellIs" dxfId="24" priority="25" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4">
+  <conditionalFormatting sqref="B6">
     <cfRule type="cellIs" dxfId="23" priority="24" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5">
+  <conditionalFormatting sqref="B7">
     <cfRule type="cellIs" dxfId="22" priority="23" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
+  <conditionalFormatting sqref="B8">
     <cfRule type="cellIs" dxfId="21" priority="22" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7">
+  <conditionalFormatting sqref="B9">
     <cfRule type="cellIs" dxfId="20" priority="21" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8">
+  <conditionalFormatting sqref="B10">
     <cfRule type="cellIs" dxfId="19" priority="20" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B9">
+  <conditionalFormatting sqref="B12">
     <cfRule type="cellIs" dxfId="18" priority="19" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B10">
+  <conditionalFormatting sqref="B13">
     <cfRule type="cellIs" dxfId="17" priority="18" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B12">
+  <conditionalFormatting sqref="B14">
     <cfRule type="cellIs" dxfId="16" priority="17" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
+  <conditionalFormatting sqref="B15">
     <cfRule type="cellIs" dxfId="15" priority="16" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
+  <conditionalFormatting sqref="B16">
     <cfRule type="cellIs" dxfId="14" priority="15" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B15">
+  <conditionalFormatting sqref="B17">
     <cfRule type="cellIs" dxfId="13" priority="14" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B16">
+  <conditionalFormatting sqref="B18">
     <cfRule type="cellIs" dxfId="12" priority="13" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B17">
+  <conditionalFormatting sqref="B19:B20">
     <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B18">
+  <conditionalFormatting sqref="B21">
     <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B19:B20">
+  <conditionalFormatting sqref="B22">
     <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B21">
+  <conditionalFormatting sqref="B23">
     <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B22">
+  <conditionalFormatting sqref="B24">
     <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B23">
+  <conditionalFormatting sqref="B25">
     <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B24">
+  <conditionalFormatting sqref="B26">
     <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B25">
+  <conditionalFormatting sqref="B27">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B26">
+  <conditionalFormatting sqref="B28">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B27">
+  <conditionalFormatting sqref="B29:B46">
     <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28">
+  <conditionalFormatting sqref="B69:B77">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B29:B46">
+  <conditionalFormatting sqref="B68">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>

--- a/datasets_test.xlsx
+++ b/datasets_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2023 cytoSR\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55655E2F-6FDB-4A5E-8571-CCDE213A964B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA47ECEB-747A-48FA-92DD-36103625378A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20235" yWindow="1740" windowWidth="16785" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7575" yWindow="2670" windowWidth="16785" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="295">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1062,6 +1062,21 @@
   <si>
     <t>vmsim647-patch-512</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioTISR\transformed\CCPs\SIM_2d-dn-rb_rescale_100.0_avepool_2_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioTISR\transformed\CCPs\WF_noise_level_1_2d_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioTISR\transformed\CCPs\WF_noise_level_2_2d_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioTISR\transformed\CCPs\WF_noise_level_3_2d_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioTISR\transformed\CCPs\test.txt</t>
   </si>
 </sst>
 </file>
@@ -5339,6 +5354,15 @@
       <c r="I78" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="J78" t="s">
+        <v>291</v>
+      </c>
+      <c r="K78" t="s">
+        <v>290</v>
+      </c>
+      <c r="L78" t="s">
+        <v>294</v>
+      </c>
       <c r="M78" t="s">
         <v>69</v>
       </c>
@@ -5377,6 +5401,15 @@
       <c r="I79" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="J79" t="s">
+        <v>292</v>
+      </c>
+      <c r="K79" t="s">
+        <v>290</v>
+      </c>
+      <c r="L79" t="s">
+        <v>294</v>
+      </c>
       <c r="M79" t="s">
         <v>69</v>
       </c>
@@ -5414,6 +5447,15 @@
       </c>
       <c r="I80" s="1" t="s">
         <v>11</v>
+      </c>
+      <c r="J80" t="s">
+        <v>293</v>
+      </c>
+      <c r="K80" t="s">
+        <v>290</v>
+      </c>
+      <c r="L80" t="s">
+        <v>294</v>
       </c>
       <c r="M80" t="s">
         <v>69</v>

--- a/datasets_test.xlsx
+++ b/datasets_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2023 cytoSR\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABDB510C-E48D-4602-925D-1CDD43AA4043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A896B8F0-BDBC-490C-82ED-A32B2DFE8862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5790" yWindow="3840" windowWidth="23550" windowHeight="16170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="23655" windowHeight="16170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="392">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1274,13 +1274,57 @@
   </si>
   <si>
     <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_382\raw_psf_101_gauss_0.5_poiss_1_sf_1_ratio_1_lambda_642\PSF.tif</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_128\test.txt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SimuMix3D-1024-31-05-1-01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_1024\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_1024\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_1024\test.txt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_1024\PSF.tif</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SimuMix3D-512-31-05-1-01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_512\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_512\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_512\test.txt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_512\PSF.tif</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1298,6 +1342,28 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -1333,7 +1399,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1342,11 +1408,37 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="33">
+  <dxfs count="35">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1953,7 +2045,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P112"/>
+  <dimension ref="A1:P114"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.75" customWidth="1"/>
@@ -4569,209 +4661,209 @@
         <v>162.5</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
+    <row r="53" spans="1:16" s="11" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="12" t="s">
         <v>322</v>
       </c>
-      <c r="C53">
-        <v>1</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="C53" s="11">
+        <v>1</v>
+      </c>
+      <c r="D53" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E53">
+      <c r="E53" s="11">
         <v>3</v>
       </c>
-      <c r="F53">
-        <v>1</v>
-      </c>
-      <c r="G53">
+      <c r="F53" s="11">
+        <v>1</v>
+      </c>
+      <c r="G53" s="11">
         <v>0.3</v>
       </c>
-      <c r="H53" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J53" s="1" t="s">
+      <c r="H53" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="I53" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="J53" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="K53" t="s">
+      <c r="K53" s="11" t="s">
         <v>366</v>
       </c>
-      <c r="L53" t="s">
+      <c r="L53" s="11" t="s">
         <v>362</v>
       </c>
-      <c r="M53" t="s">
-        <v>363</v>
-      </c>
-      <c r="N53" t="s">
+      <c r="M53" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="N53" s="11" t="s">
         <v>364</v>
       </c>
-      <c r="O53">
+      <c r="O53" s="11">
         <v>162.5</v>
       </c>
-      <c r="P53">
+      <c r="P53" s="11">
         <v>162.5</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
+    <row r="54" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="9" t="s">
         <v>322</v>
       </c>
-      <c r="C54">
-        <v>1</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="C54" s="8">
+        <v>1</v>
+      </c>
+      <c r="D54" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E54">
+      <c r="E54" s="8">
         <v>3</v>
       </c>
-      <c r="F54">
-        <v>1</v>
-      </c>
-      <c r="G54">
+      <c r="F54" s="8">
+        <v>1</v>
+      </c>
+      <c r="G54" s="8">
         <v>0.1</v>
       </c>
-      <c r="H54" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J54" s="1" t="s">
+      <c r="H54" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="I54" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="J54" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K54" t="s">
+      <c r="K54" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="L54" t="s">
+      <c r="L54" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="M54" t="s">
-        <v>363</v>
-      </c>
-      <c r="N54" t="s">
+      <c r="M54" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="N54" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="O54">
+      <c r="O54" s="8">
         <v>162.5</v>
       </c>
-      <c r="P54">
+      <c r="P54" s="8">
         <v>162.5</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>21</v>
-      </c>
-      <c r="B55" s="4" t="s">
+    <row r="55" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="B55" s="9" t="s">
         <v>322</v>
       </c>
-      <c r="C55">
-        <v>1</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="C55" s="8">
+        <v>1</v>
+      </c>
+      <c r="D55" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E55">
+      <c r="E55" s="8">
         <v>3</v>
       </c>
-      <c r="F55">
-        <v>1</v>
-      </c>
-      <c r="G55">
-        <v>1</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J55" s="1" t="s">
+      <c r="F55" s="8">
+        <v>1</v>
+      </c>
+      <c r="G55" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="H55" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="I55" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="J55" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K55" t="s">
-        <v>368</v>
-      </c>
-      <c r="L55" t="s">
-        <v>369</v>
-      </c>
-      <c r="M55" t="s">
-        <v>370</v>
-      </c>
-      <c r="N55" t="s">
-        <v>371</v>
-      </c>
-      <c r="O55">
+      <c r="K55" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="L55" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="M55" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="N55" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="O55" s="8">
         <v>162.5</v>
       </c>
-      <c r="P55">
+      <c r="P55" s="8">
         <v>162.5</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>22</v>
-      </c>
-      <c r="B56" s="4" t="s">
+    <row r="56" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="B56" s="9" t="s">
         <v>322</v>
       </c>
-      <c r="C56">
-        <v>1</v>
-      </c>
-      <c r="D56" t="s">
+      <c r="C56" s="8">
+        <v>1</v>
+      </c>
+      <c r="D56" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E56">
+      <c r="E56" s="8">
         <v>3</v>
       </c>
-      <c r="F56">
-        <v>1</v>
-      </c>
-      <c r="G56">
-        <v>1</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J56" s="1" t="s">
+      <c r="F56" s="8">
+        <v>1</v>
+      </c>
+      <c r="G56" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="H56" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="I56" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="J56" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K56" t="s">
-        <v>372</v>
-      </c>
-      <c r="L56" t="s">
-        <v>369</v>
-      </c>
-      <c r="M56" t="s">
-        <v>370</v>
-      </c>
-      <c r="N56" t="s">
-        <v>371</v>
-      </c>
-      <c r="O56">
+      <c r="K56" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="L56" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="M56" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="N56" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="O56" s="8">
         <v>162.5</v>
       </c>
-      <c r="P56">
+      <c r="P56" s="8">
         <v>162.5</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>322</v>
@@ -4789,7 +4881,7 @@
         <v>1</v>
       </c>
       <c r="G57">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>2</v>
@@ -4801,7 +4893,7 @@
         <v>9</v>
       </c>
       <c r="K57" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="L57" t="s">
         <v>369</v>
@@ -4819,59 +4911,59 @@
         <v>162.5</v>
       </c>
     </row>
-    <row r="58" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B58" s="7" t="s">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>22</v>
+      </c>
+      <c r="B58" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="C58" s="2">
-        <v>1</v>
-      </c>
-      <c r="D58" s="2" t="s">
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="D58" t="s">
         <v>39</v>
       </c>
-      <c r="E58" s="2">
+      <c r="E58">
         <v>3</v>
       </c>
-      <c r="F58" s="2">
-        <v>1</v>
-      </c>
-      <c r="G58" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J58" s="3" t="s">
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J58" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K58" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="L58" s="2" t="s">
+      <c r="K58" t="s">
+        <v>372</v>
+      </c>
+      <c r="L58" t="s">
         <v>369</v>
       </c>
-      <c r="M58" s="2" t="s">
+      <c r="M58" t="s">
         <v>370</v>
       </c>
-      <c r="N58" s="2" t="s">
+      <c r="N58" t="s">
         <v>371</v>
       </c>
-      <c r="O58" s="2">
+      <c r="O58">
         <v>162.5</v>
       </c>
-      <c r="P58" s="2">
+      <c r="P58">
         <v>162.5</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>322</v>
@@ -4889,39 +4981,39 @@
         <v>1</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J59" s="1" t="s">
         <v>9</v>
       </c>
       <c r="K59" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="L59" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="M59" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="N59" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="O59">
-        <v>92.6</v>
+        <v>162.5</v>
       </c>
       <c r="P59">
-        <v>200</v>
+        <v>162.5</v>
       </c>
     </row>
     <row r="60" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>322</v>
@@ -4939,45 +5031,45 @@
         <v>1</v>
       </c>
       <c r="G60" s="2">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>9</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="O60" s="2">
-        <v>92.6</v>
+        <v>162.5</v>
       </c>
       <c r="P60" s="2">
-        <v>200</v>
+        <v>162.5</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D61" t="s">
         <v>39</v>
@@ -4992,89 +5084,89 @@
         <v>1</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J61" s="1" t="s">
         <v>9</v>
       </c>
       <c r="K61" t="s">
-        <v>119</v>
+        <v>375</v>
       </c>
       <c r="L61" t="s">
-        <v>120</v>
+        <v>376</v>
       </c>
       <c r="M61" t="s">
-        <v>121</v>
+        <v>377</v>
       </c>
       <c r="N61" t="s">
-        <v>36</v>
+        <v>378</v>
       </c>
       <c r="O61">
-        <v>25</v>
+        <v>92.6</v>
       </c>
       <c r="P61">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>26</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="C62">
-        <v>1</v>
-      </c>
-      <c r="D62" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="C62" s="2">
+        <v>1</v>
+      </c>
+      <c r="D62" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E62">
+      <c r="E62" s="2">
         <v>3</v>
       </c>
-      <c r="F62">
-        <v>1</v>
-      </c>
-      <c r="G62">
-        <v>1</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I62" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J62" s="1" t="s">
+      <c r="F62" s="2">
+        <v>1</v>
+      </c>
+      <c r="G62" s="2">
+        <v>1</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K62" t="s">
-        <v>122</v>
-      </c>
-      <c r="L62" t="s">
-        <v>123</v>
-      </c>
-      <c r="M62" t="s">
-        <v>124</v>
-      </c>
-      <c r="N62" t="s">
-        <v>36</v>
-      </c>
-      <c r="O62">
-        <v>25</v>
-      </c>
-      <c r="P62">
-        <v>160</v>
+      <c r="K62" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="N62" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="O62" s="2">
+        <v>92.6</v>
+      </c>
+      <c r="P62" s="2">
+        <v>200</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -5101,13 +5193,13 @@
         <v>9</v>
       </c>
       <c r="K63" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="L63" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="M63" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="N63" t="s">
         <v>36</v>
@@ -5119,68 +5211,68 @@
         <v>160</v>
       </c>
     </row>
-    <row r="64" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="C64" s="5">
-        <v>1</v>
-      </c>
-      <c r="D64" s="5" t="s">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>26</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+      <c r="D64" t="s">
         <v>39</v>
       </c>
-      <c r="E64" s="5">
+      <c r="E64">
         <v>3</v>
       </c>
-      <c r="F64" s="5">
-        <v>1</v>
-      </c>
-      <c r="G64" s="5">
-        <v>1</v>
-      </c>
-      <c r="H64" s="6" t="s">
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I64" s="6" t="s">
+      <c r="I64" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J64" s="6" t="s">
+      <c r="J64" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K64" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="L64" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="M64" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="N64" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="O64" s="5">
+      <c r="K64" t="s">
+        <v>122</v>
+      </c>
+      <c r="L64" t="s">
+        <v>123</v>
+      </c>
+      <c r="M64" t="s">
+        <v>124</v>
+      </c>
+      <c r="N64" t="s">
+        <v>36</v>
+      </c>
+      <c r="O64">
         <v>25</v>
       </c>
-      <c r="P64" s="5">
+      <c r="P64">
         <v>160</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D65" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E65">
         <v>3</v>
@@ -5192,86 +5284,86 @@
         <v>1</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J65" s="1" t="s">
         <v>9</v>
       </c>
       <c r="K65" t="s">
-        <v>131</v>
-      </c>
-      <c r="L65" s="1" t="s">
-        <v>36</v>
+        <v>125</v>
+      </c>
+      <c r="L65" t="s">
+        <v>126</v>
       </c>
       <c r="M65" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="N65" t="s">
-        <v>133</v>
+        <v>36</v>
       </c>
       <c r="O65">
-        <v>92.6</v>
+        <v>25</v>
       </c>
       <c r="P65">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="2" t="s">
-        <v>88</v>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="C66" s="2">
-        <v>1</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E66" s="2">
+        <v>323</v>
+      </c>
+      <c r="C66" s="5">
+        <v>1</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E66" s="5">
         <v>3</v>
       </c>
-      <c r="F66" s="2">
-        <v>1</v>
-      </c>
-      <c r="G66" s="2">
-        <v>1</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J66" s="3" t="s">
+      <c r="F66" s="5">
+        <v>1</v>
+      </c>
+      <c r="G66" s="5">
+        <v>1</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J66" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K66" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="M66" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="N66" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="O66" s="2">
-        <v>92.6</v>
-      </c>
-      <c r="P66" s="2">
-        <v>200</v>
+      <c r="K66" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="L66" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="M66" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="N66" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="O66" s="5">
+        <v>25</v>
+      </c>
+      <c r="P66" s="5">
+        <v>160</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A67" s="1" t="s">
-        <v>89</v>
+      <c r="A67" t="s">
+        <v>87</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>324</v>
@@ -5280,7 +5372,7 @@
         <v>1</v>
       </c>
       <c r="D67" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E67">
         <v>3</v>
@@ -5292,86 +5384,86 @@
         <v>1</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J67" s="1" t="s">
         <v>9</v>
       </c>
       <c r="K67" t="s">
-        <v>137</v>
-      </c>
-      <c r="L67" t="s">
-        <v>138</v>
+        <v>131</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="M67" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="N67" t="s">
-        <v>36</v>
+        <v>133</v>
       </c>
       <c r="O67">
-        <v>25</v>
+        <v>92.6</v>
       </c>
       <c r="P67">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A68" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B68" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B68" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="C68">
-        <v>1</v>
-      </c>
-      <c r="D68" t="s">
-        <v>39</v>
-      </c>
-      <c r="E68">
+      <c r="C68" s="2">
+        <v>1</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E68" s="2">
         <v>3</v>
       </c>
-      <c r="F68">
-        <v>1</v>
-      </c>
-      <c r="G68">
-        <v>1</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J68" s="1" t="s">
+      <c r="F68" s="2">
+        <v>1</v>
+      </c>
+      <c r="G68" s="2">
+        <v>1</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J68" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K68" t="s">
-        <v>137</v>
-      </c>
-      <c r="L68" t="s">
-        <v>138</v>
-      </c>
-      <c r="M68" t="s">
-        <v>140</v>
-      </c>
-      <c r="N68" t="s">
-        <v>36</v>
-      </c>
-      <c r="O68">
-        <v>25</v>
-      </c>
-      <c r="P68">
-        <v>160</v>
+      <c r="K68" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="L68" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="O68" s="2">
+        <v>92.6</v>
+      </c>
+      <c r="P68" s="2">
+        <v>200</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>90</v>
+      <c r="A69" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>324</v>
@@ -5401,13 +5493,13 @@
         <v>9</v>
       </c>
       <c r="K69" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="L69" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="M69" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="N69" t="s">
         <v>36</v>
@@ -5420,8 +5512,8 @@
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>91</v>
+      <c r="A70" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>324</v>
@@ -5451,13 +5543,13 @@
         <v>9</v>
       </c>
       <c r="K70" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="L70" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="M70" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="N70" t="s">
         <v>36</v>
@@ -5471,7 +5563,7 @@
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>324</v>
@@ -5501,13 +5593,13 @@
         <v>9</v>
       </c>
       <c r="K71" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="L71" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M71" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="N71" t="s">
         <v>36</v>
@@ -5521,7 +5613,7 @@
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>324</v>
@@ -5551,13 +5643,13 @@
         <v>9</v>
       </c>
       <c r="K72" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="L72" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="M72" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="N72" t="s">
         <v>36</v>
@@ -5571,7 +5663,7 @@
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>324</v>
@@ -5601,13 +5693,13 @@
         <v>9</v>
       </c>
       <c r="K73" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L73" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="M73" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="N73" t="s">
         <v>36</v>
@@ -5621,7 +5713,7 @@
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>324</v>
@@ -5651,13 +5743,13 @@
         <v>9</v>
       </c>
       <c r="K74" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="L74" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="M74" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="N74" t="s">
         <v>36</v>
@@ -5671,7 +5763,7 @@
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>324</v>
@@ -5701,13 +5793,13 @@
         <v>9</v>
       </c>
       <c r="K75" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="L75" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="M75" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N75" t="s">
         <v>36</v>
@@ -5721,7 +5813,7 @@
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>324</v>
@@ -5751,13 +5843,13 @@
         <v>9</v>
       </c>
       <c r="K76" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L76" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M76" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N76" t="s">
         <v>36</v>
@@ -5769,71 +5861,71 @@
         <v>160</v>
       </c>
     </row>
-    <row r="77" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="2" t="s">
-        <v>98</v>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>96</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="C77" s="2">
-        <v>1</v>
-      </c>
-      <c r="D77" s="2" t="s">
+      <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="D77" t="s">
         <v>39</v>
       </c>
-      <c r="E77" s="2">
+      <c r="E77">
         <v>3</v>
       </c>
-      <c r="F77" s="2">
-        <v>1</v>
-      </c>
-      <c r="G77" s="2">
-        <v>1</v>
-      </c>
-      <c r="H77" s="3" t="s">
+      <c r="F77">
+        <v>1</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+      <c r="H77" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I77" s="3" t="s">
+      <c r="I77" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J77" s="3" t="s">
+      <c r="J77" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K77" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="L77" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="M77" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="N77" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="O77" s="2">
+      <c r="K77" t="s">
+        <v>153</v>
+      </c>
+      <c r="L77" t="s">
+        <v>153</v>
+      </c>
+      <c r="M77" t="s">
+        <v>154</v>
+      </c>
+      <c r="N77" t="s">
+        <v>36</v>
+      </c>
+      <c r="O77">
         <v>25</v>
       </c>
-      <c r="P77" s="2">
+      <c r="P77">
         <v>160</v>
       </c>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C78">
         <v>1</v>
       </c>
       <c r="D78" t="s">
-        <v>100</v>
+        <v>39</v>
       </c>
       <c r="E78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F78">
         <v>1</v>
@@ -5842,86 +5934,86 @@
         <v>1</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>116</v>
+        <v>6</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K78" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="L78" t="s">
+        <v>155</v>
+      </c>
+      <c r="M78" t="s">
+        <v>156</v>
+      </c>
+      <c r="N78" t="s">
+        <v>36</v>
+      </c>
+      <c r="O78">
+        <v>25</v>
+      </c>
+      <c r="P78">
         <v>160</v>
       </c>
-      <c r="M78" t="s">
-        <v>161</v>
-      </c>
-      <c r="N78" t="s">
-        <v>36</v>
-      </c>
-      <c r="O78">
-        <v>60.4</v>
-      </c>
-      <c r="P78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
-        <v>102</v>
+    </row>
+    <row r="79" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="C79">
-        <v>1</v>
-      </c>
-      <c r="D79" t="s">
-        <v>100</v>
-      </c>
-      <c r="E79">
-        <v>2</v>
-      </c>
-      <c r="F79">
-        <v>1</v>
-      </c>
-      <c r="G79">
-        <v>1</v>
-      </c>
-      <c r="H79" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I79" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="J79" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K79" t="s">
-        <v>162</v>
-      </c>
-      <c r="L79" t="s">
+        <v>324</v>
+      </c>
+      <c r="C79" s="2">
+        <v>1</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E79" s="2">
+        <v>3</v>
+      </c>
+      <c r="F79" s="2">
+        <v>1</v>
+      </c>
+      <c r="G79" s="2">
+        <v>1</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="L79" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="M79" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="N79" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O79" s="2">
+        <v>25</v>
+      </c>
+      <c r="P79" s="2">
         <v>160</v>
-      </c>
-      <c r="M79" t="s">
-        <v>161</v>
-      </c>
-      <c r="N79" t="s">
-        <v>36</v>
-      </c>
-      <c r="O79">
-        <v>60.4</v>
-      </c>
-      <c r="P79">
-        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>319</v>
@@ -5951,7 +6043,7 @@
         <v>10</v>
       </c>
       <c r="K80" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="L80" t="s">
         <v>160</v>
@@ -5971,10 +6063,10 @@
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -6001,13 +6093,13 @@
         <v>10</v>
       </c>
       <c r="K81" t="s">
-        <v>271</v>
+        <v>162</v>
       </c>
       <c r="L81" t="s">
-        <v>289</v>
+        <v>160</v>
       </c>
       <c r="M81" t="s">
-        <v>294</v>
+        <v>161</v>
       </c>
       <c r="N81" t="s">
         <v>36</v>
@@ -6021,10 +6113,10 @@
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -6051,13 +6143,13 @@
         <v>10</v>
       </c>
       <c r="K82" t="s">
-        <v>272</v>
+        <v>163</v>
       </c>
       <c r="L82" t="s">
-        <v>289</v>
+        <v>160</v>
       </c>
       <c r="M82" t="s">
-        <v>294</v>
+        <v>161</v>
       </c>
       <c r="N82" t="s">
         <v>36</v>
@@ -6071,7 +6163,7 @@
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>317</v>
@@ -6101,7 +6193,7 @@
         <v>10</v>
       </c>
       <c r="K83" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L83" t="s">
         <v>289</v>
@@ -6121,7 +6213,7 @@
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>317</v>
@@ -6151,13 +6243,13 @@
         <v>10</v>
       </c>
       <c r="K84" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="L84" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M84" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="N84" t="s">
         <v>36</v>
@@ -6171,7 +6263,7 @@
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>317</v>
@@ -6201,13 +6293,13 @@
         <v>10</v>
       </c>
       <c r="K85" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="L85" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M85" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="N85" t="s">
         <v>36</v>
@@ -6221,7 +6313,7 @@
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>317</v>
@@ -6251,7 +6343,7 @@
         <v>10</v>
       </c>
       <c r="K86" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="L86" t="s">
         <v>290</v>
@@ -6271,10 +6363,10 @@
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>286</v>
+        <v>108</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -6301,13 +6393,13 @@
         <v>10</v>
       </c>
       <c r="K87" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="L87" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="M87" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="N87" t="s">
         <v>36</v>
@@ -6321,10 +6413,10 @@
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>287</v>
+        <v>109</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -6351,13 +6443,13 @@
         <v>10</v>
       </c>
       <c r="K88" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="L88" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="M88" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="N88" t="s">
         <v>36</v>
@@ -6371,7 +6463,7 @@
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>325</v>
@@ -6401,7 +6493,7 @@
         <v>10</v>
       </c>
       <c r="K89" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="L89" t="s">
         <v>291</v>
@@ -6421,10 +6513,10 @@
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>110</v>
+        <v>287</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="C90">
         <v>1</v>
@@ -6451,13 +6543,13 @@
         <v>10</v>
       </c>
       <c r="K90" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="L90" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="M90" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="N90" t="s">
         <v>36</v>
@@ -6471,10 +6563,10 @@
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>111</v>
+        <v>288</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="C91">
         <v>1</v>
@@ -6501,13 +6593,13 @@
         <v>10</v>
       </c>
       <c r="K91" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="L91" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="M91" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="N91" t="s">
         <v>36</v>
@@ -6521,7 +6613,7 @@
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>318</v>
@@ -6551,7 +6643,7 @@
         <v>10</v>
       </c>
       <c r="K92" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="L92" t="s">
         <v>292</v>
@@ -6571,10 +6663,10 @@
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C93">
         <v>1</v>
@@ -6601,13 +6693,13 @@
         <v>10</v>
       </c>
       <c r="K93" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="L93" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M93" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="N93" t="s">
         <v>36</v>
@@ -6621,10 +6713,10 @@
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -6651,13 +6743,13 @@
         <v>10</v>
       </c>
       <c r="K94" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="L94" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M94" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="N94" t="s">
         <v>36</v>
@@ -6669,62 +6761,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="2" t="s">
-        <v>115</v>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>113</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="C95" s="2">
-        <v>1</v>
-      </c>
-      <c r="D95" s="2" t="s">
+      <c r="C95">
+        <v>1</v>
+      </c>
+      <c r="D95" t="s">
         <v>100</v>
       </c>
-      <c r="E95" s="2">
-        <v>2</v>
-      </c>
-      <c r="F95" s="2">
-        <v>1</v>
-      </c>
-      <c r="G95" s="2">
-        <v>1</v>
-      </c>
-      <c r="H95" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I95" s="3" t="s">
+      <c r="E95">
+        <v>2</v>
+      </c>
+      <c r="F95">
+        <v>1</v>
+      </c>
+      <c r="G95">
+        <v>1</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I95" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="J95" s="3" t="s">
+      <c r="J95" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K95" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="L95" s="2" t="s">
+      <c r="K95" t="s">
+        <v>283</v>
+      </c>
+      <c r="L95" t="s">
         <v>293</v>
       </c>
-      <c r="M95" s="2" t="s">
+      <c r="M95" t="s">
         <v>298</v>
       </c>
-      <c r="N95" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="O95" s="2">
+      <c r="N95" t="s">
+        <v>36</v>
+      </c>
+      <c r="O95">
         <v>60.4</v>
       </c>
-      <c r="P95" s="2">
+      <c r="P95">
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -6751,80 +6843,80 @@
         <v>10</v>
       </c>
       <c r="K96" t="s">
-        <v>259</v>
+        <v>284</v>
       </c>
       <c r="L96" t="s">
-        <v>260</v>
+        <v>293</v>
       </c>
       <c r="M96" t="s">
-        <v>261</v>
+        <v>298</v>
       </c>
       <c r="N96" t="s">
         <v>36</v>
       </c>
       <c r="O96">
-        <v>80</v>
+        <v>60.4</v>
       </c>
       <c r="P96">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A97" t="s">
-        <v>265</v>
+    <row r="97" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="C97">
-        <v>1</v>
-      </c>
-      <c r="D97" t="s">
+        <v>316</v>
+      </c>
+      <c r="C97" s="2">
+        <v>1</v>
+      </c>
+      <c r="D97" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E97">
-        <v>2</v>
-      </c>
-      <c r="F97">
-        <v>1</v>
-      </c>
-      <c r="G97">
-        <v>1</v>
-      </c>
-      <c r="H97" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I97" s="1" t="s">
+      <c r="E97" s="2">
+        <v>2</v>
+      </c>
+      <c r="F97" s="2">
+        <v>1</v>
+      </c>
+      <c r="G97" s="2">
+        <v>1</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I97" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="J97" s="1" t="s">
+      <c r="J97" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K97" t="s">
-        <v>267</v>
-      </c>
-      <c r="L97" t="s">
-        <v>268</v>
-      </c>
-      <c r="M97" t="s">
-        <v>261</v>
-      </c>
-      <c r="N97" t="s">
-        <v>36</v>
-      </c>
-      <c r="O97">
-        <v>80</v>
-      </c>
-      <c r="P97">
+      <c r="K97" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="L97" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="M97" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="N97" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O97" s="2">
+        <v>60.4</v>
+      </c>
+      <c r="P97" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -6851,13 +6943,13 @@
         <v>10</v>
       </c>
       <c r="K98" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L98" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="M98" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="N98" t="s">
         <v>36</v>
@@ -6869,162 +6961,162 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="2" t="s">
-        <v>266</v>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>265</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="C99" s="2">
-        <v>1</v>
-      </c>
-      <c r="D99" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
+      <c r="D99" t="s">
         <v>100</v>
       </c>
-      <c r="E99" s="2">
-        <v>2</v>
-      </c>
-      <c r="F99" s="2">
-        <v>1</v>
-      </c>
-      <c r="G99" s="2">
-        <v>1</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I99" s="3" t="s">
+      <c r="E99">
+        <v>2</v>
+      </c>
+      <c r="F99">
+        <v>1</v>
+      </c>
+      <c r="G99">
+        <v>1</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I99" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="J99" s="3" t="s">
+      <c r="J99" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K99" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="L99" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="M99" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="N99" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="O99" s="2">
+      <c r="K99" t="s">
+        <v>267</v>
+      </c>
+      <c r="L99" t="s">
+        <v>268</v>
+      </c>
+      <c r="M99" t="s">
+        <v>261</v>
+      </c>
+      <c r="N99" t="s">
+        <v>36</v>
+      </c>
+      <c r="O99">
         <v>80</v>
       </c>
-      <c r="P99" s="2">
+      <c r="P99">
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>299</v>
-      </c>
-      <c r="B100" t="s">
-        <v>316</v>
-      </c>
-      <c r="C100" s="4">
+        <v>118</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="C100">
         <v>1</v>
       </c>
       <c r="D100" t="s">
         <v>100</v>
       </c>
-      <c r="E100" s="4">
-        <v>2</v>
-      </c>
-      <c r="F100" s="4">
-        <v>1</v>
-      </c>
-      <c r="G100" s="4">
+      <c r="E100">
+        <v>2</v>
+      </c>
+      <c r="F100">
+        <v>1</v>
+      </c>
+      <c r="G100">
         <v>1</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>7</v>
+        <v>116</v>
       </c>
       <c r="J100" s="1" t="s">
         <v>10</v>
       </c>
       <c r="K100" t="s">
-        <v>305</v>
+        <v>262</v>
       </c>
       <c r="L100" t="s">
-        <v>306</v>
+        <v>263</v>
       </c>
       <c r="M100" t="s">
-        <v>314</v>
+        <v>264</v>
       </c>
       <c r="N100" t="s">
         <v>36</v>
       </c>
-      <c r="O100" s="4">
+      <c r="O100">
+        <v>80</v>
+      </c>
+      <c r="P100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="C101" s="2">
+        <v>1</v>
+      </c>
+      <c r="D101" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="P100" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
-        <v>300</v>
-      </c>
-      <c r="B101" t="s">
-        <v>316</v>
-      </c>
-      <c r="C101" s="4">
-        <v>1</v>
-      </c>
-      <c r="D101" t="s">
-        <v>100</v>
-      </c>
-      <c r="E101" s="4">
-        <v>2</v>
-      </c>
-      <c r="F101" s="4">
-        <v>1</v>
-      </c>
-      <c r="G101" s="4">
-        <v>1</v>
-      </c>
-      <c r="H101" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J101" s="1" t="s">
+      <c r="E101" s="2">
+        <v>2</v>
+      </c>
+      <c r="F101" s="2">
+        <v>1</v>
+      </c>
+      <c r="G101" s="2">
+        <v>1</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="J101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K101" t="s">
-        <v>307</v>
-      </c>
-      <c r="L101" t="s">
-        <v>306</v>
-      </c>
-      <c r="M101" t="s">
-        <v>314</v>
-      </c>
-      <c r="N101" t="s">
-        <v>36</v>
-      </c>
-      <c r="O101" s="4">
-        <v>100</v>
-      </c>
-      <c r="P101" s="4">
+      <c r="K101" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="L101" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="M101" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="N101" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O101" s="2">
+        <v>80</v>
+      </c>
+      <c r="P101" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B102" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="C102" s="4">
         <v>1</v>
@@ -7051,10 +7143,10 @@
         <v>10</v>
       </c>
       <c r="K102" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="L102" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="M102" t="s">
         <v>314</v>
@@ -7071,10 +7163,10 @@
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B103" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="C103" s="4">
         <v>1</v>
@@ -7101,10 +7193,10 @@
         <v>10</v>
       </c>
       <c r="K103" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="L103" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="M103" t="s">
         <v>314</v>
@@ -7121,10 +7213,10 @@
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B104" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C104" s="4">
         <v>1</v>
@@ -7151,10 +7243,10 @@
         <v>10</v>
       </c>
       <c r="K104" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="L104" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="M104" t="s">
         <v>314</v>
@@ -7169,162 +7261,162 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="2" t="s">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>302</v>
+      </c>
+      <c r="B105" t="s">
+        <v>325</v>
+      </c>
+      <c r="C105" s="4">
+        <v>1</v>
+      </c>
+      <c r="D105" t="s">
+        <v>100</v>
+      </c>
+      <c r="E105" s="4">
+        <v>2</v>
+      </c>
+      <c r="F105" s="4">
+        <v>1</v>
+      </c>
+      <c r="G105" s="4">
+        <v>1</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K105" t="s">
+        <v>310</v>
+      </c>
+      <c r="L105" t="s">
+        <v>309</v>
+      </c>
+      <c r="M105" t="s">
+        <v>314</v>
+      </c>
+      <c r="N105" t="s">
+        <v>36</v>
+      </c>
+      <c r="O105" s="4">
+        <v>100</v>
+      </c>
+      <c r="P105" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>303</v>
+      </c>
+      <c r="B106" t="s">
+        <v>317</v>
+      </c>
+      <c r="C106" s="4">
+        <v>1</v>
+      </c>
+      <c r="D106" t="s">
+        <v>100</v>
+      </c>
+      <c r="E106" s="4">
+        <v>2</v>
+      </c>
+      <c r="F106" s="4">
+        <v>1</v>
+      </c>
+      <c r="G106" s="4">
+        <v>1</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K106" t="s">
+        <v>311</v>
+      </c>
+      <c r="L106" t="s">
+        <v>312</v>
+      </c>
+      <c r="M106" t="s">
+        <v>314</v>
+      </c>
+      <c r="N106" t="s">
+        <v>36</v>
+      </c>
+      <c r="O106" s="4">
+        <v>100</v>
+      </c>
+      <c r="P106" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="B107" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="C105" s="7">
-        <v>1</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E105" s="7">
-        <v>2</v>
-      </c>
-      <c r="F105" s="7">
-        <v>1</v>
-      </c>
-      <c r="G105" s="7">
-        <v>1</v>
-      </c>
-      <c r="H105" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I105" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J105" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K105" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="L105" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="M105" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="N105" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="O105" s="7">
-        <v>100</v>
-      </c>
-      <c r="P105" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A106" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="B106" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="C106" s="4">
-        <v>1</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E106" s="4">
-        <v>3</v>
-      </c>
-      <c r="F106" s="4">
-        <v>1</v>
-      </c>
-      <c r="G106" s="4">
-        <v>1</v>
-      </c>
-      <c r="H106" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I106" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J106" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K106" t="s">
-        <v>336</v>
-      </c>
-      <c r="L106" t="s">
-        <v>337</v>
-      </c>
-      <c r="M106" t="s">
-        <v>344</v>
-      </c>
-      <c r="N106" t="s">
-        <v>36</v>
-      </c>
-      <c r="O106" s="4">
-        <v>61.18</v>
-      </c>
-      <c r="P106" s="4">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A107" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="B107" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="C107" s="4">
+      <c r="C107" s="7">
         <v>1</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E107" s="4">
-        <v>3</v>
-      </c>
-      <c r="F107" s="4">
-        <v>1</v>
-      </c>
-      <c r="G107" s="4">
-        <v>1</v>
-      </c>
-      <c r="H107" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I107" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J107" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K107" t="s">
-        <v>338</v>
-      </c>
-      <c r="L107" t="s">
-        <v>337</v>
-      </c>
-      <c r="M107" t="s">
-        <v>344</v>
-      </c>
-      <c r="N107" t="s">
-        <v>36</v>
-      </c>
-      <c r="O107" s="4">
-        <v>61.18</v>
-      </c>
-      <c r="P107" s="4">
-        <v>135</v>
+      <c r="E107" s="7">
+        <v>2</v>
+      </c>
+      <c r="F107" s="7">
+        <v>1</v>
+      </c>
+      <c r="G107" s="7">
+        <v>1</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I107" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J107" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K107" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="L107" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="M107" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="N107" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O107" s="7">
+        <v>100</v>
+      </c>
+      <c r="P107" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C108" s="4">
         <v>1</v>
@@ -7342,22 +7434,22 @@
         <v>1</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>334</v>
+        <v>6</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>334</v>
+        <v>6</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
       <c r="K108" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="L108" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="M108" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N108" t="s">
         <v>36</v>
@@ -7371,10 +7463,10 @@
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A109" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C109" s="4">
         <v>1</v>
@@ -7392,22 +7484,22 @@
         <v>1</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>334</v>
+        <v>6</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>334</v>
+        <v>6</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
       <c r="K109" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="L109" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="M109" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N109" t="s">
         <v>36</v>
@@ -7421,10 +7513,10 @@
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A110" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C110" s="4">
         <v>1</v>
@@ -7451,13 +7543,13 @@
         <v>335</v>
       </c>
       <c r="K110" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="L110" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="M110" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="N110" t="s">
         <v>36</v>
@@ -7471,10 +7563,10 @@
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C111" s="4">
         <v>1</v>
@@ -7501,13 +7593,13 @@
         <v>335</v>
       </c>
       <c r="K111" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="L111" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="M111" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="N111" t="s">
         <v>36</v>
@@ -7521,7 +7613,7 @@
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A112" s="4" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>316</v>
@@ -7542,22 +7634,22 @@
         <v>1</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="J112" s="1" t="s">
         <v>335</v>
       </c>
       <c r="K112" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="L112" t="s">
         <v>343</v>
       </c>
       <c r="M112" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="N112" t="s">
         <v>36</v>
@@ -7569,169 +7661,279 @@
         <v>135</v>
       </c>
     </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A113" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C113" s="4">
+        <v>1</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E113" s="4">
+        <v>3</v>
+      </c>
+      <c r="F113" s="4">
+        <v>1</v>
+      </c>
+      <c r="G113" s="4">
+        <v>1</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="J113" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="K113" t="s">
+        <v>347</v>
+      </c>
+      <c r="L113" t="s">
+        <v>343</v>
+      </c>
+      <c r="M113" t="s">
+        <v>348</v>
+      </c>
+      <c r="N113" t="s">
+        <v>36</v>
+      </c>
+      <c r="O113" s="4">
+        <v>61.18</v>
+      </c>
+      <c r="P113" s="4">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A114" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C114" s="4">
+        <v>1</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E114" s="4">
+        <v>3</v>
+      </c>
+      <c r="F114" s="4">
+        <v>1</v>
+      </c>
+      <c r="G114" s="4">
+        <v>1</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="J114" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="K114" t="s">
+        <v>347</v>
+      </c>
+      <c r="L114" t="s">
+        <v>343</v>
+      </c>
+      <c r="M114" t="s">
+        <v>348</v>
+      </c>
+      <c r="N114" t="s">
+        <v>36</v>
+      </c>
+      <c r="O114" s="4">
+        <v>61.18</v>
+      </c>
+      <c r="P114" s="4">
+        <v>135</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C1 C11 C47:C67 C78:C86 C98 C90:C96 C100:C111 C113:C1048576">
-    <cfRule type="cellIs" dxfId="32" priority="35" operator="equal">
+  <conditionalFormatting sqref="C1 C11 C47:C54 C80:C88 C100 C92:C98 C102:C113 C115:C1048576 C57:C69">
+    <cfRule type="cellIs" dxfId="34" priority="37" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2">
+    <cfRule type="cellIs" dxfId="33" priority="34" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3">
+    <cfRule type="cellIs" dxfId="32" priority="33" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4">
     <cfRule type="cellIs" dxfId="31" priority="32" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3">
+  <conditionalFormatting sqref="C5">
     <cfRule type="cellIs" dxfId="30" priority="31" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4">
+  <conditionalFormatting sqref="C6">
     <cfRule type="cellIs" dxfId="29" priority="30" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C5">
+  <conditionalFormatting sqref="C7">
     <cfRule type="cellIs" dxfId="28" priority="29" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C6">
+  <conditionalFormatting sqref="C8">
     <cfRule type="cellIs" dxfId="27" priority="28" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C7">
+  <conditionalFormatting sqref="C9">
     <cfRule type="cellIs" dxfId="26" priority="27" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C8">
+  <conditionalFormatting sqref="C10">
     <cfRule type="cellIs" dxfId="25" priority="26" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C9">
+  <conditionalFormatting sqref="C12">
     <cfRule type="cellIs" dxfId="24" priority="25" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C10">
+  <conditionalFormatting sqref="C13">
     <cfRule type="cellIs" dxfId="23" priority="24" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C12">
+  <conditionalFormatting sqref="C14">
     <cfRule type="cellIs" dxfId="22" priority="23" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C13">
+  <conditionalFormatting sqref="C15">
     <cfRule type="cellIs" dxfId="21" priority="22" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14">
+  <conditionalFormatting sqref="C16">
     <cfRule type="cellIs" dxfId="20" priority="21" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C15">
+  <conditionalFormatting sqref="C17">
     <cfRule type="cellIs" dxfId="19" priority="20" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16">
+  <conditionalFormatting sqref="C18">
     <cfRule type="cellIs" dxfId="18" priority="19" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17">
+  <conditionalFormatting sqref="C19:C20">
     <cfRule type="cellIs" dxfId="17" priority="18" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18">
+  <conditionalFormatting sqref="C21">
     <cfRule type="cellIs" dxfId="16" priority="17" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C19:C20">
+  <conditionalFormatting sqref="C22">
     <cfRule type="cellIs" dxfId="15" priority="16" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21">
+  <conditionalFormatting sqref="C23">
     <cfRule type="cellIs" dxfId="14" priority="15" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22">
+  <conditionalFormatting sqref="C24">
     <cfRule type="cellIs" dxfId="13" priority="14" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C23">
+  <conditionalFormatting sqref="C25">
     <cfRule type="cellIs" dxfId="12" priority="13" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24">
+  <conditionalFormatting sqref="C26">
     <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C25">
+  <conditionalFormatting sqref="C27">
     <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C26">
+  <conditionalFormatting sqref="C28">
     <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C27">
+  <conditionalFormatting sqref="C29:C46">
     <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C28">
+  <conditionalFormatting sqref="C71:C79">
     <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C29:C46">
+  <conditionalFormatting sqref="C70">
     <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C69:C77">
+  <conditionalFormatting sqref="C99">
     <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C68">
+  <conditionalFormatting sqref="C101">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C97">
+  <conditionalFormatting sqref="C89:C91">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C99">
+  <conditionalFormatting sqref="C114">
     <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C87:C89">
+  <conditionalFormatting sqref="C56">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C112">
+  <conditionalFormatting sqref="C55">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>

--- a/datasets_test.xlsx
+++ b/datasets_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2023 cytoSR\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A896B8F0-BDBC-490C-82ED-A32B2DFE8862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{006C3524-1F8E-4E0A-81BC-FD778A950A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="23655" windowHeight="16170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="432">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -449,14 +449,6 @@
     <t>(31,31)</t>
   </si>
   <si>
-    <t>deepbacs-ecoli</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>deepbacs-saureus</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>E:\qiqilu\datasets_2\RCAN3D\Confocal_2_STED\Microtubule\raw_1024x1024</t>
   </si>
   <si>
@@ -877,21 +869,9 @@
     <t>E:\qiqilu\datasets_2\BioSR\transformed\ER\noise_1_sf_1\gt</t>
   </si>
   <si>
-    <t>E:\qiqilu\datasets_2\DeepBacs\Ecoli\WF_rescale_100.0_bkgsub_auto</t>
-  </si>
-  <si>
-    <t>E:\qiqilu\datasets_2\DeepBacs\Ecoli\SIM_rescale_100.0_bkgsub_auto</t>
-  </si>
-  <si>
     <t>E:\qiqilu\datasets_2\DeepBacs\Ecoli\test.txt</t>
   </si>
   <si>
-    <t>E:\qiqilu\datasets_2\DeepBacs\Saureus\WF_rescale_100.0_bkgsub_auto</t>
-  </si>
-  <si>
-    <t>E:\qiqilu\datasets_2\DeepBacs\Saureus\SIM_rescale_100.0_bkgsub_auto</t>
-  </si>
-  <si>
     <t>E:\qiqilu\datasets_2\DeepBacs\Saureus\test.txt</t>
   </si>
   <si>
@@ -1317,6 +1297,145 @@
   </si>
   <si>
     <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_512\PSF.tif</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_9_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_8_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_7_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_6_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_5_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_4_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_3_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_2_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_1_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_9_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_8_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_7_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_6_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_5_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_4_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_3_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_2_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_1_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_9_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_8_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_7_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_6_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_5_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_4_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_3_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_2_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_1_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_12_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_11_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_10_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_9_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_8_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_7_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_6_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_5_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_4_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_3_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_2_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_1_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\ER\noise_6_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\ER\noise_5_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\ER\noise_4_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\ER\noise_3_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\ER\noise_2_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\ER\noise_1_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>path_lr_net</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2045,7 +2164,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P114"/>
+  <dimension ref="A1:Q112"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.75" customWidth="1"/>
@@ -2057,16 +2176,18 @@
     <col min="7" max="7" width="4.25" customWidth="1"/>
     <col min="8" max="9" width="9.5" style="1" customWidth="1"/>
     <col min="10" max="10" width="10.375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="40.125" customWidth="1"/>
-    <col min="14" max="14" width="8" customWidth="1"/>
+    <col min="11" max="11" width="87.25" customWidth="1"/>
+    <col min="12" max="12" width="94.5" customWidth="1"/>
+    <col min="13" max="13" width="9.375" customWidth="1"/>
+    <col min="15" max="15" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C1" t="s">
         <v>40</v>
@@ -2096,27 +2217,30 @@
         <v>32</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -2143,30 +2267,33 @@
         <v>10</v>
       </c>
       <c r="K2" t="s">
+        <v>386</v>
+      </c>
+      <c r="L2" t="s">
+        <v>162</v>
+      </c>
+      <c r="M2" t="s">
+        <v>163</v>
+      </c>
+      <c r="N2" t="s">
         <v>164</v>
       </c>
-      <c r="L2" t="s">
-        <v>165</v>
-      </c>
-      <c r="M2" t="s">
-        <v>166</v>
-      </c>
-      <c r="N2" t="s">
-        <v>36</v>
-      </c>
-      <c r="O2">
+      <c r="O2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P2">
         <v>62.6</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -2193,30 +2320,33 @@
         <v>10</v>
       </c>
       <c r="K3" t="s">
-        <v>167</v>
+        <v>387</v>
       </c>
       <c r="L3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="M3" t="s">
         <v>166</v>
       </c>
       <c r="N3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O3">
+        <v>164</v>
+      </c>
+      <c r="O3" t="s">
+        <v>36</v>
+      </c>
+      <c r="P3">
         <v>62.6</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -2243,30 +2373,33 @@
         <v>10</v>
       </c>
       <c r="K4" t="s">
-        <v>169</v>
+        <v>388</v>
       </c>
       <c r="L4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="M4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="N4" t="s">
-        <v>36</v>
-      </c>
-      <c r="O4">
+        <v>164</v>
+      </c>
+      <c r="O4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P4">
         <v>62.6</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -2293,30 +2426,33 @@
         <v>10</v>
       </c>
       <c r="K5" t="s">
-        <v>171</v>
+        <v>389</v>
       </c>
       <c r="L5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="M5" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="N5" t="s">
-        <v>36</v>
-      </c>
-      <c r="O5">
+        <v>164</v>
+      </c>
+      <c r="O5" t="s">
+        <v>36</v>
+      </c>
+      <c r="P5">
         <v>62.6</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -2343,30 +2479,33 @@
         <v>10</v>
       </c>
       <c r="K6" t="s">
-        <v>173</v>
+        <v>390</v>
       </c>
       <c r="L6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="M6" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N6" t="s">
-        <v>36</v>
-      </c>
-      <c r="O6">
+        <v>164</v>
+      </c>
+      <c r="O6" t="s">
+        <v>36</v>
+      </c>
+      <c r="P6">
         <v>62.6</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -2393,30 +2532,33 @@
         <v>10</v>
       </c>
       <c r="K7" t="s">
-        <v>175</v>
+        <v>391</v>
       </c>
       <c r="L7" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="M7" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="N7" t="s">
-        <v>36</v>
-      </c>
-      <c r="O7">
+        <v>164</v>
+      </c>
+      <c r="O7" t="s">
+        <v>36</v>
+      </c>
+      <c r="P7">
         <v>62.6</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -2443,30 +2585,33 @@
         <v>10</v>
       </c>
       <c r="K8" t="s">
-        <v>177</v>
+        <v>392</v>
       </c>
       <c r="L8" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="M8" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="N8" t="s">
-        <v>36</v>
-      </c>
-      <c r="O8">
+        <v>164</v>
+      </c>
+      <c r="O8" t="s">
+        <v>36</v>
+      </c>
+      <c r="P8">
         <v>62.6</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -2493,30 +2638,33 @@
         <v>10</v>
       </c>
       <c r="K9" t="s">
-        <v>179</v>
+        <v>393</v>
       </c>
       <c r="L9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="M9" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="N9" t="s">
-        <v>36</v>
-      </c>
-      <c r="O9">
+        <v>164</v>
+      </c>
+      <c r="O9" t="s">
+        <v>36</v>
+      </c>
+      <c r="P9">
         <v>62.6</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -2543,30 +2691,33 @@
         <v>10</v>
       </c>
       <c r="K10" t="s">
-        <v>181</v>
+        <v>394</v>
       </c>
       <c r="L10" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="M10" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="N10" t="s">
-        <v>36</v>
-      </c>
-      <c r="O10">
+        <v>164</v>
+      </c>
+      <c r="O10" t="s">
+        <v>36</v>
+      </c>
+      <c r="P10">
         <v>62.6</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -2593,30 +2744,33 @@
         <v>10</v>
       </c>
       <c r="K11" t="s">
+        <v>395</v>
+      </c>
+      <c r="L11" t="s">
+        <v>181</v>
+      </c>
+      <c r="M11" t="s">
+        <v>182</v>
+      </c>
+      <c r="N11" t="s">
         <v>183</v>
       </c>
-      <c r="L11" t="s">
-        <v>184</v>
-      </c>
-      <c r="M11" t="s">
-        <v>185</v>
-      </c>
-      <c r="N11" t="s">
-        <v>36</v>
-      </c>
-      <c r="O11">
+      <c r="O11" t="s">
+        <v>36</v>
+      </c>
+      <c r="P11">
         <v>62.6</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>50</v>
       </c>
       <c r="B12" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -2643,30 +2797,33 @@
         <v>10</v>
       </c>
       <c r="K12" t="s">
-        <v>186</v>
+        <v>396</v>
       </c>
       <c r="L12" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="M12" t="s">
         <v>185</v>
       </c>
       <c r="N12" t="s">
-        <v>36</v>
-      </c>
-      <c r="O12">
+        <v>183</v>
+      </c>
+      <c r="O12" t="s">
+        <v>36</v>
+      </c>
+      <c r="P12">
         <v>62.6</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>51</v>
       </c>
       <c r="B13" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -2693,30 +2850,33 @@
         <v>10</v>
       </c>
       <c r="K13" t="s">
-        <v>188</v>
+        <v>397</v>
       </c>
       <c r="L13" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="M13" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="N13" t="s">
-        <v>36</v>
-      </c>
-      <c r="O13">
+        <v>183</v>
+      </c>
+      <c r="O13" t="s">
+        <v>36</v>
+      </c>
+      <c r="P13">
         <v>62.6</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -2743,30 +2903,33 @@
         <v>10</v>
       </c>
       <c r="K14" t="s">
-        <v>190</v>
+        <v>398</v>
       </c>
       <c r="L14" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="M14" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="N14" t="s">
-        <v>36</v>
-      </c>
-      <c r="O14">
+        <v>183</v>
+      </c>
+      <c r="O14" t="s">
+        <v>36</v>
+      </c>
+      <c r="P14">
         <v>62.6</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>53</v>
       </c>
       <c r="B15" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -2793,30 +2956,33 @@
         <v>10</v>
       </c>
       <c r="K15" t="s">
-        <v>192</v>
+        <v>399</v>
       </c>
       <c r="L15" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="M15" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="N15" t="s">
-        <v>36</v>
-      </c>
-      <c r="O15">
+        <v>183</v>
+      </c>
+      <c r="O15" t="s">
+        <v>36</v>
+      </c>
+      <c r="P15">
         <v>62.6</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>54</v>
       </c>
       <c r="B16" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -2843,30 +3009,33 @@
         <v>10</v>
       </c>
       <c r="K16" t="s">
-        <v>194</v>
+        <v>400</v>
       </c>
       <c r="L16" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="M16" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="N16" t="s">
-        <v>36</v>
-      </c>
-      <c r="O16">
+        <v>183</v>
+      </c>
+      <c r="O16" t="s">
+        <v>36</v>
+      </c>
+      <c r="P16">
         <v>62.6</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>55</v>
       </c>
       <c r="B17" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -2893,30 +3062,33 @@
         <v>10</v>
       </c>
       <c r="K17" t="s">
-        <v>196</v>
+        <v>401</v>
       </c>
       <c r="L17" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="M17" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s">
-        <v>36</v>
-      </c>
-      <c r="O17">
+        <v>183</v>
+      </c>
+      <c r="O17" t="s">
+        <v>36</v>
+      </c>
+      <c r="P17">
         <v>62.6</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>56</v>
       </c>
       <c r="B18" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -2943,30 +3115,33 @@
         <v>10</v>
       </c>
       <c r="K18" t="s">
-        <v>198</v>
+        <v>402</v>
       </c>
       <c r="L18" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="M18" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="N18" t="s">
-        <v>36</v>
-      </c>
-      <c r="O18">
+        <v>183</v>
+      </c>
+      <c r="O18" t="s">
+        <v>36</v>
+      </c>
+      <c r="P18">
         <v>62.6</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>57</v>
       </c>
       <c r="B19" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -2993,30 +3168,33 @@
         <v>10</v>
       </c>
       <c r="K19" t="s">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="L19" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="M19" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="N19" t="s">
-        <v>36</v>
-      </c>
-      <c r="O19">
+        <v>183</v>
+      </c>
+      <c r="O19" t="s">
+        <v>36</v>
+      </c>
+      <c r="P19">
         <v>62.6</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>58</v>
       </c>
       <c r="B20" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -3043,30 +3221,33 @@
         <v>10</v>
       </c>
       <c r="K20" t="s">
+        <v>404</v>
+      </c>
+      <c r="L20" t="s">
+        <v>200</v>
+      </c>
+      <c r="M20" t="s">
+        <v>201</v>
+      </c>
+      <c r="N20" t="s">
         <v>202</v>
       </c>
-      <c r="L20" t="s">
-        <v>203</v>
-      </c>
-      <c r="M20" t="s">
-        <v>204</v>
-      </c>
-      <c r="N20" t="s">
-        <v>36</v>
-      </c>
-      <c r="O20">
+      <c r="O20" t="s">
+        <v>36</v>
+      </c>
+      <c r="P20">
         <v>62.6</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>59</v>
       </c>
       <c r="B21" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -3093,30 +3274,33 @@
         <v>10</v>
       </c>
       <c r="K21" t="s">
-        <v>205</v>
+        <v>405</v>
       </c>
       <c r="L21" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="M21" t="s">
         <v>204</v>
       </c>
       <c r="N21" t="s">
-        <v>36</v>
-      </c>
-      <c r="O21">
+        <v>202</v>
+      </c>
+      <c r="O21" t="s">
+        <v>36</v>
+      </c>
+      <c r="P21">
         <v>62.6</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>60</v>
       </c>
       <c r="B22" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -3143,30 +3327,33 @@
         <v>10</v>
       </c>
       <c r="K22" t="s">
-        <v>207</v>
+        <v>406</v>
       </c>
       <c r="L22" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="M22" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N22" t="s">
-        <v>36</v>
-      </c>
-      <c r="O22">
+        <v>202</v>
+      </c>
+      <c r="O22" t="s">
+        <v>36</v>
+      </c>
+      <c r="P22">
         <v>62.6</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>61</v>
       </c>
       <c r="B23" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -3193,30 +3380,33 @@
         <v>10</v>
       </c>
       <c r="K23" t="s">
-        <v>209</v>
+        <v>407</v>
       </c>
       <c r="L23" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="M23" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="N23" t="s">
-        <v>36</v>
-      </c>
-      <c r="O23">
+        <v>202</v>
+      </c>
+      <c r="O23" t="s">
+        <v>36</v>
+      </c>
+      <c r="P23">
         <v>62.6</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>62</v>
       </c>
       <c r="B24" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -3243,30 +3433,33 @@
         <v>10</v>
       </c>
       <c r="K24" t="s">
-        <v>211</v>
+        <v>408</v>
       </c>
       <c r="L24" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="M24" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="N24" t="s">
-        <v>36</v>
-      </c>
-      <c r="O24">
+        <v>202</v>
+      </c>
+      <c r="O24" t="s">
+        <v>36</v>
+      </c>
+      <c r="P24">
         <v>62.6</v>
       </c>
-      <c r="P24">
+      <c r="Q24">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>63</v>
       </c>
       <c r="B25" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -3293,30 +3486,33 @@
         <v>10</v>
       </c>
       <c r="K25" t="s">
-        <v>213</v>
+        <v>409</v>
       </c>
       <c r="L25" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="M25" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="N25" t="s">
-        <v>36</v>
-      </c>
-      <c r="O25">
+        <v>202</v>
+      </c>
+      <c r="O25" t="s">
+        <v>36</v>
+      </c>
+      <c r="P25">
         <v>62.6</v>
       </c>
-      <c r="P25">
+      <c r="Q25">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>64</v>
       </c>
       <c r="B26" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -3343,30 +3539,33 @@
         <v>10</v>
       </c>
       <c r="K26" t="s">
-        <v>215</v>
+        <v>410</v>
       </c>
       <c r="L26" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="M26" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="N26" t="s">
-        <v>36</v>
-      </c>
-      <c r="O26">
+        <v>202</v>
+      </c>
+      <c r="O26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P26">
         <v>62.6</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>65</v>
       </c>
       <c r="B27" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -3393,30 +3592,33 @@
         <v>10</v>
       </c>
       <c r="K27" t="s">
-        <v>217</v>
+        <v>411</v>
       </c>
       <c r="L27" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="M27" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="N27" t="s">
-        <v>36</v>
-      </c>
-      <c r="O27">
+        <v>202</v>
+      </c>
+      <c r="O27" t="s">
+        <v>36</v>
+      </c>
+      <c r="P27">
         <v>62.6</v>
       </c>
-      <c r="P27">
+      <c r="Q27">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -3443,30 +3645,33 @@
         <v>10</v>
       </c>
       <c r="K28" t="s">
-        <v>219</v>
+        <v>412</v>
       </c>
       <c r="L28" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="M28" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="N28" t="s">
-        <v>36</v>
-      </c>
-      <c r="O28">
+        <v>202</v>
+      </c>
+      <c r="O28" t="s">
+        <v>36</v>
+      </c>
+      <c r="P28">
         <v>62.6</v>
       </c>
-      <c r="P28">
+      <c r="Q28">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>67</v>
       </c>
       <c r="B29" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -3493,30 +3698,33 @@
         <v>10</v>
       </c>
       <c r="K29" t="s">
+        <v>413</v>
+      </c>
+      <c r="L29" t="s">
+        <v>219</v>
+      </c>
+      <c r="M29" t="s">
+        <v>220</v>
+      </c>
+      <c r="N29" t="s">
         <v>221</v>
       </c>
-      <c r="L29" t="s">
-        <v>222</v>
-      </c>
-      <c r="M29" t="s">
-        <v>223</v>
-      </c>
-      <c r="N29" t="s">
-        <v>36</v>
-      </c>
-      <c r="O29">
+      <c r="O29" t="s">
+        <v>36</v>
+      </c>
+      <c r="P29">
         <v>62.6</v>
       </c>
-      <c r="P29">
+      <c r="Q29">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>68</v>
       </c>
       <c r="B30" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -3543,30 +3751,33 @@
         <v>10</v>
       </c>
       <c r="K30" t="s">
-        <v>224</v>
+        <v>414</v>
       </c>
       <c r="L30" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="M30" t="s">
         <v>223</v>
       </c>
       <c r="N30" t="s">
-        <v>36</v>
-      </c>
-      <c r="O30">
+        <v>221</v>
+      </c>
+      <c r="O30" t="s">
+        <v>36</v>
+      </c>
+      <c r="P30">
         <v>62.6</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>69</v>
       </c>
       <c r="B31" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -3593,30 +3804,33 @@
         <v>10</v>
       </c>
       <c r="K31" t="s">
-        <v>226</v>
+        <v>415</v>
       </c>
       <c r="L31" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M31" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N31" t="s">
-        <v>36</v>
-      </c>
-      <c r="O31">
+        <v>221</v>
+      </c>
+      <c r="O31" t="s">
+        <v>36</v>
+      </c>
+      <c r="P31">
         <v>62.6</v>
       </c>
-      <c r="P31">
+      <c r="Q31">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>70</v>
       </c>
       <c r="B32" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -3643,30 +3857,33 @@
         <v>10</v>
       </c>
       <c r="K32" t="s">
-        <v>228</v>
+        <v>416</v>
       </c>
       <c r="L32" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="M32" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="N32" t="s">
-        <v>36</v>
-      </c>
-      <c r="O32">
+        <v>221</v>
+      </c>
+      <c r="O32" t="s">
+        <v>36</v>
+      </c>
+      <c r="P32">
         <v>62.6</v>
       </c>
-      <c r="P32">
+      <c r="Q32">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>71</v>
       </c>
       <c r="B33" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -3693,30 +3910,33 @@
         <v>10</v>
       </c>
       <c r="K33" t="s">
-        <v>230</v>
+        <v>417</v>
       </c>
       <c r="L33" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="M33" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="N33" t="s">
-        <v>36</v>
-      </c>
-      <c r="O33">
+        <v>221</v>
+      </c>
+      <c r="O33" t="s">
+        <v>36</v>
+      </c>
+      <c r="P33">
         <v>62.6</v>
       </c>
-      <c r="P33">
+      <c r="Q33">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>72</v>
       </c>
       <c r="B34" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -3743,30 +3963,33 @@
         <v>10</v>
       </c>
       <c r="K34" t="s">
-        <v>232</v>
+        <v>418</v>
       </c>
       <c r="L34" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="M34" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="N34" t="s">
-        <v>36</v>
-      </c>
-      <c r="O34">
+        <v>221</v>
+      </c>
+      <c r="O34" t="s">
+        <v>36</v>
+      </c>
+      <c r="P34">
         <v>62.6</v>
       </c>
-      <c r="P34">
+      <c r="Q34">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>73</v>
       </c>
       <c r="B35" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -3793,30 +4016,33 @@
         <v>10</v>
       </c>
       <c r="K35" t="s">
-        <v>234</v>
+        <v>419</v>
       </c>
       <c r="L35" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="M35" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="N35" t="s">
-        <v>36</v>
-      </c>
-      <c r="O35">
+        <v>221</v>
+      </c>
+      <c r="O35" t="s">
+        <v>36</v>
+      </c>
+      <c r="P35">
         <v>62.6</v>
       </c>
-      <c r="P35">
+      <c r="Q35">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>74</v>
       </c>
       <c r="B36" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -3843,30 +4069,33 @@
         <v>10</v>
       </c>
       <c r="K36" t="s">
-        <v>236</v>
+        <v>420</v>
       </c>
       <c r="L36" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="M36" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="N36" t="s">
-        <v>36</v>
-      </c>
-      <c r="O36">
+        <v>221</v>
+      </c>
+      <c r="O36" t="s">
+        <v>36</v>
+      </c>
+      <c r="P36">
         <v>62.6</v>
       </c>
-      <c r="P36">
+      <c r="Q36">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>75</v>
       </c>
       <c r="B37" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -3893,30 +4122,33 @@
         <v>10</v>
       </c>
       <c r="K37" t="s">
-        <v>238</v>
+        <v>421</v>
       </c>
       <c r="L37" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="M37" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="N37" t="s">
-        <v>36</v>
-      </c>
-      <c r="O37">
+        <v>221</v>
+      </c>
+      <c r="O37" t="s">
+        <v>36</v>
+      </c>
+      <c r="P37">
         <v>62.6</v>
       </c>
-      <c r="P37">
+      <c r="Q37">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>76</v>
       </c>
       <c r="B38" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -3943,30 +4175,33 @@
         <v>10</v>
       </c>
       <c r="K38" t="s">
-        <v>240</v>
+        <v>422</v>
       </c>
       <c r="L38" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="M38" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="N38" t="s">
-        <v>36</v>
-      </c>
-      <c r="O38">
+        <v>221</v>
+      </c>
+      <c r="O38" t="s">
+        <v>36</v>
+      </c>
+      <c r="P38">
         <v>62.6</v>
       </c>
-      <c r="P38">
+      <c r="Q38">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>77</v>
       </c>
       <c r="B39" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -3993,30 +4228,33 @@
         <v>10</v>
       </c>
       <c r="K39" t="s">
-        <v>242</v>
+        <v>423</v>
       </c>
       <c r="L39" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="M39" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="N39" t="s">
-        <v>36</v>
-      </c>
-      <c r="O39">
+        <v>221</v>
+      </c>
+      <c r="O39" t="s">
+        <v>36</v>
+      </c>
+      <c r="P39">
         <v>62.6</v>
       </c>
-      <c r="P39">
+      <c r="Q39">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>78</v>
       </c>
       <c r="B40" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -4043,30 +4281,33 @@
         <v>10</v>
       </c>
       <c r="K40" t="s">
-        <v>244</v>
+        <v>424</v>
       </c>
       <c r="L40" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="M40" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="N40" t="s">
-        <v>36</v>
-      </c>
-      <c r="O40">
+        <v>221</v>
+      </c>
+      <c r="O40" t="s">
+        <v>36</v>
+      </c>
+      <c r="P40">
         <v>62.6</v>
       </c>
-      <c r="P40">
+      <c r="Q40">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>79</v>
       </c>
       <c r="B41" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -4093,30 +4334,33 @@
         <v>10</v>
       </c>
       <c r="K41" t="s">
+        <v>425</v>
+      </c>
+      <c r="L41" t="s">
+        <v>244</v>
+      </c>
+      <c r="M41" t="s">
+        <v>245</v>
+      </c>
+      <c r="N41" t="s">
         <v>246</v>
       </c>
-      <c r="L41" t="s">
-        <v>247</v>
-      </c>
-      <c r="M41" t="s">
-        <v>248</v>
-      </c>
-      <c r="N41" t="s">
-        <v>36</v>
-      </c>
-      <c r="O41">
+      <c r="O41" t="s">
+        <v>36</v>
+      </c>
+      <c r="P41">
         <v>62.6</v>
       </c>
-      <c r="P41">
+      <c r="Q41">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>80</v>
       </c>
       <c r="B42" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -4143,30 +4387,33 @@
         <v>10</v>
       </c>
       <c r="K42" t="s">
-        <v>249</v>
+        <v>426</v>
       </c>
       <c r="L42" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="M42" t="s">
         <v>248</v>
       </c>
       <c r="N42" t="s">
-        <v>36</v>
-      </c>
-      <c r="O42">
+        <v>246</v>
+      </c>
+      <c r="O42" t="s">
+        <v>36</v>
+      </c>
+      <c r="P42">
         <v>62.6</v>
       </c>
-      <c r="P42">
+      <c r="Q42">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>81</v>
       </c>
       <c r="B43" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -4193,30 +4440,33 @@
         <v>10</v>
       </c>
       <c r="K43" t="s">
-        <v>251</v>
+        <v>427</v>
       </c>
       <c r="L43" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="M43" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="N43" t="s">
-        <v>36</v>
-      </c>
-      <c r="O43">
+        <v>246</v>
+      </c>
+      <c r="O43" t="s">
+        <v>36</v>
+      </c>
+      <c r="P43">
         <v>62.6</v>
       </c>
-      <c r="P43">
+      <c r="Q43">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>82</v>
       </c>
       <c r="B44" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -4243,30 +4493,33 @@
         <v>10</v>
       </c>
       <c r="K44" t="s">
-        <v>253</v>
+        <v>428</v>
       </c>
       <c r="L44" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="M44" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="N44" t="s">
-        <v>36</v>
-      </c>
-      <c r="O44">
+        <v>246</v>
+      </c>
+      <c r="O44" t="s">
+        <v>36</v>
+      </c>
+      <c r="P44">
         <v>62.6</v>
       </c>
-      <c r="P44">
+      <c r="Q44">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>83</v>
       </c>
       <c r="B45" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -4293,30 +4546,33 @@
         <v>10</v>
       </c>
       <c r="K45" t="s">
-        <v>255</v>
+        <v>429</v>
       </c>
       <c r="L45" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="M45" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="N45" t="s">
-        <v>36</v>
-      </c>
-      <c r="O45">
+        <v>246</v>
+      </c>
+      <c r="O45" t="s">
+        <v>36</v>
+      </c>
+      <c r="P45">
         <v>62.6</v>
       </c>
-      <c r="P45">
+      <c r="Q45">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>84</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="C46" s="2">
         <v>1</v>
@@ -4343,30 +4599,33 @@
         <v>10</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>257</v>
+        <v>430</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="O46" s="2">
+        <v>246</v>
+      </c>
+      <c r="O46" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P46" s="2">
         <v>62.6</v>
       </c>
-      <c r="P46" s="2">
+      <c r="Q46" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>11</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -4393,30 +4652,33 @@
         <v>9</v>
       </c>
       <c r="K47" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="L47" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="M47" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="N47" t="s">
-        <v>357</v>
-      </c>
-      <c r="O47">
-        <v>162.5</v>
+        <v>350</v>
+      </c>
+      <c r="O47" t="s">
+        <v>351</v>
       </c>
       <c r="P47">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q47">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>12</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -4443,30 +4705,33 @@
         <v>9</v>
       </c>
       <c r="K48" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="L48" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="M48" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="N48" t="s">
-        <v>357</v>
-      </c>
-      <c r="O48">
-        <v>162.5</v>
+        <v>350</v>
+      </c>
+      <c r="O48" t="s">
+        <v>351</v>
       </c>
       <c r="P48">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q48">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>13</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -4493,30 +4758,33 @@
         <v>9</v>
       </c>
       <c r="K49" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="L49" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="M49" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="N49" t="s">
-        <v>357</v>
-      </c>
-      <c r="O49">
-        <v>162.5</v>
+        <v>350</v>
+      </c>
+      <c r="O49" t="s">
+        <v>351</v>
       </c>
       <c r="P49">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q49">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>14</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -4543,30 +4811,33 @@
         <v>9</v>
       </c>
       <c r="K50" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="L50" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="M50" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="N50" t="s">
-        <v>353</v>
-      </c>
-      <c r="O50">
-        <v>162.5</v>
+        <v>346</v>
+      </c>
+      <c r="O50" t="s">
+        <v>347</v>
       </c>
       <c r="P50">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q50">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>17</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -4593,30 +4864,33 @@
         <v>9</v>
       </c>
       <c r="K51" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="L51" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="M51" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="N51" t="s">
-        <v>364</v>
-      </c>
-      <c r="O51">
-        <v>162.5</v>
+        <v>357</v>
+      </c>
+      <c r="O51" t="s">
+        <v>358</v>
       </c>
       <c r="P51">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q51">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>18</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -4643,30 +4917,33 @@
         <v>9</v>
       </c>
       <c r="K52" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="L52" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="M52" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="N52" t="s">
-        <v>364</v>
-      </c>
-      <c r="O52">
-        <v>162.5</v>
+        <v>357</v>
+      </c>
+      <c r="O52" t="s">
+        <v>358</v>
       </c>
       <c r="P52">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="53" spans="1:16" s="11" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q52">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" s="11" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="11" t="s">
         <v>19</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C53" s="11">
         <v>1</v>
@@ -4693,30 +4970,33 @@
         <v>9</v>
       </c>
       <c r="K53" s="11" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="L53" s="11" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="M53" s="11" t="s">
-        <v>381</v>
+        <v>356</v>
       </c>
       <c r="N53" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="O53" s="11">
-        <v>162.5</v>
+        <v>375</v>
+      </c>
+      <c r="O53" s="11" t="s">
+        <v>358</v>
       </c>
       <c r="P53" s="11">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="54" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Q53" s="11">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C54" s="8">
         <v>1</v>
@@ -4743,30 +5023,33 @@
         <v>9</v>
       </c>
       <c r="K54" s="8" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="L54" s="8" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="M54" s="8" t="s">
-        <v>381</v>
+        <v>356</v>
       </c>
       <c r="N54" s="8" t="s">
-        <v>364</v>
-      </c>
-      <c r="O54" s="8">
-        <v>162.5</v>
+        <v>375</v>
+      </c>
+      <c r="O54" s="8" t="s">
+        <v>358</v>
       </c>
       <c r="P54" s="8">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="55" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Q54" s="8">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="8" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C55" s="8">
         <v>1</v>
@@ -4793,30 +5076,33 @@
         <v>9</v>
       </c>
       <c r="K55" s="8" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="L55" s="8" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="M55" s="8" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="N55" s="8" t="s">
-        <v>391</v>
-      </c>
-      <c r="O55" s="8">
-        <v>162.5</v>
+        <v>384</v>
+      </c>
+      <c r="O55" s="8" t="s">
+        <v>385</v>
       </c>
       <c r="P55" s="8">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="56" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Q55" s="8">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="8" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C56" s="8">
         <v>1</v>
@@ -4843,30 +5129,33 @@
         <v>9</v>
       </c>
       <c r="K56" s="8" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="L56" s="8" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="M56" s="8" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="N56" s="8" t="s">
-        <v>386</v>
-      </c>
-      <c r="O56" s="8">
-        <v>162.5</v>
+        <v>379</v>
+      </c>
+      <c r="O56" s="8" t="s">
+        <v>380</v>
       </c>
       <c r="P56" s="8">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="8">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>21</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -4893,30 +5182,33 @@
         <v>9</v>
       </c>
       <c r="K57" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="L57" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M57" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="N57" t="s">
-        <v>371</v>
-      </c>
-      <c r="O57">
-        <v>162.5</v>
+        <v>364</v>
+      </c>
+      <c r="O57" t="s">
+        <v>365</v>
       </c>
       <c r="P57">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q57">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>22</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -4943,30 +5235,33 @@
         <v>9</v>
       </c>
       <c r="K58" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="L58" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="M58" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="N58" t="s">
-        <v>371</v>
-      </c>
-      <c r="O58">
-        <v>162.5</v>
+        <v>364</v>
+      </c>
+      <c r="O58" t="s">
+        <v>365</v>
       </c>
       <c r="P58">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q58">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>23</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -4993,30 +5288,33 @@
         <v>9</v>
       </c>
       <c r="K59" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="L59" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="M59" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="N59" t="s">
-        <v>371</v>
-      </c>
-      <c r="O59">
-        <v>162.5</v>
+        <v>364</v>
+      </c>
+      <c r="O59" t="s">
+        <v>365</v>
       </c>
       <c r="P59">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="60" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Q59">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C60" s="2">
         <v>1</v>
@@ -5043,30 +5341,33 @@
         <v>9</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="O60" s="2">
-        <v>162.5</v>
+        <v>364</v>
+      </c>
+      <c r="O60" s="2" t="s">
+        <v>365</v>
       </c>
       <c r="P60" s="2">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="2">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>15</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -5093,30 +5394,33 @@
         <v>9</v>
       </c>
       <c r="K61" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="L61" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="M61" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="N61" t="s">
-        <v>378</v>
-      </c>
-      <c r="O61">
+        <v>371</v>
+      </c>
+      <c r="O61" t="s">
+        <v>372</v>
+      </c>
+      <c r="P61">
         <v>92.6</v>
       </c>
-      <c r="P61">
+      <c r="Q61">
         <v>200</v>
       </c>
     </row>
-    <row r="62" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C62" s="2">
         <v>1</v>
@@ -5143,30 +5447,33 @@
         <v>9</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="O62" s="2">
+        <v>371</v>
+      </c>
+      <c r="O62" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="P62" s="2">
         <v>92.6</v>
       </c>
-      <c r="P62" s="2">
+      <c r="Q62" s="2">
         <v>200</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>25</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -5193,30 +5500,33 @@
         <v>9</v>
       </c>
       <c r="K63" t="s">
+        <v>117</v>
+      </c>
+      <c r="L63" t="s">
+        <v>117</v>
+      </c>
+      <c r="M63" t="s">
+        <v>118</v>
+      </c>
+      <c r="N63" t="s">
         <v>119</v>
       </c>
-      <c r="L63" t="s">
-        <v>120</v>
-      </c>
-      <c r="M63" t="s">
-        <v>121</v>
-      </c>
-      <c r="N63" t="s">
-        <v>36</v>
-      </c>
-      <c r="O63">
+      <c r="O63" t="s">
+        <v>36</v>
+      </c>
+      <c r="P63">
         <v>25</v>
       </c>
-      <c r="P63">
+      <c r="Q63">
         <v>160</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>26</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -5243,30 +5553,33 @@
         <v>9</v>
       </c>
       <c r="K64" t="s">
+        <v>120</v>
+      </c>
+      <c r="L64" t="s">
+        <v>120</v>
+      </c>
+      <c r="M64" t="s">
+        <v>121</v>
+      </c>
+      <c r="N64" t="s">
         <v>122</v>
       </c>
-      <c r="L64" t="s">
-        <v>123</v>
-      </c>
-      <c r="M64" t="s">
-        <v>124</v>
-      </c>
-      <c r="N64" t="s">
-        <v>36</v>
-      </c>
-      <c r="O64">
+      <c r="O64" t="s">
+        <v>36</v>
+      </c>
+      <c r="P64">
         <v>25</v>
       </c>
-      <c r="P64">
+      <c r="Q64">
         <v>160</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>27</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -5293,30 +5606,33 @@
         <v>9</v>
       </c>
       <c r="K65" t="s">
+        <v>123</v>
+      </c>
+      <c r="L65" t="s">
+        <v>123</v>
+      </c>
+      <c r="M65" t="s">
+        <v>124</v>
+      </c>
+      <c r="N65" t="s">
         <v>125</v>
       </c>
-      <c r="L65" t="s">
-        <v>126</v>
-      </c>
-      <c r="M65" t="s">
-        <v>127</v>
-      </c>
-      <c r="N65" t="s">
-        <v>36</v>
-      </c>
-      <c r="O65">
+      <c r="O65" t="s">
+        <v>36</v>
+      </c>
+      <c r="P65">
         <v>25</v>
       </c>
-      <c r="P65">
+      <c r="Q65">
         <v>160</v>
       </c>
     </row>
-    <row r="66" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C66" s="5">
         <v>1</v>
@@ -5343,30 +5659,33 @@
         <v>9</v>
       </c>
       <c r="K66" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="L66" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="M66" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="N66" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="L66" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="M66" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="N66" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="O66" s="5">
+      <c r="O66" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="P66" s="5">
         <v>25</v>
       </c>
-      <c r="P66" s="5">
+      <c r="Q66" s="5">
         <v>160</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>87</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -5393,30 +5712,33 @@
         <v>9</v>
       </c>
       <c r="K67" t="s">
+        <v>129</v>
+      </c>
+      <c r="L67" t="s">
+        <v>129</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N67" t="s">
+        <v>130</v>
+      </c>
+      <c r="O67" t="s">
         <v>131</v>
       </c>
-      <c r="L67" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M67" t="s">
-        <v>132</v>
-      </c>
-      <c r="N67" t="s">
-        <v>133</v>
-      </c>
-      <c r="O67">
+      <c r="P67">
         <v>92.6</v>
       </c>
-      <c r="P67">
+      <c r="Q67">
         <v>200</v>
       </c>
     </row>
-    <row r="68" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C68" s="2">
         <v>1</v>
@@ -5443,30 +5765,33 @@
         <v>9</v>
       </c>
       <c r="K68" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="M68" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="O68" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="L68" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="M68" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="N68" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="O68" s="2">
+      <c r="P68" s="2">
         <v>92.6</v>
       </c>
-      <c r="P68" s="2">
+      <c r="Q68" s="2">
         <v>200</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>89</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -5493,30 +5818,33 @@
         <v>9</v>
       </c>
       <c r="K69" t="s">
+        <v>135</v>
+      </c>
+      <c r="L69" t="s">
+        <v>135</v>
+      </c>
+      <c r="M69" t="s">
+        <v>136</v>
+      </c>
+      <c r="N69" t="s">
         <v>137</v>
       </c>
-      <c r="L69" t="s">
-        <v>138</v>
-      </c>
-      <c r="M69" t="s">
-        <v>139</v>
-      </c>
-      <c r="N69" t="s">
-        <v>36</v>
-      </c>
-      <c r="O69">
+      <c r="O69" t="s">
+        <v>36</v>
+      </c>
+      <c r="P69">
         <v>25</v>
       </c>
-      <c r="P69">
+      <c r="Q69">
         <v>160</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>99</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -5543,30 +5871,33 @@
         <v>9</v>
       </c>
       <c r="K70" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L70" t="s">
+        <v>135</v>
+      </c>
+      <c r="M70" t="s">
+        <v>136</v>
+      </c>
+      <c r="N70" t="s">
         <v>138</v>
       </c>
-      <c r="M70" t="s">
-        <v>140</v>
-      </c>
-      <c r="N70" t="s">
-        <v>36</v>
-      </c>
-      <c r="O70">
+      <c r="O70" t="s">
+        <v>36</v>
+      </c>
+      <c r="P70">
         <v>25</v>
       </c>
-      <c r="P70">
+      <c r="Q70">
         <v>160</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>90</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -5593,30 +5924,33 @@
         <v>9</v>
       </c>
       <c r="K71" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L71" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="M71" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="N71" t="s">
-        <v>36</v>
-      </c>
-      <c r="O71">
+        <v>140</v>
+      </c>
+      <c r="O71" t="s">
+        <v>36</v>
+      </c>
+      <c r="P71">
         <v>25</v>
       </c>
-      <c r="P71">
+      <c r="Q71">
         <v>160</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>91</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -5643,30 +5977,33 @@
         <v>9</v>
       </c>
       <c r="K72" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L72" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="M72" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="N72" t="s">
-        <v>36</v>
-      </c>
-      <c r="O72">
+        <v>142</v>
+      </c>
+      <c r="O72" t="s">
+        <v>36</v>
+      </c>
+      <c r="P72">
         <v>25</v>
       </c>
-      <c r="P72">
+      <c r="Q72">
         <v>160</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>92</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -5693,30 +6030,33 @@
         <v>9</v>
       </c>
       <c r="K73" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L73" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="M73" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="N73" t="s">
-        <v>36</v>
-      </c>
-      <c r="O73">
+        <v>144</v>
+      </c>
+      <c r="O73" t="s">
+        <v>36</v>
+      </c>
+      <c r="P73">
         <v>25</v>
       </c>
-      <c r="P73">
+      <c r="Q73">
         <v>160</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>93</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -5743,30 +6083,33 @@
         <v>9</v>
       </c>
       <c r="K74" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="L74" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="M74" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="N74" t="s">
-        <v>36</v>
-      </c>
-      <c r="O74">
+        <v>146</v>
+      </c>
+      <c r="O74" t="s">
+        <v>36</v>
+      </c>
+      <c r="P74">
         <v>25</v>
       </c>
-      <c r="P74">
+      <c r="Q74">
         <v>160</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>94</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -5793,30 +6136,33 @@
         <v>9</v>
       </c>
       <c r="K75" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L75" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="M75" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N75" t="s">
-        <v>36</v>
-      </c>
-      <c r="O75">
+        <v>148</v>
+      </c>
+      <c r="O75" t="s">
+        <v>36</v>
+      </c>
+      <c r="P75">
         <v>25</v>
       </c>
-      <c r="P75">
+      <c r="Q75">
         <v>160</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>95</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -5843,30 +6189,33 @@
         <v>9</v>
       </c>
       <c r="K76" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L76" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M76" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="N76" t="s">
-        <v>36</v>
-      </c>
-      <c r="O76">
+        <v>150</v>
+      </c>
+      <c r="O76" t="s">
+        <v>36</v>
+      </c>
+      <c r="P76">
         <v>25</v>
       </c>
-      <c r="P76">
+      <c r="Q76">
         <v>160</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>96</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -5893,30 +6242,33 @@
         <v>9</v>
       </c>
       <c r="K77" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L77" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="M77" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="N77" t="s">
-        <v>36</v>
-      </c>
-      <c r="O77">
+        <v>152</v>
+      </c>
+      <c r="O77" t="s">
+        <v>36</v>
+      </c>
+      <c r="P77">
         <v>25</v>
       </c>
-      <c r="P77">
+      <c r="Q77">
         <v>160</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>97</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -5943,30 +6295,33 @@
         <v>9</v>
       </c>
       <c r="K78" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="L78" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="M78" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="N78" t="s">
-        <v>36</v>
-      </c>
-      <c r="O78">
+        <v>154</v>
+      </c>
+      <c r="O78" t="s">
+        <v>36</v>
+      </c>
+      <c r="P78">
         <v>25</v>
       </c>
-      <c r="P78">
+      <c r="Q78">
         <v>160</v>
       </c>
     </row>
-    <row r="79" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>98</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C79" s="2">
         <v>1</v>
@@ -5993,30 +6348,33 @@
         <v>9</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="O79" s="2">
+        <v>156</v>
+      </c>
+      <c r="O79" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P79" s="2">
         <v>25</v>
       </c>
-      <c r="P79" s="2">
+      <c r="Q79" s="2">
         <v>160</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>101</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -6043,30 +6401,33 @@
         <v>10</v>
       </c>
       <c r="K80" t="s">
+        <v>157</v>
+      </c>
+      <c r="L80" t="s">
+        <v>157</v>
+      </c>
+      <c r="M80" t="s">
+        <v>158</v>
+      </c>
+      <c r="N80" t="s">
         <v>159</v>
       </c>
-      <c r="L80" t="s">
-        <v>160</v>
-      </c>
-      <c r="M80" t="s">
-        <v>161</v>
-      </c>
-      <c r="N80" t="s">
-        <v>36</v>
-      </c>
-      <c r="O80">
+      <c r="O80" t="s">
+        <v>36</v>
+      </c>
+      <c r="P80">
         <v>60.4</v>
       </c>
-      <c r="P80">
+      <c r="Q80">
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>102</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -6093,30 +6454,33 @@
         <v>10</v>
       </c>
       <c r="K81" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="L81" t="s">
         <v>160</v>
       </c>
       <c r="M81" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="N81" t="s">
-        <v>36</v>
-      </c>
-      <c r="O81">
+        <v>159</v>
+      </c>
+      <c r="O81" t="s">
+        <v>36</v>
+      </c>
+      <c r="P81">
         <v>60.4</v>
       </c>
-      <c r="P81">
+      <c r="Q81">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>103</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -6143,30 +6507,33 @@
         <v>10</v>
       </c>
       <c r="K82" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="L82" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M82" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="N82" t="s">
-        <v>36</v>
-      </c>
-      <c r="O82">
+        <v>159</v>
+      </c>
+      <c r="O82" t="s">
+        <v>36</v>
+      </c>
+      <c r="P82">
         <v>60.4</v>
       </c>
-      <c r="P82">
+      <c r="Q82">
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>104</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -6193,30 +6560,33 @@
         <v>10</v>
       </c>
       <c r="K83" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="L83" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="M83" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="N83" t="s">
-        <v>36</v>
-      </c>
-      <c r="O83">
+        <v>288</v>
+      </c>
+      <c r="O83" t="s">
+        <v>36</v>
+      </c>
+      <c r="P83">
         <v>60.4</v>
       </c>
-      <c r="P83">
+      <c r="Q83">
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>105</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C84">
         <v>1</v>
@@ -6243,30 +6613,33 @@
         <v>10</v>
       </c>
       <c r="K84" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="L84" t="s">
-        <v>289</v>
+        <v>266</v>
       </c>
       <c r="M84" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="N84" t="s">
-        <v>36</v>
-      </c>
-      <c r="O84">
+        <v>288</v>
+      </c>
+      <c r="O84" t="s">
+        <v>36</v>
+      </c>
+      <c r="P84">
         <v>60.4</v>
       </c>
-      <c r="P84">
+      <c r="Q84">
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>106</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -6293,30 +6666,33 @@
         <v>10</v>
       </c>
       <c r="K85" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="L85" t="s">
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="M85" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="N85" t="s">
-        <v>36</v>
-      </c>
-      <c r="O85">
+        <v>288</v>
+      </c>
+      <c r="O85" t="s">
+        <v>36</v>
+      </c>
+      <c r="P85">
         <v>60.4</v>
       </c>
-      <c r="P85">
+      <c r="Q85">
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>107</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -6343,30 +6719,33 @@
         <v>10</v>
       </c>
       <c r="K86" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="L86" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="M86" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="N86" t="s">
-        <v>36</v>
-      </c>
-      <c r="O86">
+        <v>289</v>
+      </c>
+      <c r="O86" t="s">
+        <v>36</v>
+      </c>
+      <c r="P86">
         <v>60.4</v>
       </c>
-      <c r="P86">
+      <c r="Q86">
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>108</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -6393,30 +6772,33 @@
         <v>10</v>
       </c>
       <c r="K87" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="L87" t="s">
-        <v>290</v>
+        <v>269</v>
       </c>
       <c r="M87" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="N87" t="s">
-        <v>36</v>
-      </c>
-      <c r="O87">
+        <v>289</v>
+      </c>
+      <c r="O87" t="s">
+        <v>36</v>
+      </c>
+      <c r="P87">
         <v>60.4</v>
       </c>
-      <c r="P87">
+      <c r="Q87">
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>109</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -6443,30 +6825,33 @@
         <v>10</v>
       </c>
       <c r="K88" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="L88" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="M88" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="N88" t="s">
-        <v>36</v>
-      </c>
-      <c r="O88">
+        <v>289</v>
+      </c>
+      <c r="O88" t="s">
+        <v>36</v>
+      </c>
+      <c r="P88">
         <v>60.4</v>
       </c>
-      <c r="P88">
+      <c r="Q88">
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -6493,30 +6878,33 @@
         <v>10</v>
       </c>
       <c r="K89" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="L89" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="M89" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="N89" t="s">
-        <v>36</v>
-      </c>
-      <c r="O89">
+        <v>290</v>
+      </c>
+      <c r="O89" t="s">
+        <v>36</v>
+      </c>
+      <c r="P89">
         <v>60.4</v>
       </c>
-      <c r="P89">
+      <c r="Q89">
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C90">
         <v>1</v>
@@ -6543,30 +6931,33 @@
         <v>10</v>
       </c>
       <c r="K90" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="L90" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="M90" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="N90" t="s">
-        <v>36</v>
-      </c>
-      <c r="O90">
+        <v>290</v>
+      </c>
+      <c r="O90" t="s">
+        <v>36</v>
+      </c>
+      <c r="P90">
         <v>60.4</v>
       </c>
-      <c r="P90">
+      <c r="Q90">
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C91">
         <v>1</v>
@@ -6593,30 +6984,33 @@
         <v>10</v>
       </c>
       <c r="K91" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="L91" t="s">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="M91" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="N91" t="s">
-        <v>36</v>
-      </c>
-      <c r="O91">
+        <v>290</v>
+      </c>
+      <c r="O91" t="s">
+        <v>36</v>
+      </c>
+      <c r="P91">
         <v>60.4</v>
       </c>
-      <c r="P91">
+      <c r="Q91">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>110</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C92">
         <v>1</v>
@@ -6643,30 +7037,33 @@
         <v>10</v>
       </c>
       <c r="K92" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="L92" t="s">
-        <v>292</v>
+        <v>274</v>
       </c>
       <c r="M92" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="N92" t="s">
-        <v>36</v>
-      </c>
-      <c r="O92">
+        <v>291</v>
+      </c>
+      <c r="O92" t="s">
+        <v>36</v>
+      </c>
+      <c r="P92">
         <v>60.4</v>
       </c>
-      <c r="P92">
+      <c r="Q92">
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>111</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C93">
         <v>1</v>
@@ -6693,30 +7090,33 @@
         <v>10</v>
       </c>
       <c r="K93" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="L93" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="M93" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="N93" t="s">
-        <v>36</v>
-      </c>
-      <c r="O93">
+        <v>291</v>
+      </c>
+      <c r="O93" t="s">
+        <v>36</v>
+      </c>
+      <c r="P93">
         <v>60.4</v>
       </c>
-      <c r="P93">
+      <c r="Q93">
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>112</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -6743,30 +7143,33 @@
         <v>10</v>
       </c>
       <c r="K94" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="L94" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="M94" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="N94" t="s">
-        <v>36</v>
-      </c>
-      <c r="O94">
+        <v>291</v>
+      </c>
+      <c r="O94" t="s">
+        <v>36</v>
+      </c>
+      <c r="P94">
         <v>60.4</v>
       </c>
-      <c r="P94">
+      <c r="Q94">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>113</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -6793,30 +7196,33 @@
         <v>10</v>
       </c>
       <c r="K95" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="L95" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="M95" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="N95" t="s">
-        <v>36</v>
-      </c>
-      <c r="O95">
+        <v>292</v>
+      </c>
+      <c r="O95" t="s">
+        <v>36</v>
+      </c>
+      <c r="P95">
         <v>60.4</v>
       </c>
-      <c r="P95">
+      <c r="Q95">
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>114</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -6843,30 +7249,33 @@
         <v>10</v>
       </c>
       <c r="K96" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="L96" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="M96" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="N96" t="s">
-        <v>36</v>
-      </c>
-      <c r="O96">
+        <v>292</v>
+      </c>
+      <c r="O96" t="s">
+        <v>36</v>
+      </c>
+      <c r="P96">
         <v>60.4</v>
       </c>
-      <c r="P96">
+      <c r="Q96">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>115</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C97" s="2">
         <v>1</v>
@@ -6893,30 +7302,33 @@
         <v>10</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="O97" s="2">
+        <v>292</v>
+      </c>
+      <c r="O97" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P97" s="2">
         <v>60.4</v>
       </c>
-      <c r="P97" s="2">
+      <c r="Q97" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>117</v>
+        <v>259</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -6943,180 +7355,192 @@
         <v>10</v>
       </c>
       <c r="K98" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="L98" t="s">
+        <v>261</v>
+      </c>
+      <c r="M98" t="s">
+        <v>262</v>
+      </c>
+      <c r="N98" t="s">
+        <v>257</v>
+      </c>
+      <c r="O98" t="s">
+        <v>36</v>
+      </c>
+      <c r="P98">
+        <v>80</v>
+      </c>
+      <c r="Q98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="M98" t="s">
-        <v>261</v>
-      </c>
-      <c r="N98" t="s">
-        <v>36</v>
-      </c>
-      <c r="O98">
+      <c r="B99" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="C99" s="2">
+        <v>1</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E99" s="2">
+        <v>2</v>
+      </c>
+      <c r="F99" s="2">
+        <v>1</v>
+      </c>
+      <c r="G99" s="2">
+        <v>1</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="J99" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K99" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="L99" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="M99" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="N99" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="O99" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P99" s="2">
         <v>80</v>
       </c>
-      <c r="P98">
+      <c r="Q99" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A99" t="s">
-        <v>265</v>
-      </c>
-      <c r="B99" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="C99">
-        <v>1</v>
-      </c>
-      <c r="D99" t="s">
-        <v>100</v>
-      </c>
-      <c r="E99">
-        <v>2</v>
-      </c>
-      <c r="F99">
-        <v>1</v>
-      </c>
-      <c r="G99">
-        <v>1</v>
-      </c>
-      <c r="H99" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I99" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="J99" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K99" t="s">
-        <v>267</v>
-      </c>
-      <c r="L99" t="s">
-        <v>268</v>
-      </c>
-      <c r="M99" t="s">
-        <v>261</v>
-      </c>
-      <c r="N99" t="s">
-        <v>36</v>
-      </c>
-      <c r="O99">
-        <v>80</v>
-      </c>
-      <c r="P99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>118</v>
-      </c>
-      <c r="B100" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="C100">
+        <v>293</v>
+      </c>
+      <c r="B100" t="s">
+        <v>310</v>
+      </c>
+      <c r="C100" s="4">
         <v>1</v>
       </c>
       <c r="D100" t="s">
         <v>100</v>
       </c>
-      <c r="E100">
-        <v>2</v>
-      </c>
-      <c r="F100">
-        <v>1</v>
-      </c>
-      <c r="G100">
+      <c r="E100" s="4">
+        <v>2</v>
+      </c>
+      <c r="F100" s="4">
+        <v>1</v>
+      </c>
+      <c r="G100" s="4">
         <v>1</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>116</v>
+        <v>7</v>
       </c>
       <c r="J100" s="1" t="s">
         <v>10</v>
       </c>
       <c r="K100" t="s">
-        <v>262</v>
+        <v>299</v>
       </c>
       <c r="L100" t="s">
-        <v>263</v>
+        <v>299</v>
       </c>
       <c r="M100" t="s">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="N100" t="s">
-        <v>36</v>
-      </c>
-      <c r="O100">
-        <v>80</v>
-      </c>
-      <c r="P100">
+        <v>308</v>
+      </c>
+      <c r="O100" t="s">
+        <v>36</v>
+      </c>
+      <c r="P100" s="4">
+        <v>100</v>
+      </c>
+      <c r="Q100" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="B101" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="C101" s="2">
-        <v>1</v>
-      </c>
-      <c r="D101" s="2" t="s">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>294</v>
+      </c>
+      <c r="B101" t="s">
+        <v>310</v>
+      </c>
+      <c r="C101" s="4">
+        <v>1</v>
+      </c>
+      <c r="D101" t="s">
         <v>100</v>
       </c>
-      <c r="E101" s="2">
-        <v>2</v>
-      </c>
-      <c r="F101" s="2">
-        <v>1</v>
-      </c>
-      <c r="G101" s="2">
-        <v>1</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="J101" s="3" t="s">
+      <c r="E101" s="4">
+        <v>2</v>
+      </c>
+      <c r="F101" s="4">
+        <v>1</v>
+      </c>
+      <c r="G101" s="4">
+        <v>1</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J101" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K101" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="L101" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="M101" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="N101" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="O101" s="2">
-        <v>80</v>
-      </c>
-      <c r="P101" s="2">
+      <c r="K101" t="s">
+        <v>301</v>
+      </c>
+      <c r="L101" t="s">
+        <v>301</v>
+      </c>
+      <c r="M101" t="s">
+        <v>300</v>
+      </c>
+      <c r="N101" t="s">
+        <v>308</v>
+      </c>
+      <c r="O101" t="s">
+        <v>36</v>
+      </c>
+      <c r="P101" s="4">
+        <v>100</v>
+      </c>
+      <c r="Q101" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B102" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C102" s="4">
         <v>1</v>
@@ -7143,30 +7567,33 @@
         <v>10</v>
       </c>
       <c r="K102" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="L102" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="M102" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="N102" t="s">
-        <v>36</v>
-      </c>
-      <c r="O102" s="4">
+        <v>308</v>
+      </c>
+      <c r="O102" t="s">
+        <v>36</v>
+      </c>
+      <c r="P102" s="4">
         <v>100</v>
       </c>
-      <c r="P102" s="4">
+      <c r="Q102" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B103" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C103" s="4">
         <v>1</v>
@@ -7193,30 +7620,33 @@
         <v>10</v>
       </c>
       <c r="K103" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="L103" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="M103" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="N103" t="s">
-        <v>36</v>
-      </c>
-      <c r="O103" s="4">
+        <v>308</v>
+      </c>
+      <c r="O103" t="s">
+        <v>36</v>
+      </c>
+      <c r="P103" s="4">
         <v>100</v>
       </c>
-      <c r="P103" s="4">
+      <c r="Q103" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B104" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="C104" s="4">
         <v>1</v>
@@ -7243,89 +7673,95 @@
         <v>10</v>
       </c>
       <c r="K104" t="s">
+        <v>305</v>
+      </c>
+      <c r="L104" t="s">
+        <v>305</v>
+      </c>
+      <c r="M104" t="s">
+        <v>306</v>
+      </c>
+      <c r="N104" t="s">
         <v>308</v>
       </c>
-      <c r="L104" t="s">
-        <v>309</v>
-      </c>
-      <c r="M104" t="s">
-        <v>314</v>
-      </c>
-      <c r="N104" t="s">
-        <v>36</v>
-      </c>
-      <c r="O104" s="4">
+      <c r="O104" t="s">
+        <v>36</v>
+      </c>
+      <c r="P104" s="4">
         <v>100</v>
       </c>
-      <c r="P104" s="4">
+      <c r="Q104" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A105" t="s">
-        <v>302</v>
-      </c>
-      <c r="B105" t="s">
-        <v>325</v>
-      </c>
-      <c r="C105" s="4">
-        <v>1</v>
-      </c>
-      <c r="D105" t="s">
+    <row r="105" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C105" s="7">
+        <v>1</v>
+      </c>
+      <c r="D105" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E105" s="4">
-        <v>2</v>
-      </c>
-      <c r="F105" s="4">
-        <v>1</v>
-      </c>
-      <c r="G105" s="4">
-        <v>1</v>
-      </c>
-      <c r="H105" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I105" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J105" s="1" t="s">
+      <c r="E105" s="7">
+        <v>2</v>
+      </c>
+      <c r="F105" s="7">
+        <v>1</v>
+      </c>
+      <c r="G105" s="7">
+        <v>1</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J105" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K105" t="s">
-        <v>310</v>
-      </c>
-      <c r="L105" t="s">
-        <v>309</v>
-      </c>
-      <c r="M105" t="s">
-        <v>314</v>
-      </c>
-      <c r="N105" t="s">
-        <v>36</v>
-      </c>
-      <c r="O105" s="4">
+      <c r="K105" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="L105" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="M105" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="N105" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="O105" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P105" s="7">
         <v>100</v>
       </c>
-      <c r="P105" s="4">
+      <c r="Q105" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A106" t="s">
-        <v>303</v>
-      </c>
-      <c r="B106" t="s">
-        <v>317</v>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A106" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>311</v>
       </c>
       <c r="C106" s="4">
         <v>1</v>
       </c>
-      <c r="D106" t="s">
+      <c r="D106" s="2" t="s">
         <v>100</v>
       </c>
       <c r="E106" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F106" s="4">
         <v>1</v>
@@ -7334,89 +7770,95 @@
         <v>1</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K106" t="s">
+        <v>330</v>
+      </c>
+      <c r="L106" t="s">
+        <v>330</v>
+      </c>
+      <c r="M106" t="s">
+        <v>331</v>
+      </c>
+      <c r="N106" t="s">
+        <v>338</v>
+      </c>
+      <c r="O106" t="s">
+        <v>36</v>
+      </c>
+      <c r="P106" s="4">
+        <v>61.18</v>
+      </c>
+      <c r="Q106" s="4">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A107" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="B107" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="L106" t="s">
-        <v>312</v>
-      </c>
-      <c r="M106" t="s">
-        <v>314</v>
-      </c>
-      <c r="N106" t="s">
-        <v>36</v>
-      </c>
-      <c r="O106" s="4">
-        <v>100</v>
-      </c>
-      <c r="P106" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="C107" s="7">
+      <c r="C107" s="4">
         <v>1</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E107" s="7">
-        <v>2</v>
-      </c>
-      <c r="F107" s="7">
-        <v>1</v>
-      </c>
-      <c r="G107" s="7">
-        <v>1</v>
-      </c>
-      <c r="H107" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I107" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J107" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K107" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="L107" s="2" t="s">
+      <c r="E107" s="4">
+        <v>3</v>
+      </c>
+      <c r="F107" s="4">
+        <v>1</v>
+      </c>
+      <c r="G107" s="4">
+        <v>1</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K107" t="s">
+        <v>332</v>
+      </c>
+      <c r="L107" t="s">
+        <v>332</v>
+      </c>
+      <c r="M107" t="s">
+        <v>331</v>
+      </c>
+      <c r="N107" t="s">
+        <v>338</v>
+      </c>
+      <c r="O107" t="s">
+        <v>36</v>
+      </c>
+      <c r="P107" s="4">
+        <v>61.18</v>
+      </c>
+      <c r="Q107" s="4">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A108" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B108" s="4" t="s">
         <v>312</v>
-      </c>
-      <c r="M107" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="N107" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="O107" s="7">
-        <v>100</v>
-      </c>
-      <c r="P107" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A108" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="B108" s="4" t="s">
-        <v>317</v>
       </c>
       <c r="C108" s="4">
         <v>1</v>
@@ -7434,39 +7876,42 @@
         <v>1</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>6</v>
+        <v>328</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>6</v>
+        <v>328</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>9</v>
+        <v>329</v>
       </c>
       <c r="K108" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="L108" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="M108" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="N108" t="s">
-        <v>36</v>
-      </c>
-      <c r="O108" s="4">
+        <v>339</v>
+      </c>
+      <c r="O108" t="s">
+        <v>36</v>
+      </c>
+      <c r="P108" s="4">
         <v>61.18</v>
       </c>
-      <c r="P108" s="4">
+      <c r="Q108" s="4">
         <v>135</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A109" s="4" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C109" s="4">
         <v>1</v>
@@ -7484,39 +7929,42 @@
         <v>1</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>6</v>
+        <v>328</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>6</v>
+        <v>328</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>9</v>
+        <v>329</v>
       </c>
       <c r="K109" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="L109" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="M109" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="N109" t="s">
-        <v>36</v>
-      </c>
-      <c r="O109" s="4">
+        <v>339</v>
+      </c>
+      <c r="O109" t="s">
+        <v>36</v>
+      </c>
+      <c r="P109" s="4">
         <v>61.18</v>
       </c>
-      <c r="P109" s="4">
+      <c r="Q109" s="4">
         <v>135</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A110" s="4" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C110" s="4">
         <v>1</v>
@@ -7534,39 +7982,42 @@
         <v>1</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="K110" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="L110" t="s">
+        <v>336</v>
+      </c>
+      <c r="M110" t="s">
+        <v>337</v>
+      </c>
+      <c r="N110" t="s">
         <v>340</v>
       </c>
-      <c r="M110" t="s">
-        <v>345</v>
-      </c>
-      <c r="N110" t="s">
-        <v>36</v>
-      </c>
-      <c r="O110" s="4">
+      <c r="O110" t="s">
+        <v>36</v>
+      </c>
+      <c r="P110" s="4">
         <v>61.18</v>
       </c>
-      <c r="P110" s="4">
+      <c r="Q110" s="4">
         <v>135</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C111" s="4">
         <v>1</v>
@@ -7584,39 +8035,42 @@
         <v>1</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="K111" t="s">
         <v>341</v>
       </c>
       <c r="L111" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M111" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="N111" t="s">
-        <v>36</v>
-      </c>
-      <c r="O111" s="4">
+        <v>342</v>
+      </c>
+      <c r="O111" t="s">
+        <v>36</v>
+      </c>
+      <c r="P111" s="4">
         <v>61.18</v>
       </c>
-      <c r="P111" s="4">
+      <c r="Q111" s="4">
         <v>135</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A112" s="4" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C112" s="4">
         <v>1</v>
@@ -7634,136 +8088,39 @@
         <v>1</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="K112" t="s">
+        <v>341</v>
+      </c>
+      <c r="L112" t="s">
+        <v>341</v>
+      </c>
+      <c r="M112" t="s">
+        <v>337</v>
+      </c>
+      <c r="N112" t="s">
         <v>342</v>
       </c>
-      <c r="L112" t="s">
-        <v>343</v>
-      </c>
-      <c r="M112" t="s">
-        <v>346</v>
-      </c>
-      <c r="N112" t="s">
-        <v>36</v>
-      </c>
-      <c r="O112" s="4">
+      <c r="O112" t="s">
+        <v>36</v>
+      </c>
+      <c r="P112" s="4">
         <v>61.18</v>
       </c>
-      <c r="P112" s="4">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A113" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="B113" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="C113" s="4">
-        <v>1</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E113" s="4">
-        <v>3</v>
-      </c>
-      <c r="F113" s="4">
-        <v>1</v>
-      </c>
-      <c r="G113" s="4">
-        <v>1</v>
-      </c>
-      <c r="H113" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="I113" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="J113" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="K113" t="s">
-        <v>347</v>
-      </c>
-      <c r="L113" t="s">
-        <v>343</v>
-      </c>
-      <c r="M113" t="s">
-        <v>348</v>
-      </c>
-      <c r="N113" t="s">
-        <v>36</v>
-      </c>
-      <c r="O113" s="4">
-        <v>61.18</v>
-      </c>
-      <c r="P113" s="4">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A114" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="B114" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="C114" s="4">
-        <v>1</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E114" s="4">
-        <v>3</v>
-      </c>
-      <c r="F114" s="4">
-        <v>1</v>
-      </c>
-      <c r="G114" s="4">
-        <v>1</v>
-      </c>
-      <c r="H114" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="I114" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="J114" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="K114" t="s">
-        <v>347</v>
-      </c>
-      <c r="L114" t="s">
-        <v>343</v>
-      </c>
-      <c r="M114" t="s">
-        <v>348</v>
-      </c>
-      <c r="N114" t="s">
-        <v>36</v>
-      </c>
-      <c r="O114" s="4">
-        <v>61.18</v>
-      </c>
-      <c r="P114" s="4">
+      <c r="Q112" s="4">
         <v>135</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C1 C11 C47:C54 C80:C88 C100 C92:C98 C102:C113 C115:C1048576 C57:C69">
+  <conditionalFormatting sqref="C1 C11 C47:C54 C80:C88 C92:C97 C100:C111 C113:C1048576 C57:C69">
     <cfRule type="cellIs" dxfId="34" priority="37" operator="equal">
       <formula>1</formula>
     </cfRule>
@@ -7908,12 +8265,12 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C99">
+  <conditionalFormatting sqref="C98">
     <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C101">
+  <conditionalFormatting sqref="C99">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>1</formula>
     </cfRule>
@@ -7923,7 +8280,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C114">
+  <conditionalFormatting sqref="C112">
     <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>1</formula>
     </cfRule>

--- a/datasets_test.xlsx
+++ b/datasets_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2023 cytoSR\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D162ED0-E3A1-4B44-AEE4-1CDE7E1309A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F8A93D6-EDE9-442C-BF30-2CCB6EB618ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3705" yWindow="2385" windowWidth="21570" windowHeight="16170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2760" yWindow="4215" windowWidth="21570" windowHeight="16170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="426">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1415,6 +1415,10 @@
   </si>
   <si>
     <t>(9,31,31)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dark</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2128,7 +2132,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R109"/>
+  <dimension ref="A1:S109"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.75" customWidth="1"/>
@@ -2137,16 +2141,16 @@
     <col min="4" max="4" width="3.375" customWidth="1"/>
     <col min="5" max="5" width="2.25" customWidth="1"/>
     <col min="6" max="6" width="2.375" customWidth="1"/>
-    <col min="7" max="8" width="4.25" customWidth="1"/>
-    <col min="9" max="10" width="9.5" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="113.75" customWidth="1"/>
-    <col min="13" max="13" width="94.5" customWidth="1"/>
-    <col min="14" max="14" width="9.375" customWidth="1"/>
-    <col min="16" max="16" width="8" customWidth="1"/>
+    <col min="7" max="9" width="4.25" customWidth="1"/>
+    <col min="10" max="11" width="9.5" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="113.75" customWidth="1"/>
+    <col min="14" max="14" width="94.5" customWidth="1"/>
+    <col min="15" max="15" width="9.375" customWidth="1"/>
+    <col min="17" max="17" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2171,38 +2175,41 @@
       <c r="H1" t="s">
         <v>422</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>1</v>
+      <c r="I1" t="s">
+        <v>425</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -2227,38 +2234,41 @@
       <c r="H2">
         <v>0</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>7</v>
+      <c r="I2">
+        <v>0</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>376</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>154</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>155</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>156</v>
       </c>
-      <c r="P2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q2">
+      <c r="Q2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R2">
         <v>62.6</v>
       </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -2283,38 +2293,41 @@
       <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>7</v>
+      <c r="I3">
+        <v>0</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>377</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>157</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>158</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>156</v>
       </c>
-      <c r="P3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q3">
+      <c r="Q3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R3">
         <v>62.6</v>
       </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>41</v>
       </c>
@@ -2339,38 +2352,41 @@
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>7</v>
+      <c r="I4">
+        <v>0</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>378</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>159</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>160</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>156</v>
       </c>
-      <c r="P4" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q4">
+      <c r="Q4" t="s">
+        <v>34</v>
+      </c>
+      <c r="R4">
         <v>62.6</v>
       </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>42</v>
       </c>
@@ -2395,38 +2411,41 @@
       <c r="H5">
         <v>0</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>7</v>
+      <c r="I5">
+        <v>0</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>379</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>161</v>
       </c>
-      <c r="N5" t="s">
+      <c r="O5" t="s">
         <v>162</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>156</v>
       </c>
-      <c r="P5" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q5">
+      <c r="Q5" t="s">
+        <v>34</v>
+      </c>
+      <c r="R5">
         <v>62.6</v>
       </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -2451,38 +2470,41 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>7</v>
+      <c r="I6">
+        <v>0</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>380</v>
       </c>
-      <c r="M6" t="s">
+      <c r="N6" t="s">
         <v>163</v>
       </c>
-      <c r="N6" t="s">
+      <c r="O6" t="s">
         <v>164</v>
       </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
         <v>156</v>
       </c>
-      <c r="P6" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q6">
+      <c r="Q6" t="s">
+        <v>34</v>
+      </c>
+      <c r="R6">
         <v>62.6</v>
       </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>44</v>
       </c>
@@ -2507,38 +2529,41 @@
       <c r="H7">
         <v>0</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>7</v>
+      <c r="I7">
+        <v>0</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
         <v>381</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>165</v>
       </c>
-      <c r="N7" t="s">
+      <c r="O7" t="s">
         <v>166</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>156</v>
       </c>
-      <c r="P7" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q7">
+      <c r="Q7" t="s">
+        <v>34</v>
+      </c>
+      <c r="R7">
         <v>62.6</v>
       </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>45</v>
       </c>
@@ -2563,38 +2588,41 @@
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>7</v>
+      <c r="I8">
+        <v>0</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>382</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N8" t="s">
         <v>167</v>
       </c>
-      <c r="N8" t="s">
+      <c r="O8" t="s">
         <v>168</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>156</v>
       </c>
-      <c r="P8" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q8">
+      <c r="Q8" t="s">
+        <v>34</v>
+      </c>
+      <c r="R8">
         <v>62.6</v>
       </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>46</v>
       </c>
@@ -2619,38 +2647,41 @@
       <c r="H9">
         <v>0</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>7</v>
+      <c r="I9">
+        <v>0</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>383</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>169</v>
       </c>
-      <c r="N9" t="s">
+      <c r="O9" t="s">
         <v>170</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>156</v>
       </c>
-      <c r="P9" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q9">
+      <c r="Q9" t="s">
+        <v>34</v>
+      </c>
+      <c r="R9">
         <v>62.6</v>
       </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -2675,38 +2706,41 @@
       <c r="H10">
         <v>0</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>7</v>
+      <c r="I10">
+        <v>0</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L10" t="s">
+      <c r="M10" t="s">
         <v>384</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" t="s">
         <v>171</v>
       </c>
-      <c r="N10" t="s">
+      <c r="O10" t="s">
         <v>172</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>156</v>
       </c>
-      <c r="P10" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q10">
+      <c r="Q10" t="s">
+        <v>34</v>
+      </c>
+      <c r="R10">
         <v>62.6</v>
       </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -2731,38 +2765,41 @@
       <c r="H11">
         <v>0</v>
       </c>
-      <c r="I11" s="1" t="s">
-        <v>7</v>
+      <c r="I11">
+        <v>0</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L11" t="s">
+      <c r="M11" t="s">
         <v>385</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N11" t="s">
         <v>173</v>
       </c>
-      <c r="N11" t="s">
+      <c r="O11" t="s">
         <v>174</v>
       </c>
-      <c r="O11" t="s">
+      <c r="P11" t="s">
         <v>175</v>
       </c>
-      <c r="P11" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q11">
+      <c r="Q11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R11">
         <v>62.6</v>
       </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>48</v>
       </c>
@@ -2787,38 +2824,41 @@
       <c r="H12">
         <v>0</v>
       </c>
-      <c r="I12" s="1" t="s">
-        <v>7</v>
+      <c r="I12">
+        <v>0</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L12" t="s">
+      <c r="M12" t="s">
         <v>386</v>
       </c>
-      <c r="M12" t="s">
+      <c r="N12" t="s">
         <v>176</v>
       </c>
-      <c r="N12" t="s">
+      <c r="O12" t="s">
         <v>177</v>
       </c>
-      <c r="O12" t="s">
+      <c r="P12" t="s">
         <v>175</v>
       </c>
-      <c r="P12" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q12">
+      <c r="Q12" t="s">
+        <v>34</v>
+      </c>
+      <c r="R12">
         <v>62.6</v>
       </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -2843,38 +2883,41 @@
       <c r="H13">
         <v>0</v>
       </c>
-      <c r="I13" s="1" t="s">
-        <v>7</v>
+      <c r="I13">
+        <v>0</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L13" t="s">
+      <c r="M13" t="s">
         <v>387</v>
       </c>
-      <c r="M13" t="s">
+      <c r="N13" t="s">
         <v>178</v>
       </c>
-      <c r="N13" t="s">
+      <c r="O13" t="s">
         <v>179</v>
       </c>
-      <c r="O13" t="s">
+      <c r="P13" t="s">
         <v>175</v>
       </c>
-      <c r="P13" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q13">
+      <c r="Q13" t="s">
+        <v>34</v>
+      </c>
+      <c r="R13">
         <v>62.6</v>
       </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>50</v>
       </c>
@@ -2899,38 +2942,41 @@
       <c r="H14">
         <v>0</v>
       </c>
-      <c r="I14" s="1" t="s">
-        <v>7</v>
+      <c r="I14">
+        <v>0</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L14" t="s">
+      <c r="M14" t="s">
         <v>388</v>
       </c>
-      <c r="M14" t="s">
+      <c r="N14" t="s">
         <v>180</v>
       </c>
-      <c r="N14" t="s">
+      <c r="O14" t="s">
         <v>181</v>
       </c>
-      <c r="O14" t="s">
+      <c r="P14" t="s">
         <v>175</v>
       </c>
-      <c r="P14" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q14">
+      <c r="Q14" t="s">
+        <v>34</v>
+      </c>
+      <c r="R14">
         <v>62.6</v>
       </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>51</v>
       </c>
@@ -2955,38 +3001,41 @@
       <c r="H15">
         <v>0</v>
       </c>
-      <c r="I15" s="1" t="s">
-        <v>7</v>
+      <c r="I15">
+        <v>0</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L15" t="s">
+      <c r="M15" t="s">
         <v>389</v>
       </c>
-      <c r="M15" t="s">
+      <c r="N15" t="s">
         <v>182</v>
       </c>
-      <c r="N15" t="s">
+      <c r="O15" t="s">
         <v>183</v>
       </c>
-      <c r="O15" t="s">
+      <c r="P15" t="s">
         <v>175</v>
       </c>
-      <c r="P15" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q15">
+      <c r="Q15" t="s">
+        <v>34</v>
+      </c>
+      <c r="R15">
         <v>62.6</v>
       </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>52</v>
       </c>
@@ -3011,38 +3060,41 @@
       <c r="H16">
         <v>0</v>
       </c>
-      <c r="I16" s="1" t="s">
-        <v>7</v>
+      <c r="I16">
+        <v>0</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L16" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L16" t="s">
+      <c r="M16" t="s">
         <v>390</v>
       </c>
-      <c r="M16" t="s">
+      <c r="N16" t="s">
         <v>184</v>
       </c>
-      <c r="N16" t="s">
+      <c r="O16" t="s">
         <v>185</v>
       </c>
-      <c r="O16" t="s">
+      <c r="P16" t="s">
         <v>175</v>
       </c>
-      <c r="P16" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q16">
+      <c r="Q16" t="s">
+        <v>34</v>
+      </c>
+      <c r="R16">
         <v>62.6</v>
       </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>53</v>
       </c>
@@ -3067,38 +3119,41 @@
       <c r="H17">
         <v>0</v>
       </c>
-      <c r="I17" s="1" t="s">
-        <v>7</v>
+      <c r="I17">
+        <v>0</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L17" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L17" t="s">
+      <c r="M17" t="s">
         <v>391</v>
       </c>
-      <c r="M17" t="s">
+      <c r="N17" t="s">
         <v>186</v>
       </c>
-      <c r="N17" t="s">
+      <c r="O17" t="s">
         <v>187</v>
       </c>
-      <c r="O17" t="s">
+      <c r="P17" t="s">
         <v>175</v>
       </c>
-      <c r="P17" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q17">
+      <c r="Q17" t="s">
+        <v>34</v>
+      </c>
+      <c r="R17">
         <v>62.6</v>
       </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>54</v>
       </c>
@@ -3123,38 +3178,41 @@
       <c r="H18">
         <v>0</v>
       </c>
-      <c r="I18" s="1" t="s">
-        <v>7</v>
+      <c r="I18">
+        <v>0</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L18" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L18" t="s">
+      <c r="M18" t="s">
         <v>392</v>
       </c>
-      <c r="M18" t="s">
+      <c r="N18" t="s">
         <v>188</v>
       </c>
-      <c r="N18" t="s">
+      <c r="O18" t="s">
         <v>189</v>
       </c>
-      <c r="O18" t="s">
+      <c r="P18" t="s">
         <v>175</v>
       </c>
-      <c r="P18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q18">
+      <c r="Q18" t="s">
+        <v>34</v>
+      </c>
+      <c r="R18">
         <v>62.6</v>
       </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>55</v>
       </c>
@@ -3179,38 +3237,41 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19" s="1" t="s">
-        <v>7</v>
+      <c r="I19">
+        <v>0</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L19" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L19" t="s">
+      <c r="M19" t="s">
         <v>393</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" t="s">
         <v>190</v>
       </c>
-      <c r="N19" t="s">
+      <c r="O19" t="s">
         <v>191</v>
       </c>
-      <c r="O19" t="s">
+      <c r="P19" t="s">
         <v>175</v>
       </c>
-      <c r="P19" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q19">
+      <c r="Q19" t="s">
+        <v>34</v>
+      </c>
+      <c r="R19">
         <v>62.6</v>
       </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>56</v>
       </c>
@@ -3235,38 +3296,41 @@
       <c r="H20">
         <v>0</v>
       </c>
-      <c r="I20" s="1" t="s">
-        <v>7</v>
+      <c r="I20">
+        <v>0</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L20" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L20" t="s">
+      <c r="M20" t="s">
         <v>394</v>
       </c>
-      <c r="M20" t="s">
+      <c r="N20" t="s">
         <v>192</v>
       </c>
-      <c r="N20" t="s">
+      <c r="O20" t="s">
         <v>193</v>
       </c>
-      <c r="O20" t="s">
+      <c r="P20" t="s">
         <v>194</v>
       </c>
-      <c r="P20" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q20">
+      <c r="Q20" t="s">
+        <v>34</v>
+      </c>
+      <c r="R20">
         <v>62.6</v>
       </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>57</v>
       </c>
@@ -3291,38 +3355,41 @@
       <c r="H21">
         <v>0</v>
       </c>
-      <c r="I21" s="1" t="s">
-        <v>7</v>
+      <c r="I21">
+        <v>0</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L21" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L21" t="s">
+      <c r="M21" t="s">
         <v>395</v>
       </c>
-      <c r="M21" t="s">
+      <c r="N21" t="s">
         <v>195</v>
       </c>
-      <c r="N21" t="s">
+      <c r="O21" t="s">
         <v>196</v>
       </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
         <v>194</v>
       </c>
-      <c r="P21" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q21">
+      <c r="Q21" t="s">
+        <v>34</v>
+      </c>
+      <c r="R21">
         <v>62.6</v>
       </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>58</v>
       </c>
@@ -3347,38 +3414,41 @@
       <c r="H22">
         <v>0</v>
       </c>
-      <c r="I22" s="1" t="s">
-        <v>7</v>
+      <c r="I22">
+        <v>0</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L22" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L22" t="s">
+      <c r="M22" t="s">
         <v>396</v>
       </c>
-      <c r="M22" t="s">
+      <c r="N22" t="s">
         <v>197</v>
       </c>
-      <c r="N22" t="s">
+      <c r="O22" t="s">
         <v>198</v>
       </c>
-      <c r="O22" t="s">
+      <c r="P22" t="s">
         <v>194</v>
       </c>
-      <c r="P22" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q22">
+      <c r="Q22" t="s">
+        <v>34</v>
+      </c>
+      <c r="R22">
         <v>62.6</v>
       </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>59</v>
       </c>
@@ -3403,38 +3473,41 @@
       <c r="H23">
         <v>0</v>
       </c>
-      <c r="I23" s="1" t="s">
-        <v>7</v>
+      <c r="I23">
+        <v>0</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L23" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L23" t="s">
+      <c r="M23" t="s">
         <v>397</v>
       </c>
-      <c r="M23" t="s">
+      <c r="N23" t="s">
         <v>199</v>
       </c>
-      <c r="N23" t="s">
+      <c r="O23" t="s">
         <v>200</v>
       </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
         <v>194</v>
       </c>
-      <c r="P23" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q23">
+      <c r="Q23" t="s">
+        <v>34</v>
+      </c>
+      <c r="R23">
         <v>62.6</v>
       </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -3459,38 +3532,41 @@
       <c r="H24">
         <v>0</v>
       </c>
-      <c r="I24" s="1" t="s">
-        <v>7</v>
+      <c r="I24">
+        <v>0</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L24" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L24" t="s">
+      <c r="M24" t="s">
         <v>398</v>
       </c>
-      <c r="M24" t="s">
+      <c r="N24" t="s">
         <v>201</v>
       </c>
-      <c r="N24" t="s">
+      <c r="O24" t="s">
         <v>202</v>
       </c>
-      <c r="O24" t="s">
+      <c r="P24" t="s">
         <v>194</v>
       </c>
-      <c r="P24" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q24">
+      <c r="Q24" t="s">
+        <v>34</v>
+      </c>
+      <c r="R24">
         <v>62.6</v>
       </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -3515,38 +3591,41 @@
       <c r="H25">
         <v>0</v>
       </c>
-      <c r="I25" s="1" t="s">
-        <v>7</v>
+      <c r="I25">
+        <v>0</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L25" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L25" t="s">
+      <c r="M25" t="s">
         <v>399</v>
       </c>
-      <c r="M25" t="s">
+      <c r="N25" t="s">
         <v>203</v>
       </c>
-      <c r="N25" t="s">
+      <c r="O25" t="s">
         <v>204</v>
       </c>
-      <c r="O25" t="s">
+      <c r="P25" t="s">
         <v>194</v>
       </c>
-      <c r="P25" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q25">
+      <c r="Q25" t="s">
+        <v>34</v>
+      </c>
+      <c r="R25">
         <v>62.6</v>
       </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -3571,38 +3650,41 @@
       <c r="H26">
         <v>0</v>
       </c>
-      <c r="I26" s="1" t="s">
-        <v>7</v>
+      <c r="I26">
+        <v>0</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L26" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L26" t="s">
+      <c r="M26" t="s">
         <v>400</v>
       </c>
-      <c r="M26" t="s">
+      <c r="N26" t="s">
         <v>205</v>
       </c>
-      <c r="N26" t="s">
+      <c r="O26" t="s">
         <v>206</v>
       </c>
-      <c r="O26" t="s">
+      <c r="P26" t="s">
         <v>194</v>
       </c>
-      <c r="P26" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q26">
+      <c r="Q26" t="s">
+        <v>34</v>
+      </c>
+      <c r="R26">
         <v>62.6</v>
       </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -3627,38 +3709,41 @@
       <c r="H27">
         <v>0</v>
       </c>
-      <c r="I27" s="1" t="s">
-        <v>7</v>
+      <c r="I27">
+        <v>0</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L27" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L27" t="s">
+      <c r="M27" t="s">
         <v>401</v>
       </c>
-      <c r="M27" t="s">
+      <c r="N27" t="s">
         <v>207</v>
       </c>
-      <c r="N27" t="s">
+      <c r="O27" t="s">
         <v>208</v>
       </c>
-      <c r="O27" t="s">
+      <c r="P27" t="s">
         <v>194</v>
       </c>
-      <c r="P27" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q27">
+      <c r="Q27" t="s">
+        <v>34</v>
+      </c>
+      <c r="R27">
         <v>62.6</v>
       </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>64</v>
       </c>
@@ -3683,38 +3768,41 @@
       <c r="H28">
         <v>0</v>
       </c>
-      <c r="I28" s="1" t="s">
-        <v>7</v>
+      <c r="I28">
+        <v>0</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L28" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L28" t="s">
+      <c r="M28" t="s">
         <v>402</v>
       </c>
-      <c r="M28" t="s">
+      <c r="N28" t="s">
         <v>209</v>
       </c>
-      <c r="N28" t="s">
+      <c r="O28" t="s">
         <v>210</v>
       </c>
-      <c r="O28" t="s">
+      <c r="P28" t="s">
         <v>194</v>
       </c>
-      <c r="P28" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q28">
+      <c r="Q28" t="s">
+        <v>34</v>
+      </c>
+      <c r="R28">
         <v>62.6</v>
       </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>65</v>
       </c>
@@ -3739,38 +3827,41 @@
       <c r="H29">
         <v>0</v>
       </c>
-      <c r="I29" s="1" t="s">
-        <v>7</v>
+      <c r="I29">
+        <v>0</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L29" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L29" t="s">
+      <c r="M29" t="s">
         <v>403</v>
       </c>
-      <c r="M29" t="s">
+      <c r="N29" t="s">
         <v>211</v>
       </c>
-      <c r="N29" t="s">
+      <c r="O29" t="s">
         <v>212</v>
       </c>
-      <c r="O29" t="s">
+      <c r="P29" t="s">
         <v>213</v>
       </c>
-      <c r="P29" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q29">
+      <c r="Q29" t="s">
+        <v>34</v>
+      </c>
+      <c r="R29">
         <v>62.6</v>
       </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -3795,38 +3886,41 @@
       <c r="H30">
         <v>0</v>
       </c>
-      <c r="I30" s="1" t="s">
-        <v>7</v>
+      <c r="I30">
+        <v>0</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L30" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L30" t="s">
+      <c r="M30" t="s">
         <v>404</v>
       </c>
-      <c r="M30" t="s">
+      <c r="N30" t="s">
         <v>214</v>
       </c>
-      <c r="N30" t="s">
+      <c r="O30" t="s">
         <v>215</v>
       </c>
-      <c r="O30" t="s">
+      <c r="P30" t="s">
         <v>213</v>
       </c>
-      <c r="P30" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q30">
+      <c r="Q30" t="s">
+        <v>34</v>
+      </c>
+      <c r="R30">
         <v>62.6</v>
       </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>67</v>
       </c>
@@ -3851,38 +3945,41 @@
       <c r="H31">
         <v>0</v>
       </c>
-      <c r="I31" s="1" t="s">
-        <v>7</v>
+      <c r="I31">
+        <v>0</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L31" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L31" t="s">
+      <c r="M31" t="s">
         <v>405</v>
       </c>
-      <c r="M31" t="s">
+      <c r="N31" t="s">
         <v>216</v>
       </c>
-      <c r="N31" t="s">
+      <c r="O31" t="s">
         <v>217</v>
       </c>
-      <c r="O31" t="s">
+      <c r="P31" t="s">
         <v>213</v>
       </c>
-      <c r="P31" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q31">
+      <c r="Q31" t="s">
+        <v>34</v>
+      </c>
+      <c r="R31">
         <v>62.6</v>
       </c>
-      <c r="R31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>68</v>
       </c>
@@ -3907,38 +4004,41 @@
       <c r="H32">
         <v>0</v>
       </c>
-      <c r="I32" s="1" t="s">
-        <v>7</v>
+      <c r="I32">
+        <v>0</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L32" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L32" t="s">
+      <c r="M32" t="s">
         <v>406</v>
       </c>
-      <c r="M32" t="s">
+      <c r="N32" t="s">
         <v>218</v>
       </c>
-      <c r="N32" t="s">
+      <c r="O32" t="s">
         <v>219</v>
       </c>
-      <c r="O32" t="s">
+      <c r="P32" t="s">
         <v>213</v>
       </c>
-      <c r="P32" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q32">
+      <c r="Q32" t="s">
+        <v>34</v>
+      </c>
+      <c r="R32">
         <v>62.6</v>
       </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -3963,38 +4063,41 @@
       <c r="H33">
         <v>0</v>
       </c>
-      <c r="I33" s="1" t="s">
-        <v>7</v>
+      <c r="I33">
+        <v>0</v>
       </c>
       <c r="J33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L33" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L33" t="s">
+      <c r="M33" t="s">
         <v>407</v>
       </c>
-      <c r="M33" t="s">
+      <c r="N33" t="s">
         <v>220</v>
       </c>
-      <c r="N33" t="s">
+      <c r="O33" t="s">
         <v>221</v>
       </c>
-      <c r="O33" t="s">
+      <c r="P33" t="s">
         <v>213</v>
       </c>
-      <c r="P33" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q33">
+      <c r="Q33" t="s">
+        <v>34</v>
+      </c>
+      <c r="R33">
         <v>62.6</v>
       </c>
-      <c r="R33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>70</v>
       </c>
@@ -4019,38 +4122,41 @@
       <c r="H34">
         <v>0</v>
       </c>
-      <c r="I34" s="1" t="s">
-        <v>7</v>
+      <c r="I34">
+        <v>0</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L34" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L34" t="s">
+      <c r="M34" t="s">
         <v>408</v>
       </c>
-      <c r="M34" t="s">
+      <c r="N34" t="s">
         <v>222</v>
       </c>
-      <c r="N34" t="s">
+      <c r="O34" t="s">
         <v>223</v>
       </c>
-      <c r="O34" t="s">
+      <c r="P34" t="s">
         <v>213</v>
       </c>
-      <c r="P34" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q34">
+      <c r="Q34" t="s">
+        <v>34</v>
+      </c>
+      <c r="R34">
         <v>62.6</v>
       </c>
-      <c r="R34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>71</v>
       </c>
@@ -4075,38 +4181,41 @@
       <c r="H35">
         <v>0</v>
       </c>
-      <c r="I35" s="1" t="s">
-        <v>7</v>
+      <c r="I35">
+        <v>0</v>
       </c>
       <c r="J35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L35" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L35" t="s">
+      <c r="M35" t="s">
         <v>409</v>
       </c>
-      <c r="M35" t="s">
+      <c r="N35" t="s">
         <v>224</v>
       </c>
-      <c r="N35" t="s">
+      <c r="O35" t="s">
         <v>225</v>
       </c>
-      <c r="O35" t="s">
+      <c r="P35" t="s">
         <v>213</v>
       </c>
-      <c r="P35" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q35">
+      <c r="Q35" t="s">
+        <v>34</v>
+      </c>
+      <c r="R35">
         <v>62.6</v>
       </c>
-      <c r="R35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>72</v>
       </c>
@@ -4131,38 +4240,41 @@
       <c r="H36">
         <v>0</v>
       </c>
-      <c r="I36" s="1" t="s">
-        <v>7</v>
+      <c r="I36">
+        <v>0</v>
       </c>
       <c r="J36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L36" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L36" t="s">
+      <c r="M36" t="s">
         <v>410</v>
       </c>
-      <c r="M36" t="s">
+      <c r="N36" t="s">
         <v>226</v>
       </c>
-      <c r="N36" t="s">
+      <c r="O36" t="s">
         <v>227</v>
       </c>
-      <c r="O36" t="s">
+      <c r="P36" t="s">
         <v>213</v>
       </c>
-      <c r="P36" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q36">
+      <c r="Q36" t="s">
+        <v>34</v>
+      </c>
+      <c r="R36">
         <v>62.6</v>
       </c>
-      <c r="R36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>73</v>
       </c>
@@ -4187,38 +4299,41 @@
       <c r="H37">
         <v>0</v>
       </c>
-      <c r="I37" s="1" t="s">
-        <v>7</v>
+      <c r="I37">
+        <v>0</v>
       </c>
       <c r="J37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L37" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L37" t="s">
+      <c r="M37" t="s">
         <v>411</v>
       </c>
-      <c r="M37" t="s">
+      <c r="N37" t="s">
         <v>228</v>
       </c>
-      <c r="N37" t="s">
+      <c r="O37" t="s">
         <v>229</v>
       </c>
-      <c r="O37" t="s">
+      <c r="P37" t="s">
         <v>213</v>
       </c>
-      <c r="P37" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q37">
+      <c r="Q37" t="s">
+        <v>34</v>
+      </c>
+      <c r="R37">
         <v>62.6</v>
       </c>
-      <c r="R37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>74</v>
       </c>
@@ -4243,38 +4358,41 @@
       <c r="H38">
         <v>0</v>
       </c>
-      <c r="I38" s="1" t="s">
-        <v>7</v>
+      <c r="I38">
+        <v>0</v>
       </c>
       <c r="J38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L38" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L38" t="s">
+      <c r="M38" t="s">
         <v>412</v>
       </c>
-      <c r="M38" t="s">
+      <c r="N38" t="s">
         <v>230</v>
       </c>
-      <c r="N38" t="s">
+      <c r="O38" t="s">
         <v>231</v>
       </c>
-      <c r="O38" t="s">
+      <c r="P38" t="s">
         <v>213</v>
       </c>
-      <c r="P38" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q38">
+      <c r="Q38" t="s">
+        <v>34</v>
+      </c>
+      <c r="R38">
         <v>62.6</v>
       </c>
-      <c r="R38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>75</v>
       </c>
@@ -4299,38 +4417,41 @@
       <c r="H39">
         <v>0</v>
       </c>
-      <c r="I39" s="1" t="s">
-        <v>7</v>
+      <c r="I39">
+        <v>0</v>
       </c>
       <c r="J39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L39" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L39" t="s">
+      <c r="M39" t="s">
         <v>413</v>
       </c>
-      <c r="M39" t="s">
+      <c r="N39" t="s">
         <v>232</v>
       </c>
-      <c r="N39" t="s">
+      <c r="O39" t="s">
         <v>233</v>
       </c>
-      <c r="O39" t="s">
+      <c r="P39" t="s">
         <v>213</v>
       </c>
-      <c r="P39" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q39">
+      <c r="Q39" t="s">
+        <v>34</v>
+      </c>
+      <c r="R39">
         <v>62.6</v>
       </c>
-      <c r="R39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>76</v>
       </c>
@@ -4355,38 +4476,41 @@
       <c r="H40">
         <v>0</v>
       </c>
-      <c r="I40" s="1" t="s">
-        <v>7</v>
+      <c r="I40">
+        <v>0</v>
       </c>
       <c r="J40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L40" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L40" t="s">
+      <c r="M40" t="s">
         <v>414</v>
       </c>
-      <c r="M40" t="s">
+      <c r="N40" t="s">
         <v>234</v>
       </c>
-      <c r="N40" t="s">
+      <c r="O40" t="s">
         <v>235</v>
       </c>
-      <c r="O40" t="s">
+      <c r="P40" t="s">
         <v>213</v>
       </c>
-      <c r="P40" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q40">
+      <c r="Q40" t="s">
+        <v>34</v>
+      </c>
+      <c r="R40">
         <v>62.6</v>
       </c>
-      <c r="R40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>77</v>
       </c>
@@ -4411,38 +4535,41 @@
       <c r="H41">
         <v>0</v>
       </c>
-      <c r="I41" s="1" t="s">
-        <v>7</v>
+      <c r="I41">
+        <v>0</v>
       </c>
       <c r="J41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L41" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L41" t="s">
+      <c r="M41" t="s">
         <v>415</v>
       </c>
-      <c r="M41" t="s">
+      <c r="N41" t="s">
         <v>236</v>
       </c>
-      <c r="N41" t="s">
+      <c r="O41" t="s">
         <v>237</v>
       </c>
-      <c r="O41" t="s">
+      <c r="P41" t="s">
         <v>238</v>
       </c>
-      <c r="P41" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q41">
+      <c r="Q41" t="s">
+        <v>34</v>
+      </c>
+      <c r="R41">
         <v>62.6</v>
       </c>
-      <c r="R41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>78</v>
       </c>
@@ -4467,38 +4594,41 @@
       <c r="H42">
         <v>0</v>
       </c>
-      <c r="I42" s="1" t="s">
-        <v>7</v>
+      <c r="I42">
+        <v>0</v>
       </c>
       <c r="J42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L42" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L42" t="s">
+      <c r="M42" t="s">
         <v>416</v>
       </c>
-      <c r="M42" t="s">
+      <c r="N42" t="s">
         <v>239</v>
       </c>
-      <c r="N42" t="s">
+      <c r="O42" t="s">
         <v>240</v>
       </c>
-      <c r="O42" t="s">
+      <c r="P42" t="s">
         <v>238</v>
       </c>
-      <c r="P42" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q42">
+      <c r="Q42" t="s">
+        <v>34</v>
+      </c>
+      <c r="R42">
         <v>62.6</v>
       </c>
-      <c r="R42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>79</v>
       </c>
@@ -4523,38 +4653,41 @@
       <c r="H43">
         <v>0</v>
       </c>
-      <c r="I43" s="1" t="s">
-        <v>7</v>
+      <c r="I43">
+        <v>0</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L43" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L43" t="s">
+      <c r="M43" t="s">
         <v>417</v>
       </c>
-      <c r="M43" t="s">
+      <c r="N43" t="s">
         <v>241</v>
       </c>
-      <c r="N43" t="s">
+      <c r="O43" t="s">
         <v>242</v>
       </c>
-      <c r="O43" t="s">
+      <c r="P43" t="s">
         <v>238</v>
       </c>
-      <c r="P43" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q43">
+      <c r="Q43" t="s">
+        <v>34</v>
+      </c>
+      <c r="R43">
         <v>62.6</v>
       </c>
-      <c r="R43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>80</v>
       </c>
@@ -4579,38 +4712,41 @@
       <c r="H44">
         <v>0</v>
       </c>
-      <c r="I44" s="1" t="s">
-        <v>7</v>
+      <c r="I44">
+        <v>0</v>
       </c>
       <c r="J44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L44" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L44" t="s">
+      <c r="M44" t="s">
         <v>418</v>
       </c>
-      <c r="M44" t="s">
+      <c r="N44" t="s">
         <v>243</v>
       </c>
-      <c r="N44" t="s">
+      <c r="O44" t="s">
         <v>244</v>
       </c>
-      <c r="O44" t="s">
+      <c r="P44" t="s">
         <v>238</v>
       </c>
-      <c r="P44" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q44">
+      <c r="Q44" t="s">
+        <v>34</v>
+      </c>
+      <c r="R44">
         <v>62.6</v>
       </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>81</v>
       </c>
@@ -4635,38 +4771,41 @@
       <c r="H45">
         <v>0</v>
       </c>
-      <c r="I45" s="1" t="s">
-        <v>7</v>
+      <c r="I45">
+        <v>0</v>
       </c>
       <c r="J45" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L45" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L45" t="s">
+      <c r="M45" t="s">
         <v>419</v>
       </c>
-      <c r="M45" t="s">
+      <c r="N45" t="s">
         <v>245</v>
       </c>
-      <c r="N45" t="s">
+      <c r="O45" t="s">
         <v>246</v>
       </c>
-      <c r="O45" t="s">
+      <c r="P45" t="s">
         <v>238</v>
       </c>
-      <c r="P45" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q45">
+      <c r="Q45" t="s">
+        <v>34</v>
+      </c>
+      <c r="R45">
         <v>62.6</v>
       </c>
-      <c r="R45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="S45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>82</v>
       </c>
@@ -4691,38 +4830,41 @@
       <c r="H46">
         <v>0</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>7</v>
+      <c r="I46">
+        <v>0</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>7</v>
       </c>
       <c r="K46" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L46" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L46" s="2" t="s">
+      <c r="M46" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="M46" s="2" t="s">
+      <c r="N46" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="N46" s="2" t="s">
+      <c r="O46" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="O46" s="2" t="s">
+      <c r="P46" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="P46" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q46" s="2">
+      <c r="Q46" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R46" s="2">
         <v>62.6</v>
       </c>
-      <c r="R46" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>11</v>
       </c>
@@ -4747,38 +4889,41 @@
       <c r="H47">
         <v>0</v>
       </c>
-      <c r="I47" s="1" t="s">
-        <v>2</v>
+      <c r="I47">
+        <v>0</v>
       </c>
       <c r="J47" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L47" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="L47" t="s">
-        <v>338</v>
       </c>
       <c r="M47" t="s">
         <v>338</v>
       </c>
       <c r="N47" t="s">
+        <v>338</v>
+      </c>
+      <c r="O47" t="s">
         <v>339</v>
       </c>
-      <c r="O47" t="s">
+      <c r="P47" t="s">
         <v>340</v>
       </c>
-      <c r="P47" t="s">
+      <c r="Q47" t="s">
         <v>341</v>
-      </c>
-      <c r="Q47">
-        <v>162.5</v>
       </c>
       <c r="R47">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S47">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>12</v>
       </c>
@@ -4803,38 +4948,41 @@
       <c r="H48">
         <v>0</v>
       </c>
-      <c r="I48" s="1" t="s">
-        <v>2</v>
+      <c r="I48">
+        <v>0</v>
       </c>
       <c r="J48" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K48" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L48" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="L48" t="s">
-        <v>342</v>
       </c>
       <c r="M48" t="s">
         <v>342</v>
       </c>
       <c r="N48" t="s">
+        <v>342</v>
+      </c>
+      <c r="O48" t="s">
         <v>339</v>
       </c>
-      <c r="O48" t="s">
+      <c r="P48" t="s">
         <v>340</v>
       </c>
-      <c r="P48" t="s">
+      <c r="Q48" t="s">
         <v>341</v>
-      </c>
-      <c r="Q48">
-        <v>162.5</v>
       </c>
       <c r="R48">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S48">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>13</v>
       </c>
@@ -4859,38 +5007,41 @@
       <c r="H49">
         <v>0</v>
       </c>
-      <c r="I49" s="1" t="s">
-        <v>2</v>
+      <c r="I49">
+        <v>0</v>
       </c>
       <c r="J49" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K49" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L49" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="L49" t="s">
-        <v>343</v>
       </c>
       <c r="M49" t="s">
         <v>343</v>
       </c>
       <c r="N49" t="s">
+        <v>343</v>
+      </c>
+      <c r="O49" t="s">
         <v>339</v>
       </c>
-      <c r="O49" t="s">
+      <c r="P49" t="s">
         <v>340</v>
       </c>
-      <c r="P49" t="s">
+      <c r="Q49" t="s">
         <v>341</v>
-      </c>
-      <c r="Q49">
-        <v>162.5</v>
       </c>
       <c r="R49">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S49">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>14</v>
       </c>
@@ -4915,38 +5066,41 @@
       <c r="H50">
         <v>0</v>
       </c>
-      <c r="I50" s="1" t="s">
-        <v>2</v>
+      <c r="I50">
+        <v>0</v>
       </c>
       <c r="J50" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K50" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L50" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="L50" t="s">
-        <v>344</v>
       </c>
       <c r="M50" t="s">
         <v>344</v>
       </c>
       <c r="N50" t="s">
+        <v>344</v>
+      </c>
+      <c r="O50" t="s">
         <v>335</v>
       </c>
-      <c r="O50" t="s">
+      <c r="P50" t="s">
         <v>336</v>
       </c>
-      <c r="P50" t="s">
+      <c r="Q50" t="s">
         <v>337</v>
-      </c>
-      <c r="Q50">
-        <v>162.5</v>
       </c>
       <c r="R50">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S50">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>17</v>
       </c>
@@ -4971,38 +5125,41 @@
       <c r="H51">
         <v>0</v>
       </c>
-      <c r="I51" s="1" t="s">
-        <v>2</v>
+      <c r="I51">
+        <v>0</v>
       </c>
       <c r="J51" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K51" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L51" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="L51" t="s">
-        <v>345</v>
       </c>
       <c r="M51" t="s">
         <v>345</v>
       </c>
       <c r="N51" t="s">
+        <v>345</v>
+      </c>
+      <c r="O51" t="s">
         <v>346</v>
       </c>
-      <c r="O51" t="s">
+      <c r="P51" t="s">
         <v>347</v>
       </c>
-      <c r="P51" t="s">
+      <c r="Q51" t="s">
         <v>348</v>
-      </c>
-      <c r="Q51">
-        <v>162.5</v>
       </c>
       <c r="R51">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S51">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -5027,38 +5184,41 @@
       <c r="H52">
         <v>0</v>
       </c>
-      <c r="I52" s="1" t="s">
-        <v>2</v>
+      <c r="I52">
+        <v>0</v>
       </c>
       <c r="J52" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K52" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L52" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="L52" t="s">
-        <v>349</v>
       </c>
       <c r="M52" t="s">
         <v>349</v>
       </c>
       <c r="N52" t="s">
+        <v>349</v>
+      </c>
+      <c r="O52" t="s">
         <v>346</v>
       </c>
-      <c r="O52" t="s">
+      <c r="P52" t="s">
         <v>347</v>
       </c>
-      <c r="P52" t="s">
+      <c r="Q52" t="s">
         <v>348</v>
-      </c>
-      <c r="Q52">
-        <v>162.5</v>
       </c>
       <c r="R52">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="53" spans="1:18" s="9" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="S52">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" s="9" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="9" t="s">
         <v>19</v>
       </c>
@@ -5083,38 +5243,41 @@
       <c r="H53">
         <v>0</v>
       </c>
-      <c r="I53" s="11" t="s">
-        <v>2</v>
+      <c r="I53">
+        <v>0</v>
       </c>
       <c r="J53" s="11" t="s">
         <v>2</v>
       </c>
       <c r="K53" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="L53" s="11" t="s">
         <v>9</v>
-      </c>
-      <c r="L53" s="9" t="s">
-        <v>350</v>
       </c>
       <c r="M53" s="9" t="s">
         <v>350</v>
       </c>
       <c r="N53" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="O53" s="9" t="s">
         <v>346</v>
       </c>
-      <c r="O53" s="9" t="s">
+      <c r="P53" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="P53" s="9" t="s">
+      <c r="Q53" s="9" t="s">
         <v>348</v>
-      </c>
-      <c r="Q53" s="9">
-        <v>162.5</v>
       </c>
       <c r="R53" s="9">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="54" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="S53" s="9">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
         <v>20</v>
       </c>
@@ -5139,38 +5302,41 @@
       <c r="H54">
         <v>1</v>
       </c>
-      <c r="I54" s="8" t="s">
-        <v>2</v>
+      <c r="I54">
+        <v>0</v>
       </c>
       <c r="J54" s="8" t="s">
         <v>2</v>
       </c>
       <c r="K54" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="L54" s="8" t="s">
         <v>9</v>
-      </c>
-      <c r="L54" s="6" t="s">
-        <v>351</v>
       </c>
       <c r="M54" s="6" t="s">
         <v>351</v>
       </c>
       <c r="N54" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="O54" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="O54" s="6" t="s">
+      <c r="P54" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="P54" s="6" t="s">
+      <c r="Q54" s="6" t="s">
         <v>348</v>
-      </c>
-      <c r="Q54" s="6">
-        <v>162.5</v>
       </c>
       <c r="R54" s="6">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="55" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="S54" s="6">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
         <v>371</v>
       </c>
@@ -5195,38 +5361,41 @@
       <c r="H55">
         <v>1</v>
       </c>
-      <c r="I55" s="8" t="s">
-        <v>2</v>
+      <c r="I55">
+        <v>0</v>
       </c>
       <c r="J55" s="8" t="s">
         <v>2</v>
       </c>
       <c r="K55" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="L55" s="8" t="s">
         <v>9</v>
-      </c>
-      <c r="L55" s="6" t="s">
-        <v>372</v>
       </c>
       <c r="M55" s="6" t="s">
         <v>372</v>
       </c>
       <c r="N55" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="O55" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="O55" s="6" t="s">
+      <c r="P55" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="P55" s="6" t="s">
+      <c r="Q55" s="6" t="s">
         <v>375</v>
-      </c>
-      <c r="Q55" s="6">
-        <v>162.5</v>
       </c>
       <c r="R55" s="6">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="56" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="S55" s="6">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="6" t="s">
         <v>366</v>
       </c>
@@ -5251,38 +5420,41 @@
       <c r="H56">
         <v>1</v>
       </c>
-      <c r="I56" s="8" t="s">
-        <v>2</v>
+      <c r="I56">
+        <v>0</v>
       </c>
       <c r="J56" s="8" t="s">
         <v>2</v>
       </c>
       <c r="K56" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="L56" s="8" t="s">
         <v>9</v>
-      </c>
-      <c r="L56" s="6" t="s">
-        <v>367</v>
       </c>
       <c r="M56" s="6" t="s">
         <v>367</v>
       </c>
       <c r="N56" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="O56" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="O56" s="6" t="s">
+      <c r="P56" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="P56" s="6" t="s">
+      <c r="Q56" s="6" t="s">
         <v>370</v>
-      </c>
-      <c r="Q56" s="6">
-        <v>162.5</v>
       </c>
       <c r="R56" s="6">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="6">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>21</v>
       </c>
@@ -5307,38 +5479,41 @@
       <c r="H57">
         <v>0</v>
       </c>
-      <c r="I57" s="1" t="s">
-        <v>2</v>
+      <c r="I57">
+        <v>0</v>
       </c>
       <c r="J57" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K57" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L57" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="L57" t="s">
-        <v>352</v>
       </c>
       <c r="M57" t="s">
         <v>352</v>
       </c>
       <c r="N57" t="s">
+        <v>352</v>
+      </c>
+      <c r="O57" t="s">
         <v>353</v>
       </c>
-      <c r="O57" t="s">
+      <c r="P57" t="s">
         <v>354</v>
       </c>
-      <c r="P57" t="s">
+      <c r="Q57" t="s">
         <v>355</v>
-      </c>
-      <c r="Q57">
-        <v>162.5</v>
       </c>
       <c r="R57">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S57">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>22</v>
       </c>
@@ -5363,38 +5538,41 @@
       <c r="H58">
         <v>0</v>
       </c>
-      <c r="I58" s="1" t="s">
-        <v>2</v>
+      <c r="I58">
+        <v>0</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K58" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L58" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="L58" t="s">
-        <v>356</v>
       </c>
       <c r="M58" t="s">
         <v>356</v>
       </c>
       <c r="N58" t="s">
+        <v>356</v>
+      </c>
+      <c r="O58" t="s">
         <v>353</v>
       </c>
-      <c r="O58" t="s">
+      <c r="P58" t="s">
         <v>354</v>
       </c>
-      <c r="P58" t="s">
+      <c r="Q58" t="s">
         <v>355</v>
-      </c>
-      <c r="Q58">
-        <v>162.5</v>
       </c>
       <c r="R58">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S58">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>23</v>
       </c>
@@ -5419,38 +5597,41 @@
       <c r="H59">
         <v>0</v>
       </c>
-      <c r="I59" s="1" t="s">
-        <v>2</v>
+      <c r="I59">
+        <v>0</v>
       </c>
       <c r="J59" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K59" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L59" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="L59" t="s">
-        <v>357</v>
       </c>
       <c r="M59" t="s">
         <v>357</v>
       </c>
       <c r="N59" t="s">
+        <v>357</v>
+      </c>
+      <c r="O59" t="s">
         <v>353</v>
       </c>
-      <c r="O59" t="s">
+      <c r="P59" t="s">
         <v>354</v>
       </c>
-      <c r="P59" t="s">
+      <c r="Q59" t="s">
         <v>355</v>
-      </c>
-      <c r="Q59">
-        <v>162.5</v>
       </c>
       <c r="R59">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="60" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="S59">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>24</v>
       </c>
@@ -5475,38 +5656,41 @@
       <c r="H60">
         <v>0</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>2</v>
+      <c r="I60">
+        <v>0</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>2</v>
       </c>
       <c r="K60" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="L60" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="L60" s="2" t="s">
-        <v>358</v>
       </c>
       <c r="M60" s="2" t="s">
         <v>358</v>
       </c>
       <c r="N60" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="O60" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="O60" s="2" t="s">
+      <c r="P60" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="P60" s="2" t="s">
+      <c r="Q60" s="2" t="s">
         <v>355</v>
-      </c>
-      <c r="Q60" s="2">
-        <v>162.5</v>
       </c>
       <c r="R60" s="2">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="2">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>15</v>
       </c>
@@ -5531,38 +5715,41 @@
       <c r="H61">
         <v>0</v>
       </c>
-      <c r="I61" s="1" t="s">
-        <v>4</v>
+      <c r="I61">
+        <v>0</v>
       </c>
       <c r="J61" s="1" t="s">
         <v>4</v>
       </c>
       <c r="K61" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L61" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="L61" t="s">
-        <v>359</v>
       </c>
       <c r="M61" t="s">
         <v>359</v>
       </c>
       <c r="N61" t="s">
+        <v>359</v>
+      </c>
+      <c r="O61" t="s">
         <v>360</v>
       </c>
-      <c r="O61" t="s">
+      <c r="P61" t="s">
         <v>361</v>
       </c>
-      <c r="P61" t="s">
+      <c r="Q61" t="s">
         <v>362</v>
       </c>
-      <c r="Q61">
+      <c r="R61">
         <v>92.6</v>
       </c>
-      <c r="R61">
+      <c r="S61">
         <v>200</v>
       </c>
     </row>
-    <row r="62" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>16</v>
       </c>
@@ -5587,38 +5774,41 @@
       <c r="H62">
         <v>0</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
+      <c r="I62">
+        <v>0</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="L62" s="2" t="s">
-        <v>363</v>
       </c>
       <c r="M62" s="2" t="s">
         <v>363</v>
       </c>
       <c r="N62" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="O62" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="O62" s="2" t="s">
+      <c r="P62" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="P62" s="2" t="s">
+      <c r="Q62" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="Q62" s="2">
+      <c r="R62" s="2">
         <v>92.6</v>
       </c>
-      <c r="R62" s="2">
+      <c r="S62" s="2">
         <v>200</v>
       </c>
     </row>
-    <row r="63" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="12" t="s">
         <v>25</v>
       </c>
@@ -5643,38 +5833,41 @@
       <c r="H63" s="12">
         <v>1</v>
       </c>
-      <c r="I63" s="8" t="s">
-        <v>334</v>
+      <c r="I63">
+        <v>0</v>
       </c>
       <c r="J63" s="8" t="s">
         <v>334</v>
       </c>
       <c r="K63" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="L63" s="8" t="s">
         <v>9</v>
-      </c>
-      <c r="L63" s="12" t="s">
-        <v>115</v>
       </c>
       <c r="M63" s="12" t="s">
         <v>115</v>
       </c>
       <c r="N63" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="O63" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="O63" s="12" t="s">
+      <c r="P63" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="P63" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q63" s="12">
+      <c r="Q63" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="R63" s="12">
         <v>25</v>
       </c>
-      <c r="R63" s="12">
+      <c r="S63" s="12">
         <v>160</v>
       </c>
     </row>
-    <row r="64" spans="1:18" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:19" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="13" t="s">
         <v>26</v>
       </c>
@@ -5699,38 +5892,41 @@
       <c r="H64" s="12">
         <v>1</v>
       </c>
-      <c r="I64" s="8" t="s">
-        <v>334</v>
+      <c r="I64">
+        <v>0</v>
       </c>
       <c r="J64" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="K64" s="15" t="s">
+      <c r="K64" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="L64" s="15" t="s">
         <v>9</v>
-      </c>
-      <c r="L64" s="13" t="s">
-        <v>118</v>
       </c>
       <c r="M64" s="13" t="s">
         <v>118</v>
       </c>
       <c r="N64" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="O64" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="O64" s="13" t="s">
+      <c r="P64" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="P64" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q64" s="13">
+      <c r="Q64" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="R64" s="13">
         <v>25</v>
       </c>
-      <c r="R64" s="13">
+      <c r="S64" s="13">
         <v>160</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>85</v>
       </c>
@@ -5755,38 +5951,41 @@
       <c r="H65">
         <v>0</v>
       </c>
-      <c r="I65" s="1" t="s">
-        <v>4</v>
+      <c r="I65">
+        <v>0</v>
       </c>
       <c r="J65" s="1" t="s">
         <v>4</v>
       </c>
       <c r="K65" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L65" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="L65" t="s">
-        <v>121</v>
       </c>
       <c r="M65" t="s">
         <v>121</v>
       </c>
-      <c r="N65" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="O65" t="s">
+      <c r="N65" t="s">
+        <v>121</v>
+      </c>
+      <c r="O65" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P65" t="s">
         <v>122</v>
       </c>
-      <c r="P65" t="s">
+      <c r="Q65" t="s">
         <v>123</v>
       </c>
-      <c r="Q65">
+      <c r="R65">
         <v>92.6</v>
       </c>
-      <c r="R65">
+      <c r="S65">
         <v>200</v>
       </c>
     </row>
-    <row r="66" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>86</v>
       </c>
@@ -5811,38 +6010,41 @@
       <c r="H66">
         <v>0</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>4</v>
+      <c r="I66">
+        <v>0</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L66" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="L66" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="M66" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="O66" s="2" t="s">
+      <c r="N66" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="P66" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="P66" s="2" t="s">
+      <c r="Q66" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="Q66" s="2">
+      <c r="R66" s="2">
         <v>92.6</v>
       </c>
-      <c r="R66" s="2">
+      <c r="S66" s="2">
         <v>200</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>87</v>
       </c>
@@ -5867,38 +6069,41 @@
       <c r="H67">
         <v>0</v>
       </c>
-      <c r="I67" s="1" t="s">
-        <v>6</v>
+      <c r="I67">
+        <v>0</v>
       </c>
       <c r="J67" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L67" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="L67" t="s">
-        <v>127</v>
       </c>
       <c r="M67" t="s">
         <v>127</v>
       </c>
       <c r="N67" t="s">
+        <v>127</v>
+      </c>
+      <c r="O67" t="s">
         <v>128</v>
       </c>
-      <c r="O67" t="s">
+      <c r="P67" t="s">
         <v>129</v>
       </c>
-      <c r="P67" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q67">
+      <c r="Q67" t="s">
+        <v>34</v>
+      </c>
+      <c r="R67">
         <v>25</v>
       </c>
-      <c r="R67">
+      <c r="S67">
         <v>160</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>97</v>
       </c>
@@ -5923,38 +6128,41 @@
       <c r="H68">
         <v>0</v>
       </c>
-      <c r="I68" s="1" t="s">
-        <v>6</v>
+      <c r="I68">
+        <v>0</v>
       </c>
       <c r="J68" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L68" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="L68" t="s">
-        <v>127</v>
       </c>
       <c r="M68" t="s">
         <v>127</v>
       </c>
       <c r="N68" t="s">
+        <v>127</v>
+      </c>
+      <c r="O68" t="s">
         <v>128</v>
       </c>
-      <c r="O68" t="s">
+      <c r="P68" t="s">
         <v>130</v>
       </c>
-      <c r="P68" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q68">
+      <c r="Q68" t="s">
+        <v>34</v>
+      </c>
+      <c r="R68">
         <v>25</v>
       </c>
-      <c r="R68">
+      <c r="S68">
         <v>160</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>88</v>
       </c>
@@ -5979,17 +6187,17 @@
       <c r="H69">
         <v>0</v>
       </c>
-      <c r="I69" s="1" t="s">
-        <v>6</v>
+      <c r="I69">
+        <v>0</v>
       </c>
       <c r="J69" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L69" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="L69" t="s">
-        <v>131</v>
       </c>
       <c r="M69" t="s">
         <v>131</v>
@@ -5998,19 +6206,22 @@
         <v>131</v>
       </c>
       <c r="O69" t="s">
+        <v>131</v>
+      </c>
+      <c r="P69" t="s">
         <v>132</v>
       </c>
-      <c r="P69" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q69">
+      <c r="Q69" t="s">
+        <v>34</v>
+      </c>
+      <c r="R69">
         <v>25</v>
       </c>
-      <c r="R69">
+      <c r="S69">
         <v>160</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>89</v>
       </c>
@@ -6035,17 +6246,17 @@
       <c r="H70">
         <v>0</v>
       </c>
-      <c r="I70" s="1" t="s">
-        <v>6</v>
+      <c r="I70">
+        <v>0</v>
       </c>
       <c r="J70" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L70" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="L70" t="s">
-        <v>133</v>
       </c>
       <c r="M70" t="s">
         <v>133</v>
@@ -6054,19 +6265,22 @@
         <v>133</v>
       </c>
       <c r="O70" t="s">
+        <v>133</v>
+      </c>
+      <c r="P70" t="s">
         <v>134</v>
       </c>
-      <c r="P70" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q70">
+      <c r="Q70" t="s">
+        <v>34</v>
+      </c>
+      <c r="R70">
         <v>25</v>
       </c>
-      <c r="R70">
+      <c r="S70">
         <v>160</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>90</v>
       </c>
@@ -6091,17 +6305,17 @@
       <c r="H71">
         <v>0</v>
       </c>
-      <c r="I71" s="1" t="s">
-        <v>6</v>
+      <c r="I71">
+        <v>0</v>
       </c>
       <c r="J71" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L71" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="L71" t="s">
-        <v>135</v>
       </c>
       <c r="M71" t="s">
         <v>135</v>
@@ -6110,19 +6324,22 @@
         <v>135</v>
       </c>
       <c r="O71" t="s">
+        <v>135</v>
+      </c>
+      <c r="P71" t="s">
         <v>136</v>
       </c>
-      <c r="P71" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q71">
+      <c r="Q71" t="s">
+        <v>34</v>
+      </c>
+      <c r="R71">
         <v>25</v>
       </c>
-      <c r="R71">
+      <c r="S71">
         <v>160</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>91</v>
       </c>
@@ -6147,17 +6364,17 @@
       <c r="H72">
         <v>0</v>
       </c>
-      <c r="I72" s="1" t="s">
-        <v>6</v>
+      <c r="I72">
+        <v>0</v>
       </c>
       <c r="J72" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L72" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="L72" t="s">
-        <v>137</v>
       </c>
       <c r="M72" t="s">
         <v>137</v>
@@ -6166,19 +6383,22 @@
         <v>137</v>
       </c>
       <c r="O72" t="s">
+        <v>137</v>
+      </c>
+      <c r="P72" t="s">
         <v>138</v>
       </c>
-      <c r="P72" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q72">
+      <c r="Q72" t="s">
+        <v>34</v>
+      </c>
+      <c r="R72">
         <v>25</v>
       </c>
-      <c r="R72">
+      <c r="S72">
         <v>160</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>92</v>
       </c>
@@ -6203,17 +6423,17 @@
       <c r="H73">
         <v>0</v>
       </c>
-      <c r="I73" s="1" t="s">
-        <v>6</v>
+      <c r="I73">
+        <v>0</v>
       </c>
       <c r="J73" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K73" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L73" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="L73" t="s">
-        <v>139</v>
       </c>
       <c r="M73" t="s">
         <v>139</v>
@@ -6222,19 +6442,22 @@
         <v>139</v>
       </c>
       <c r="O73" t="s">
+        <v>139</v>
+      </c>
+      <c r="P73" t="s">
         <v>140</v>
       </c>
-      <c r="P73" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q73">
+      <c r="Q73" t="s">
+        <v>34</v>
+      </c>
+      <c r="R73">
         <v>25</v>
       </c>
-      <c r="R73">
+      <c r="S73">
         <v>160</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>93</v>
       </c>
@@ -6259,17 +6482,17 @@
       <c r="H74">
         <v>0</v>
       </c>
-      <c r="I74" s="1" t="s">
-        <v>6</v>
+      <c r="I74">
+        <v>0</v>
       </c>
       <c r="J74" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K74" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L74" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="L74" t="s">
-        <v>141</v>
       </c>
       <c r="M74" t="s">
         <v>141</v>
@@ -6278,19 +6501,22 @@
         <v>141</v>
       </c>
       <c r="O74" t="s">
+        <v>141</v>
+      </c>
+      <c r="P74" t="s">
         <v>142</v>
       </c>
-      <c r="P74" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q74">
+      <c r="Q74" t="s">
+        <v>34</v>
+      </c>
+      <c r="R74">
         <v>25</v>
       </c>
-      <c r="R74">
+      <c r="S74">
         <v>160</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>94</v>
       </c>
@@ -6315,17 +6541,17 @@
       <c r="H75">
         <v>0</v>
       </c>
-      <c r="I75" s="1" t="s">
-        <v>6</v>
+      <c r="I75">
+        <v>0</v>
       </c>
       <c r="J75" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K75" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L75" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="L75" t="s">
-        <v>143</v>
       </c>
       <c r="M75" t="s">
         <v>143</v>
@@ -6334,19 +6560,22 @@
         <v>143</v>
       </c>
       <c r="O75" t="s">
+        <v>143</v>
+      </c>
+      <c r="P75" t="s">
         <v>144</v>
       </c>
-      <c r="P75" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q75">
+      <c r="Q75" t="s">
+        <v>34</v>
+      </c>
+      <c r="R75">
         <v>25</v>
       </c>
-      <c r="R75">
+      <c r="S75">
         <v>160</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>95</v>
       </c>
@@ -6371,17 +6600,17 @@
       <c r="H76">
         <v>0</v>
       </c>
-      <c r="I76" s="1" t="s">
-        <v>6</v>
+      <c r="I76">
+        <v>0</v>
       </c>
       <c r="J76" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K76" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L76" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="L76" t="s">
-        <v>145</v>
       </c>
       <c r="M76" t="s">
         <v>145</v>
@@ -6390,19 +6619,22 @@
         <v>145</v>
       </c>
       <c r="O76" t="s">
+        <v>145</v>
+      </c>
+      <c r="P76" t="s">
         <v>146</v>
       </c>
-      <c r="P76" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q76">
+      <c r="Q76" t="s">
+        <v>34</v>
+      </c>
+      <c r="R76">
         <v>25</v>
       </c>
-      <c r="R76">
+      <c r="S76">
         <v>160</v>
       </c>
     </row>
-    <row r="77" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
         <v>96</v>
       </c>
@@ -6427,17 +6659,17 @@
       <c r="H77">
         <v>0</v>
       </c>
-      <c r="I77" s="3" t="s">
-        <v>6</v>
+      <c r="I77">
+        <v>0</v>
       </c>
       <c r="J77" s="3" t="s">
         <v>6</v>
       </c>
       <c r="K77" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L77" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="L77" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="M77" s="2" t="s">
         <v>147</v>
@@ -6446,19 +6678,22 @@
         <v>147</v>
       </c>
       <c r="O77" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="P77" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="P77" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q77" s="2">
+      <c r="Q77" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R77" s="2">
         <v>25</v>
       </c>
-      <c r="R77" s="2">
+      <c r="S77" s="2">
         <v>160</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>99</v>
       </c>
@@ -6483,38 +6718,41 @@
       <c r="H78">
         <v>0</v>
       </c>
-      <c r="I78" s="1" t="s">
-        <v>7</v>
+      <c r="I78">
+        <v>0</v>
       </c>
       <c r="J78" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K78" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K78" s="1" t="s">
+      <c r="L78" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L78" t="s">
-        <v>149</v>
       </c>
       <c r="M78" t="s">
         <v>149</v>
       </c>
       <c r="N78" t="s">
+        <v>149</v>
+      </c>
+      <c r="O78" t="s">
         <v>150</v>
       </c>
-      <c r="O78" t="s">
+      <c r="P78" t="s">
         <v>151</v>
       </c>
-      <c r="P78" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q78">
+      <c r="Q78" t="s">
+        <v>34</v>
+      </c>
+      <c r="R78">
         <v>60.4</v>
       </c>
-      <c r="R78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>100</v>
       </c>
@@ -6539,38 +6777,41 @@
       <c r="H79">
         <v>0</v>
       </c>
-      <c r="I79" s="1" t="s">
-        <v>7</v>
+      <c r="I79">
+        <v>0</v>
       </c>
       <c r="J79" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K79" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K79" s="1" t="s">
+      <c r="L79" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L79" t="s">
-        <v>152</v>
       </c>
       <c r="M79" t="s">
         <v>152</v>
       </c>
       <c r="N79" t="s">
+        <v>152</v>
+      </c>
+      <c r="O79" t="s">
         <v>150</v>
       </c>
-      <c r="O79" t="s">
+      <c r="P79" t="s">
         <v>151</v>
       </c>
-      <c r="P79" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q79">
+      <c r="Q79" t="s">
+        <v>34</v>
+      </c>
+      <c r="R79">
         <v>60.4</v>
       </c>
-      <c r="R79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>101</v>
       </c>
@@ -6595,38 +6836,41 @@
       <c r="H80">
         <v>0</v>
       </c>
-      <c r="I80" s="1" t="s">
-        <v>7</v>
+      <c r="I80">
+        <v>0</v>
       </c>
       <c r="J80" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K80" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K80" s="1" t="s">
+      <c r="L80" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L80" t="s">
-        <v>153</v>
       </c>
       <c r="M80" t="s">
         <v>153</v>
       </c>
       <c r="N80" t="s">
+        <v>153</v>
+      </c>
+      <c r="O80" t="s">
         <v>150</v>
       </c>
-      <c r="O80" t="s">
+      <c r="P80" t="s">
         <v>151</v>
       </c>
-      <c r="P80" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q80">
+      <c r="Q80" t="s">
+        <v>34</v>
+      </c>
+      <c r="R80">
         <v>60.4</v>
       </c>
-      <c r="R80">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>102</v>
       </c>
@@ -6651,38 +6895,41 @@
       <c r="H81">
         <v>0</v>
       </c>
-      <c r="I81" s="1" t="s">
-        <v>7</v>
+      <c r="I81">
+        <v>0</v>
       </c>
       <c r="J81" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K81" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K81" s="1" t="s">
+      <c r="L81" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L81" t="s">
-        <v>257</v>
       </c>
       <c r="M81" t="s">
         <v>257</v>
       </c>
       <c r="N81" t="s">
+        <v>257</v>
+      </c>
+      <c r="O81" t="s">
         <v>275</v>
       </c>
-      <c r="O81" t="s">
+      <c r="P81" t="s">
         <v>280</v>
       </c>
-      <c r="P81" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q81">
+      <c r="Q81" t="s">
+        <v>34</v>
+      </c>
+      <c r="R81">
         <v>60.4</v>
       </c>
-      <c r="R81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>103</v>
       </c>
@@ -6707,38 +6954,41 @@
       <c r="H82">
         <v>0</v>
       </c>
-      <c r="I82" s="1" t="s">
-        <v>7</v>
+      <c r="I82">
+        <v>0</v>
       </c>
       <c r="J82" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K82" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K82" s="1" t="s">
+      <c r="L82" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L82" t="s">
-        <v>258</v>
       </c>
       <c r="M82" t="s">
         <v>258</v>
       </c>
       <c r="N82" t="s">
+        <v>258</v>
+      </c>
+      <c r="O82" t="s">
         <v>275</v>
       </c>
-      <c r="O82" t="s">
+      <c r="P82" t="s">
         <v>280</v>
       </c>
-      <c r="P82" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q82">
+      <c r="Q82" t="s">
+        <v>34</v>
+      </c>
+      <c r="R82">
         <v>60.4</v>
       </c>
-      <c r="R82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>104</v>
       </c>
@@ -6763,38 +7013,41 @@
       <c r="H83">
         <v>0</v>
       </c>
-      <c r="I83" s="1" t="s">
-        <v>7</v>
+      <c r="I83">
+        <v>0</v>
       </c>
       <c r="J83" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K83" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K83" s="1" t="s">
+      <c r="L83" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L83" t="s">
-        <v>259</v>
       </c>
       <c r="M83" t="s">
         <v>259</v>
       </c>
       <c r="N83" t="s">
+        <v>259</v>
+      </c>
+      <c r="O83" t="s">
         <v>275</v>
       </c>
-      <c r="O83" t="s">
+      <c r="P83" t="s">
         <v>280</v>
       </c>
-      <c r="P83" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q83">
+      <c r="Q83" t="s">
+        <v>34</v>
+      </c>
+      <c r="R83">
         <v>60.4</v>
       </c>
-      <c r="R83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>105</v>
       </c>
@@ -6819,38 +7072,41 @@
       <c r="H84">
         <v>0</v>
       </c>
-      <c r="I84" s="1" t="s">
-        <v>7</v>
+      <c r="I84">
+        <v>0</v>
       </c>
       <c r="J84" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K84" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K84" s="1" t="s">
+      <c r="L84" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L84" t="s">
-        <v>260</v>
       </c>
       <c r="M84" t="s">
         <v>260</v>
       </c>
       <c r="N84" t="s">
+        <v>260</v>
+      </c>
+      <c r="O84" t="s">
         <v>276</v>
       </c>
-      <c r="O84" t="s">
+      <c r="P84" t="s">
         <v>281</v>
       </c>
-      <c r="P84" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q84">
+      <c r="Q84" t="s">
+        <v>34</v>
+      </c>
+      <c r="R84">
         <v>60.4</v>
       </c>
-      <c r="R84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>106</v>
       </c>
@@ -6875,38 +7131,41 @@
       <c r="H85">
         <v>0</v>
       </c>
-      <c r="I85" s="1" t="s">
-        <v>7</v>
+      <c r="I85">
+        <v>0</v>
       </c>
       <c r="J85" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K85" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K85" s="1" t="s">
+      <c r="L85" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L85" t="s">
-        <v>261</v>
       </c>
       <c r="M85" t="s">
         <v>261</v>
       </c>
       <c r="N85" t="s">
+        <v>261</v>
+      </c>
+      <c r="O85" t="s">
         <v>276</v>
       </c>
-      <c r="O85" t="s">
+      <c r="P85" t="s">
         <v>281</v>
       </c>
-      <c r="P85" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q85">
+      <c r="Q85" t="s">
+        <v>34</v>
+      </c>
+      <c r="R85">
         <v>60.4</v>
       </c>
-      <c r="R85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>107</v>
       </c>
@@ -6931,38 +7190,41 @@
       <c r="H86">
         <v>0</v>
       </c>
-      <c r="I86" s="1" t="s">
-        <v>7</v>
+      <c r="I86">
+        <v>0</v>
       </c>
       <c r="J86" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K86" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K86" s="1" t="s">
+      <c r="L86" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L86" t="s">
-        <v>262</v>
       </c>
       <c r="M86" t="s">
         <v>262</v>
       </c>
       <c r="N86" t="s">
+        <v>262</v>
+      </c>
+      <c r="O86" t="s">
         <v>276</v>
       </c>
-      <c r="O86" t="s">
+      <c r="P86" t="s">
         <v>281</v>
       </c>
-      <c r="P86" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q86">
+      <c r="Q86" t="s">
+        <v>34</v>
+      </c>
+      <c r="R86">
         <v>60.4</v>
       </c>
-      <c r="R86">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>272</v>
       </c>
@@ -6987,38 +7249,41 @@
       <c r="H87">
         <v>0</v>
       </c>
-      <c r="I87" s="1" t="s">
-        <v>7</v>
+      <c r="I87">
+        <v>0</v>
       </c>
       <c r="J87" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K87" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K87" s="1" t="s">
+      <c r="L87" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L87" t="s">
-        <v>263</v>
       </c>
       <c r="M87" t="s">
         <v>263</v>
       </c>
       <c r="N87" t="s">
+        <v>263</v>
+      </c>
+      <c r="O87" t="s">
         <v>277</v>
       </c>
-      <c r="O87" t="s">
+      <c r="P87" t="s">
         <v>282</v>
       </c>
-      <c r="P87" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q87">
+      <c r="Q87" t="s">
+        <v>34</v>
+      </c>
+      <c r="R87">
         <v>60.4</v>
       </c>
-      <c r="R87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>273</v>
       </c>
@@ -7043,38 +7308,41 @@
       <c r="H88">
         <v>0</v>
       </c>
-      <c r="I88" s="1" t="s">
-        <v>7</v>
+      <c r="I88">
+        <v>0</v>
       </c>
       <c r="J88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K88" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K88" s="1" t="s">
+      <c r="L88" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L88" t="s">
-        <v>264</v>
       </c>
       <c r="M88" t="s">
         <v>264</v>
       </c>
       <c r="N88" t="s">
+        <v>264</v>
+      </c>
+      <c r="O88" t="s">
         <v>277</v>
       </c>
-      <c r="O88" t="s">
+      <c r="P88" t="s">
         <v>282</v>
       </c>
-      <c r="P88" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q88">
+      <c r="Q88" t="s">
+        <v>34</v>
+      </c>
+      <c r="R88">
         <v>60.4</v>
       </c>
-      <c r="R88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>274</v>
       </c>
@@ -7099,38 +7367,41 @@
       <c r="H89">
         <v>0</v>
       </c>
-      <c r="I89" s="1" t="s">
-        <v>7</v>
+      <c r="I89">
+        <v>0</v>
       </c>
       <c r="J89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K89" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K89" s="1" t="s">
+      <c r="L89" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L89" t="s">
-        <v>265</v>
       </c>
       <c r="M89" t="s">
         <v>265</v>
       </c>
       <c r="N89" t="s">
+        <v>265</v>
+      </c>
+      <c r="O89" t="s">
         <v>277</v>
       </c>
-      <c r="O89" t="s">
+      <c r="P89" t="s">
         <v>282</v>
       </c>
-      <c r="P89" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q89">
+      <c r="Q89" t="s">
+        <v>34</v>
+      </c>
+      <c r="R89">
         <v>60.4</v>
       </c>
-      <c r="R89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>108</v>
       </c>
@@ -7155,38 +7426,41 @@
       <c r="H90">
         <v>0</v>
       </c>
-      <c r="I90" s="1" t="s">
-        <v>7</v>
+      <c r="I90">
+        <v>0</v>
       </c>
       <c r="J90" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K90" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K90" s="1" t="s">
+      <c r="L90" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L90" t="s">
-        <v>266</v>
       </c>
       <c r="M90" t="s">
         <v>266</v>
       </c>
       <c r="N90" t="s">
+        <v>266</v>
+      </c>
+      <c r="O90" t="s">
         <v>278</v>
       </c>
-      <c r="O90" t="s">
+      <c r="P90" t="s">
         <v>283</v>
       </c>
-      <c r="P90" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q90">
+      <c r="Q90" t="s">
+        <v>34</v>
+      </c>
+      <c r="R90">
         <v>60.4</v>
       </c>
-      <c r="R90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>109</v>
       </c>
@@ -7211,38 +7485,41 @@
       <c r="H91">
         <v>0</v>
       </c>
-      <c r="I91" s="1" t="s">
-        <v>7</v>
+      <c r="I91">
+        <v>0</v>
       </c>
       <c r="J91" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K91" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K91" s="1" t="s">
+      <c r="L91" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L91" t="s">
-        <v>267</v>
       </c>
       <c r="M91" t="s">
         <v>267</v>
       </c>
       <c r="N91" t="s">
+        <v>267</v>
+      </c>
+      <c r="O91" t="s">
         <v>278</v>
       </c>
-      <c r="O91" t="s">
+      <c r="P91" t="s">
         <v>283</v>
       </c>
-      <c r="P91" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q91">
+      <c r="Q91" t="s">
+        <v>34</v>
+      </c>
+      <c r="R91">
         <v>60.4</v>
       </c>
-      <c r="R91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>110</v>
       </c>
@@ -7267,38 +7544,41 @@
       <c r="H92">
         <v>0</v>
       </c>
-      <c r="I92" s="1" t="s">
-        <v>7</v>
+      <c r="I92">
+        <v>0</v>
       </c>
       <c r="J92" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K92" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K92" s="1" t="s">
+      <c r="L92" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L92" t="s">
-        <v>268</v>
       </c>
       <c r="M92" t="s">
         <v>268</v>
       </c>
       <c r="N92" t="s">
+        <v>268</v>
+      </c>
+      <c r="O92" t="s">
         <v>278</v>
       </c>
-      <c r="O92" t="s">
+      <c r="P92" t="s">
         <v>283</v>
       </c>
-      <c r="P92" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q92">
+      <c r="Q92" t="s">
+        <v>34</v>
+      </c>
+      <c r="R92">
         <v>60.4</v>
       </c>
-      <c r="R92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>111</v>
       </c>
@@ -7323,38 +7603,41 @@
       <c r="H93">
         <v>0</v>
       </c>
-      <c r="I93" s="1" t="s">
-        <v>7</v>
+      <c r="I93">
+        <v>0</v>
       </c>
       <c r="J93" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K93" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K93" s="1" t="s">
+      <c r="L93" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L93" t="s">
-        <v>269</v>
       </c>
       <c r="M93" t="s">
         <v>269</v>
       </c>
       <c r="N93" t="s">
+        <v>269</v>
+      </c>
+      <c r="O93" t="s">
         <v>279</v>
       </c>
-      <c r="O93" t="s">
+      <c r="P93" t="s">
         <v>284</v>
       </c>
-      <c r="P93" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q93">
+      <c r="Q93" t="s">
+        <v>34</v>
+      </c>
+      <c r="R93">
         <v>60.4</v>
       </c>
-      <c r="R93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>112</v>
       </c>
@@ -7379,38 +7662,41 @@
       <c r="H94">
         <v>0</v>
       </c>
-      <c r="I94" s="1" t="s">
-        <v>7</v>
+      <c r="I94">
+        <v>0</v>
       </c>
       <c r="J94" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K94" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K94" s="1" t="s">
+      <c r="L94" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L94" t="s">
-        <v>270</v>
       </c>
       <c r="M94" t="s">
         <v>270</v>
       </c>
       <c r="N94" t="s">
+        <v>270</v>
+      </c>
+      <c r="O94" t="s">
         <v>279</v>
       </c>
-      <c r="O94" t="s">
+      <c r="P94" t="s">
         <v>284</v>
       </c>
-      <c r="P94" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q94">
+      <c r="Q94" t="s">
+        <v>34</v>
+      </c>
+      <c r="R94">
         <v>60.4</v>
       </c>
-      <c r="R94">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="S94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
         <v>113</v>
       </c>
@@ -7435,38 +7721,41 @@
       <c r="H95">
         <v>0</v>
       </c>
-      <c r="I95" s="3" t="s">
-        <v>7</v>
+      <c r="I95">
+        <v>0</v>
       </c>
       <c r="J95" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K95" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="K95" s="3" t="s">
+      <c r="L95" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="L95" s="2" t="s">
-        <v>271</v>
       </c>
       <c r="M95" s="2" t="s">
         <v>271</v>
       </c>
       <c r="N95" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="O95" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="O95" s="2" t="s">
+      <c r="P95" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="P95" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q95" s="2">
+      <c r="Q95" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R95" s="2">
         <v>60.4</v>
       </c>
-      <c r="R95" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>251</v>
       </c>
@@ -7491,38 +7780,41 @@
       <c r="H96">
         <v>0</v>
       </c>
-      <c r="I96" s="1" t="s">
-        <v>7</v>
+      <c r="I96">
+        <v>0</v>
       </c>
       <c r="J96" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K96" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K96" s="1" t="s">
+      <c r="L96" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L96" t="s">
-        <v>253</v>
       </c>
       <c r="M96" t="s">
         <v>253</v>
       </c>
       <c r="N96" t="s">
+        <v>253</v>
+      </c>
+      <c r="O96" t="s">
         <v>254</v>
       </c>
-      <c r="O96" t="s">
+      <c r="P96" t="s">
         <v>249</v>
       </c>
-      <c r="P96" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q96">
+      <c r="Q96" t="s">
+        <v>34</v>
+      </c>
+      <c r="R96">
         <v>80</v>
       </c>
-      <c r="R96">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="S96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>252</v>
       </c>
@@ -7547,38 +7839,41 @@
       <c r="H97">
         <v>0</v>
       </c>
-      <c r="I97" s="3" t="s">
-        <v>7</v>
+      <c r="I97">
+        <v>0</v>
       </c>
       <c r="J97" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K97" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="K97" s="3" t="s">
+      <c r="L97" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="L97" s="2" t="s">
-        <v>255</v>
       </c>
       <c r="M97" s="2" t="s">
         <v>255</v>
       </c>
       <c r="N97" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="O97" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="O97" s="2" t="s">
+      <c r="P97" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="P97" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q97" s="2">
+      <c r="Q97" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R97" s="2">
         <v>80</v>
       </c>
-      <c r="R97" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>285</v>
       </c>
@@ -7603,38 +7898,41 @@
       <c r="H98">
         <v>0</v>
       </c>
-      <c r="I98" s="1" t="s">
-        <v>7</v>
+      <c r="I98">
+        <v>0</v>
       </c>
       <c r="J98" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K98" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L98" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L98" t="s">
-        <v>291</v>
       </c>
       <c r="M98" t="s">
         <v>291</v>
       </c>
       <c r="N98" t="s">
+        <v>291</v>
+      </c>
+      <c r="O98" t="s">
         <v>292</v>
       </c>
-      <c r="O98" t="s">
+      <c r="P98" t="s">
         <v>300</v>
       </c>
-      <c r="P98" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q98" s="4">
+      <c r="Q98" t="s">
+        <v>34</v>
+      </c>
+      <c r="R98" s="4">
         <v>100</v>
       </c>
-      <c r="R98" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>286</v>
       </c>
@@ -7659,38 +7957,41 @@
       <c r="H99">
         <v>0</v>
       </c>
-      <c r="I99" s="1" t="s">
-        <v>7</v>
+      <c r="I99">
+        <v>0</v>
       </c>
       <c r="J99" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K99" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L99" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L99" t="s">
-        <v>293</v>
       </c>
       <c r="M99" t="s">
         <v>293</v>
       </c>
       <c r="N99" t="s">
+        <v>293</v>
+      </c>
+      <c r="O99" t="s">
         <v>292</v>
       </c>
-      <c r="O99" t="s">
+      <c r="P99" t="s">
         <v>300</v>
       </c>
-      <c r="P99" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q99" s="4">
+      <c r="Q99" t="s">
+        <v>34</v>
+      </c>
+      <c r="R99" s="4">
         <v>100</v>
       </c>
-      <c r="R99" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>287</v>
       </c>
@@ -7715,38 +8016,41 @@
       <c r="H100">
         <v>0</v>
       </c>
-      <c r="I100" s="1" t="s">
-        <v>7</v>
+      <c r="I100">
+        <v>0</v>
       </c>
       <c r="J100" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K100" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L100" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L100" t="s">
-        <v>294</v>
       </c>
       <c r="M100" t="s">
         <v>294</v>
       </c>
       <c r="N100" t="s">
+        <v>294</v>
+      </c>
+      <c r="O100" t="s">
         <v>295</v>
       </c>
-      <c r="O100" t="s">
+      <c r="P100" t="s">
         <v>300</v>
       </c>
-      <c r="P100" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q100" s="4">
+      <c r="Q100" t="s">
+        <v>34</v>
+      </c>
+      <c r="R100" s="4">
         <v>100</v>
       </c>
-      <c r="R100" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>288</v>
       </c>
@@ -7771,38 +8075,41 @@
       <c r="H101">
         <v>0</v>
       </c>
-      <c r="I101" s="1" t="s">
-        <v>7</v>
+      <c r="I101">
+        <v>0</v>
       </c>
       <c r="J101" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K101" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L101" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L101" t="s">
-        <v>296</v>
       </c>
       <c r="M101" t="s">
         <v>296</v>
       </c>
       <c r="N101" t="s">
+        <v>296</v>
+      </c>
+      <c r="O101" t="s">
         <v>295</v>
       </c>
-      <c r="O101" t="s">
+      <c r="P101" t="s">
         <v>300</v>
       </c>
-      <c r="P101" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q101" s="4">
+      <c r="Q101" t="s">
+        <v>34</v>
+      </c>
+      <c r="R101" s="4">
         <v>100</v>
       </c>
-      <c r="R101" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>289</v>
       </c>
@@ -7827,38 +8134,41 @@
       <c r="H102">
         <v>0</v>
       </c>
-      <c r="I102" s="1" t="s">
-        <v>7</v>
+      <c r="I102">
+        <v>0</v>
       </c>
       <c r="J102" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K102" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L102" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L102" t="s">
-        <v>297</v>
       </c>
       <c r="M102" t="s">
         <v>297</v>
       </c>
       <c r="N102" t="s">
+        <v>297</v>
+      </c>
+      <c r="O102" t="s">
         <v>298</v>
       </c>
-      <c r="O102" t="s">
+      <c r="P102" t="s">
         <v>300</v>
       </c>
-      <c r="P102" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q102" s="4">
+      <c r="Q102" t="s">
+        <v>34</v>
+      </c>
+      <c r="R102" s="4">
         <v>100</v>
       </c>
-      <c r="R102" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="S102" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
         <v>290</v>
       </c>
@@ -7883,38 +8193,41 @@
       <c r="H103">
         <v>0</v>
       </c>
-      <c r="I103" s="3" t="s">
-        <v>7</v>
+      <c r="I103">
+        <v>0</v>
       </c>
       <c r="J103" s="3" t="s">
         <v>7</v>
       </c>
       <c r="K103" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L103" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="L103" s="2" t="s">
-        <v>299</v>
       </c>
       <c r="M103" s="2" t="s">
         <v>299</v>
       </c>
       <c r="N103" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="O103" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="O103" s="2" t="s">
+      <c r="P103" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="P103" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q103" s="5">
+      <c r="Q103" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R103" s="5">
         <v>100</v>
       </c>
-      <c r="R103" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S103" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
         <v>314</v>
       </c>
@@ -7939,38 +8252,41 @@
       <c r="H104">
         <v>0</v>
       </c>
-      <c r="I104" s="1" t="s">
-        <v>334</v>
+      <c r="I104">
+        <v>0</v>
       </c>
       <c r="J104" s="1" t="s">
         <v>334</v>
       </c>
       <c r="K104" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="L104" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="L104" t="s">
-        <v>321</v>
       </c>
       <c r="M104" t="s">
         <v>321</v>
       </c>
       <c r="N104" t="s">
+        <v>321</v>
+      </c>
+      <c r="O104" t="s">
         <v>322</v>
       </c>
-      <c r="O104" t="s">
+      <c r="P104" t="s">
         <v>329</v>
       </c>
-      <c r="P104" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q104" s="4">
+      <c r="Q104" t="s">
+        <v>34</v>
+      </c>
+      <c r="R104" s="4">
         <v>61.18</v>
       </c>
-      <c r="R104" s="4">
+      <c r="S104" s="4">
         <v>135</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
         <v>315</v>
       </c>
@@ -7995,38 +8311,41 @@
       <c r="H105">
         <v>0</v>
       </c>
-      <c r="I105" s="1" t="s">
-        <v>334</v>
+      <c r="I105">
+        <v>0</v>
       </c>
       <c r="J105" s="1" t="s">
         <v>334</v>
       </c>
       <c r="K105" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="L105" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="L105" t="s">
-        <v>323</v>
       </c>
       <c r="M105" t="s">
         <v>323</v>
       </c>
       <c r="N105" t="s">
+        <v>323</v>
+      </c>
+      <c r="O105" t="s">
         <v>322</v>
       </c>
-      <c r="O105" t="s">
+      <c r="P105" t="s">
         <v>329</v>
       </c>
-      <c r="P105" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q105" s="4">
+      <c r="Q105" t="s">
+        <v>34</v>
+      </c>
+      <c r="R105" s="4">
         <v>61.18</v>
       </c>
-      <c r="R105" s="4">
+      <c r="S105" s="4">
         <v>135</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A106" s="4" t="s">
         <v>316</v>
       </c>
@@ -8051,38 +8370,41 @@
       <c r="H106">
         <v>0</v>
       </c>
-      <c r="I106" s="1" t="s">
-        <v>423</v>
+      <c r="I106">
+        <v>0</v>
       </c>
       <c r="J106" s="1" t="s">
         <v>423</v>
       </c>
       <c r="K106" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="L106" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="L106" t="s">
-        <v>324</v>
       </c>
       <c r="M106" t="s">
         <v>324</v>
       </c>
       <c r="N106" t="s">
+        <v>324</v>
+      </c>
+      <c r="O106" t="s">
         <v>325</v>
       </c>
-      <c r="O106" t="s">
+      <c r="P106" t="s">
         <v>330</v>
       </c>
-      <c r="P106" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q106" s="4">
+      <c r="Q106" t="s">
+        <v>34</v>
+      </c>
+      <c r="R106" s="4">
         <v>61.18</v>
       </c>
-      <c r="R106" s="4">
+      <c r="S106" s="4">
         <v>135</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
         <v>317</v>
       </c>
@@ -8107,38 +8429,41 @@
       <c r="H107">
         <v>0</v>
       </c>
-      <c r="I107" s="1" t="s">
-        <v>423</v>
+      <c r="I107">
+        <v>0</v>
       </c>
       <c r="J107" s="1" t="s">
         <v>423</v>
       </c>
       <c r="K107" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="L107" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="L107" t="s">
-        <v>326</v>
       </c>
       <c r="M107" t="s">
         <v>326</v>
       </c>
       <c r="N107" t="s">
+        <v>326</v>
+      </c>
+      <c r="O107" t="s">
         <v>325</v>
       </c>
-      <c r="O107" t="s">
+      <c r="P107" t="s">
         <v>330</v>
       </c>
-      <c r="P107" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q107" s="4">
+      <c r="Q107" t="s">
+        <v>34</v>
+      </c>
+      <c r="R107" s="4">
         <v>61.18</v>
       </c>
-      <c r="R107" s="4">
+      <c r="S107" s="4">
         <v>135</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
         <v>318</v>
       </c>
@@ -8163,38 +8488,41 @@
       <c r="H108">
         <v>0</v>
       </c>
-      <c r="I108" s="1" t="s">
-        <v>424</v>
+      <c r="I108">
+        <v>0</v>
       </c>
       <c r="J108" s="1" t="s">
         <v>424</v>
       </c>
       <c r="K108" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="L108" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="L108" t="s">
-        <v>327</v>
       </c>
       <c r="M108" t="s">
         <v>327</v>
       </c>
       <c r="N108" t="s">
+        <v>327</v>
+      </c>
+      <c r="O108" t="s">
         <v>328</v>
       </c>
-      <c r="O108" t="s">
+      <c r="P108" t="s">
         <v>331</v>
       </c>
-      <c r="P108" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q108" s="4">
+      <c r="Q108" t="s">
+        <v>34</v>
+      </c>
+      <c r="R108" s="4">
         <v>61.18</v>
       </c>
-      <c r="R108" s="4">
+      <c r="S108" s="4">
         <v>135</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A109" s="4" t="s">
         <v>319</v>
       </c>
@@ -8219,34 +8547,37 @@
       <c r="H109">
         <v>0</v>
       </c>
-      <c r="I109" s="1" t="s">
-        <v>424</v>
+      <c r="I109">
+        <v>1</v>
       </c>
       <c r="J109" s="1" t="s">
         <v>424</v>
       </c>
       <c r="K109" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="L109" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="L109" t="s">
-        <v>332</v>
       </c>
       <c r="M109" t="s">
         <v>332</v>
       </c>
       <c r="N109" t="s">
+        <v>332</v>
+      </c>
+      <c r="O109" t="s">
         <v>328</v>
       </c>
-      <c r="O109" t="s">
+      <c r="P109" t="s">
         <v>333</v>
       </c>
-      <c r="P109" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q109" s="4">
+      <c r="Q109" t="s">
+        <v>34</v>
+      </c>
+      <c r="R109" s="4">
         <v>61.18</v>
       </c>
-      <c r="R109" s="4">
+      <c r="S109" s="4">
         <v>135</v>
       </c>
     </row>

--- a/datasets_test.xlsx
+++ b/datasets_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2023 cytoSR\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F8A93D6-EDE9-442C-BF30-2CCB6EB618ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A87A4394-5D27-4AAB-8AE3-FDB186493EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="4215" windowWidth="21570" windowHeight="16170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6495" yWindow="2775" windowWidth="18885" windowHeight="16170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2135,8 +2135,8 @@
   <dimension ref="A1:S109"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.75" customWidth="1"/>
-    <col min="2" max="2" width="18.75" customWidth="1"/>
+    <col min="1" max="1" width="20.75" customWidth="1"/>
+    <col min="2" max="2" width="9.375" customWidth="1"/>
     <col min="3" max="3" width="2.5" customWidth="1"/>
     <col min="4" max="4" width="3.375" customWidth="1"/>
     <col min="5" max="5" width="2.25" customWidth="1"/>
@@ -2145,7 +2145,7 @@
     <col min="10" max="11" width="9.5" style="1" customWidth="1"/>
     <col min="12" max="12" width="10.375" style="1" customWidth="1"/>
     <col min="13" max="13" width="113.75" customWidth="1"/>
-    <col min="14" max="14" width="94.5" customWidth="1"/>
+    <col min="14" max="14" width="101" customWidth="1"/>
     <col min="15" max="15" width="9.375" customWidth="1"/>
     <col min="17" max="17" width="8" customWidth="1"/>
   </cols>

--- a/datasets_test.xlsx
+++ b/datasets_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2023 cytoSR\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A87A4394-5D27-4AAB-8AE3-FDB186493EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC6AC618-7309-44C7-B18E-E639BBCC32EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6495" yWindow="2775" windowWidth="18885" windowHeight="16170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="428">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1419,6 +1419,14 @@
   </si>
   <si>
     <t>dark</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SimuMix3D-512-31-0-0-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_512\raw_psf_31_gauss_0_poiss_0_sf_1_ratio_1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1426,7 +1434,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1463,6 +1471,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1493,7 +1509,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1511,11 +1527,24 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="34">
+  <dxfs count="35">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2132,10 +2161,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S109"/>
+  <dimension ref="A1:S110"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.75" customWidth="1"/>
+    <col min="1" max="1" width="32.125" customWidth="1"/>
     <col min="2" max="2" width="9.375" customWidth="1"/>
     <col min="3" max="3" width="2.5" customWidth="1"/>
     <col min="4" max="4" width="3.375" customWidth="1"/>
@@ -5336,68 +5365,68 @@
         <v>162.5</v>
       </c>
     </row>
-    <row r="55" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="B55" s="7" t="s">
+    <row r="55" spans="1:19" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="17" t="s">
+        <v>426</v>
+      </c>
+      <c r="B55" s="18" t="s">
         <v>308</v>
       </c>
-      <c r="C55" s="6">
-        <v>1</v>
-      </c>
-      <c r="D55" s="6" t="s">
+      <c r="C55" s="17">
+        <v>1</v>
+      </c>
+      <c r="D55" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="E55" s="6">
+      <c r="E55" s="17">
         <v>3</v>
       </c>
-      <c r="F55" s="6">
-        <v>1</v>
-      </c>
-      <c r="G55" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="H55">
-        <v>1</v>
-      </c>
-      <c r="I55">
-        <v>0</v>
-      </c>
-      <c r="J55" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="K55" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="L55" s="8" t="s">
+      <c r="F55" s="17">
+        <v>1</v>
+      </c>
+      <c r="G55" s="17">
+        <v>1</v>
+      </c>
+      <c r="H55" s="17">
+        <v>1</v>
+      </c>
+      <c r="I55" s="17">
+        <v>0</v>
+      </c>
+      <c r="J55" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="K55" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="L55" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="M55" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="N55" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="O55" s="6" t="s">
+      <c r="M55" s="17" t="s">
+        <v>427</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>427</v>
+      </c>
+      <c r="O55" s="17" t="s">
         <v>373</v>
       </c>
-      <c r="P55" s="6" t="s">
+      <c r="P55" s="17" t="s">
         <v>374</v>
       </c>
-      <c r="Q55" s="6" t="s">
+      <c r="Q55" s="17" t="s">
         <v>375</v>
       </c>
-      <c r="R55" s="6">
+      <c r="R55" s="17">
         <v>162.5</v>
       </c>
-      <c r="S55" s="6">
+      <c r="S55" s="17">
         <v>162.5</v>
       </c>
     </row>
     <row r="56" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="6" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>308</v>
@@ -5433,19 +5462,19 @@
         <v>9</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="Q56" s="6" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="R56" s="6">
         <v>162.5</v>
@@ -5454,68 +5483,68 @@
         <v>162.5</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>21</v>
-      </c>
-      <c r="B57" s="4" t="s">
+    <row r="57" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="B57" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="C57">
-        <v>1</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="C57" s="6">
+        <v>1</v>
+      </c>
+      <c r="D57" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E57">
+      <c r="E57" s="6">
         <v>3</v>
       </c>
-      <c r="F57">
-        <v>1</v>
-      </c>
-      <c r="G57">
-        <v>1</v>
+      <c r="F57" s="6">
+        <v>1</v>
+      </c>
+      <c r="G57" s="6">
+        <v>0.1</v>
       </c>
       <c r="H57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57">
         <v>0</v>
       </c>
-      <c r="J57" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="L57" s="1" t="s">
+      <c r="J57" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="K57" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="L57" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M57" t="s">
-        <v>352</v>
-      </c>
-      <c r="N57" t="s">
-        <v>352</v>
-      </c>
-      <c r="O57" t="s">
-        <v>353</v>
-      </c>
-      <c r="P57" t="s">
-        <v>354</v>
-      </c>
-      <c r="Q57" t="s">
-        <v>355</v>
-      </c>
-      <c r="R57">
+      <c r="M57" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="N57" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="O57" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="P57" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q57" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="R57" s="6">
         <v>162.5</v>
       </c>
-      <c r="S57">
+      <c r="S57" s="6">
         <v>162.5</v>
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>308</v>
@@ -5551,10 +5580,10 @@
         <v>9</v>
       </c>
       <c r="M58" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="N58" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="O58" t="s">
         <v>353</v>
@@ -5574,7 +5603,7 @@
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>308</v>
@@ -5592,7 +5621,7 @@
         <v>1</v>
       </c>
       <c r="G59">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="H59">
         <v>0</v>
@@ -5610,10 +5639,10 @@
         <v>9</v>
       </c>
       <c r="M59" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="N59" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O59" t="s">
         <v>353</v>
@@ -5631,262 +5660,262 @@
         <v>162.5</v>
       </c>
     </row>
-    <row r="60" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="2" t="s">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>23</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+      <c r="D60" t="s">
+        <v>37</v>
+      </c>
+      <c r="E60">
+        <v>3</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+      <c r="G60">
+        <v>0.3</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M60" t="s">
+        <v>357</v>
+      </c>
+      <c r="N60" t="s">
+        <v>357</v>
+      </c>
+      <c r="O60" t="s">
+        <v>353</v>
+      </c>
+      <c r="P60" t="s">
+        <v>354</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>355</v>
+      </c>
+      <c r="R60">
+        <v>162.5</v>
+      </c>
+      <c r="S60">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B61" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="C60" s="2">
-        <v>1</v>
-      </c>
-      <c r="D60" s="2" t="s">
+      <c r="C61" s="2">
+        <v>1</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E60" s="2">
+      <c r="E61" s="2">
         <v>3</v>
       </c>
-      <c r="F60" s="2">
-        <v>1</v>
-      </c>
-      <c r="G60" s="2">
+      <c r="F61" s="2">
+        <v>1</v>
+      </c>
+      <c r="G61" s="2">
         <v>0.1</v>
       </c>
-      <c r="H60">
-        <v>0</v>
-      </c>
-      <c r="I60">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="L60" s="3" t="s">
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="L61" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M60" s="2" t="s">
+      <c r="M61" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="N60" s="2" t="s">
+      <c r="N61" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="O60" s="2" t="s">
+      <c r="O61" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="P60" s="2" t="s">
+      <c r="P61" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="Q60" s="2" t="s">
+      <c r="Q61" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="R60" s="2">
+      <c r="R61" s="2">
         <v>162.5</v>
       </c>
-      <c r="S60" s="2">
+      <c r="S61" s="2">
         <v>162.5</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
         <v>15</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B62" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="C61">
-        <v>1</v>
-      </c>
-      <c r="D61" t="s">
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62" t="s">
         <v>37</v>
       </c>
-      <c r="E61">
+      <c r="E62">
         <v>3</v>
       </c>
-      <c r="F61">
-        <v>1</v>
-      </c>
-      <c r="G61">
-        <v>1</v>
-      </c>
-      <c r="H61">
-        <v>0</v>
-      </c>
-      <c r="I61">
-        <v>0</v>
-      </c>
-      <c r="J61" s="1" t="s">
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K61" s="1" t="s">
+      <c r="K62" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L61" s="1" t="s">
+      <c r="L62" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M61" t="s">
+      <c r="M62" t="s">
         <v>359</v>
       </c>
-      <c r="N61" t="s">
+      <c r="N62" t="s">
         <v>359</v>
       </c>
-      <c r="O61" t="s">
+      <c r="O62" t="s">
         <v>360</v>
       </c>
-      <c r="P61" t="s">
+      <c r="P62" t="s">
         <v>361</v>
       </c>
-      <c r="Q61" t="s">
+      <c r="Q62" t="s">
         <v>362</v>
       </c>
-      <c r="R61">
+      <c r="R62">
         <v>92.6</v>
       </c>
-      <c r="S61">
+      <c r="S62">
         <v>200</v>
       </c>
     </row>
-    <row r="62" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="2" t="s">
+    <row r="63" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B63" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="C62" s="2">
-        <v>1</v>
-      </c>
-      <c r="D62" s="2" t="s">
+      <c r="C63" s="2">
+        <v>1</v>
+      </c>
+      <c r="D63" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E63" s="2">
         <v>3</v>
       </c>
-      <c r="F62" s="2">
-        <v>1</v>
-      </c>
-      <c r="G62" s="2">
-        <v>1</v>
-      </c>
-      <c r="H62">
-        <v>0</v>
-      </c>
-      <c r="I62">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="s">
+      <c r="F63" s="2">
+        <v>1</v>
+      </c>
+      <c r="G63" s="2">
+        <v>1</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3" t="s">
+      <c r="K63" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="3" t="s">
+      <c r="L63" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M62" s="2" t="s">
+      <c r="M63" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="N62" s="2" t="s">
+      <c r="N63" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="O62" s="2" t="s">
+      <c r="O63" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="P62" s="2" t="s">
+      <c r="P63" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="Q62" s="2" t="s">
+      <c r="Q63" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="R62" s="2">
+      <c r="R63" s="2">
         <v>92.6</v>
       </c>
-      <c r="S62" s="2">
+      <c r="S63" s="2">
         <v>200</v>
       </c>
     </row>
-    <row r="63" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="12" t="s">
+    <row r="64" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B63" s="7" t="s">
+      <c r="B64" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="C63" s="12">
-        <v>1</v>
-      </c>
-      <c r="D63" s="12" t="s">
+      <c r="C64" s="12">
+        <v>1</v>
+      </c>
+      <c r="D64" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E63" s="12">
+      <c r="E64" s="12">
         <v>3</v>
       </c>
-      <c r="F63" s="12">
-        <v>1</v>
-      </c>
-      <c r="G63" s="12">
-        <v>1</v>
-      </c>
-      <c r="H63" s="12">
-        <v>1</v>
-      </c>
-      <c r="I63">
-        <v>0</v>
-      </c>
-      <c r="J63" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="K63" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="L63" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="M63" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="N63" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="O63" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="P63" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q63" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="R63" s="12">
-        <v>25</v>
-      </c>
-      <c r="S63" s="12">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B64" s="14" t="s">
-        <v>309</v>
-      </c>
-      <c r="C64" s="13">
-        <v>1</v>
-      </c>
-      <c r="D64" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E64" s="13">
-        <v>3</v>
-      </c>
-      <c r="F64" s="13">
-        <v>1</v>
-      </c>
-      <c r="G64" s="13">
+      <c r="F64" s="12">
+        <v>1</v>
+      </c>
+      <c r="G64" s="12">
         <v>1</v>
       </c>
       <c r="H64" s="12">
@@ -5901,211 +5930,211 @@
       <c r="K64" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="L64" s="15" t="s">
+      <c r="L64" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M64" s="13" t="s">
+      <c r="M64" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="N64" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="O64" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="P64" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q64" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="R64" s="12">
+        <v>25</v>
+      </c>
+      <c r="S64" s="12">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B65" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="C65" s="13">
+        <v>1</v>
+      </c>
+      <c r="D65" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E65" s="13">
+        <v>3</v>
+      </c>
+      <c r="F65" s="13">
+        <v>1</v>
+      </c>
+      <c r="G65" s="13">
+        <v>1</v>
+      </c>
+      <c r="H65" s="12">
+        <v>1</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="K65" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="L65" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="M65" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="N64" s="13" t="s">
+      <c r="N65" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="O64" s="13" t="s">
+      <c r="O65" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="P64" s="13" t="s">
+      <c r="P65" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="Q64" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="R64" s="13">
+      <c r="Q65" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="R65" s="13">
         <v>25</v>
       </c>
-      <c r="S64" s="13">
+      <c r="S65" s="13">
         <v>160</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
         <v>85</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B66" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C65">
-        <v>1</v>
-      </c>
-      <c r="D65" t="s">
+      <c r="C66">
+        <v>1</v>
+      </c>
+      <c r="D66" t="s">
         <v>36</v>
       </c>
-      <c r="E65">
+      <c r="E66">
         <v>3</v>
       </c>
-      <c r="F65">
-        <v>1</v>
-      </c>
-      <c r="G65">
-        <v>1</v>
-      </c>
-      <c r="H65">
-        <v>0</v>
-      </c>
-      <c r="I65">
-        <v>0</v>
-      </c>
-      <c r="J65" s="1" t="s">
+      <c r="F66">
+        <v>1</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K65" s="1" t="s">
+      <c r="K66" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L65" s="1" t="s">
+      <c r="L66" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M65" t="s">
+      <c r="M66" t="s">
         <v>121</v>
       </c>
-      <c r="N65" t="s">
+      <c r="N66" t="s">
         <v>121</v>
       </c>
-      <c r="O65" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="P65" t="s">
+      <c r="O66" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P66" t="s">
         <v>122</v>
       </c>
-      <c r="Q65" t="s">
+      <c r="Q66" t="s">
         <v>123</v>
       </c>
-      <c r="R65">
+      <c r="R66">
         <v>92.6</v>
       </c>
-      <c r="S65">
+      <c r="S66">
         <v>200</v>
       </c>
     </row>
-    <row r="66" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="2" t="s">
+    <row r="67" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="B67" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="C66" s="2">
-        <v>1</v>
-      </c>
-      <c r="D66" s="2" t="s">
+      <c r="C67" s="2">
+        <v>1</v>
+      </c>
+      <c r="D67" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E66" s="2">
+      <c r="E67" s="2">
         <v>3</v>
       </c>
-      <c r="F66" s="2">
-        <v>1</v>
-      </c>
-      <c r="G66" s="2">
-        <v>1</v>
-      </c>
-      <c r="H66">
-        <v>0</v>
-      </c>
-      <c r="I66">
-        <v>0</v>
-      </c>
-      <c r="J66" s="3" t="s">
+      <c r="F67" s="2">
+        <v>1</v>
+      </c>
+      <c r="G67" s="2">
+        <v>1</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K66" s="3" t="s">
+      <c r="K67" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L66" s="3" t="s">
+      <c r="L67" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M66" s="2" t="s">
+      <c r="M67" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="N66" s="2" t="s">
+      <c r="N67" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="P66" s="2" t="s">
+      <c r="O67" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="P67" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="Q66" s="2" t="s">
+      <c r="Q67" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="R66" s="2">
+      <c r="R67" s="2">
         <v>92.6</v>
       </c>
-      <c r="S66" s="2">
+      <c r="S67" s="2">
         <v>200</v>
-      </c>
-    </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A67" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="C67">
-        <v>1</v>
-      </c>
-      <c r="D67" t="s">
-        <v>37</v>
-      </c>
-      <c r="E67">
-        <v>3</v>
-      </c>
-      <c r="F67">
-        <v>1</v>
-      </c>
-      <c r="G67">
-        <v>1</v>
-      </c>
-      <c r="H67">
-        <v>0</v>
-      </c>
-      <c r="I67">
-        <v>0</v>
-      </c>
-      <c r="J67" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L67" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M67" t="s">
-        <v>127</v>
-      </c>
-      <c r="N67" t="s">
-        <v>127</v>
-      </c>
-      <c r="O67" t="s">
-        <v>128</v>
-      </c>
-      <c r="P67" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q67" t="s">
-        <v>34</v>
-      </c>
-      <c r="R67">
-        <v>25</v>
-      </c>
-      <c r="S67">
-        <v>160</v>
       </c>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>310</v>
@@ -6150,7 +6179,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q68" t="s">
         <v>34</v>
@@ -6163,8 +6192,8 @@
       </c>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>88</v>
+      <c r="A69" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>310</v>
@@ -6200,16 +6229,16 @@
         <v>9</v>
       </c>
       <c r="M69" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="N69" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="O69" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="P69" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="Q69" t="s">
         <v>34</v>
@@ -6223,7 +6252,7 @@
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>310</v>
@@ -6259,16 +6288,16 @@
         <v>9</v>
       </c>
       <c r="M70" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="N70" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="O70" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="P70" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="Q70" t="s">
         <v>34</v>
@@ -6282,7 +6311,7 @@
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>310</v>
@@ -6318,16 +6347,16 @@
         <v>9</v>
       </c>
       <c r="M71" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="N71" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="O71" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="P71" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="Q71" t="s">
         <v>34</v>
@@ -6341,7 +6370,7 @@
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>310</v>
@@ -6377,16 +6406,16 @@
         <v>9</v>
       </c>
       <c r="M72" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="N72" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="O72" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="P72" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="Q72" t="s">
         <v>34</v>
@@ -6400,7 +6429,7 @@
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>310</v>
@@ -6436,16 +6465,16 @@
         <v>9</v>
       </c>
       <c r="M73" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="N73" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O73" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="P73" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="Q73" t="s">
         <v>34</v>
@@ -6459,7 +6488,7 @@
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>310</v>
@@ -6495,16 +6524,16 @@
         <v>9</v>
       </c>
       <c r="M74" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="N74" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="O74" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="Q74" t="s">
         <v>34</v>
@@ -6518,7 +6547,7 @@
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>310</v>
@@ -6554,16 +6583,16 @@
         <v>9</v>
       </c>
       <c r="M75" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="N75" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="O75" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P75" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q75" t="s">
         <v>34</v>
@@ -6577,7 +6606,7 @@
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>310</v>
@@ -6613,16 +6642,16 @@
         <v>9</v>
       </c>
       <c r="M76" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="N76" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="O76" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="Q76" t="s">
         <v>34</v>
@@ -6634,26 +6663,26 @@
         <v>160</v>
       </c>
     </row>
-    <row r="77" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="2" t="s">
-        <v>96</v>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>95</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C77" s="2">
-        <v>1</v>
-      </c>
-      <c r="D77" s="2" t="s">
+      <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="D77" t="s">
         <v>37</v>
       </c>
-      <c r="E77" s="2">
+      <c r="E77">
         <v>3</v>
       </c>
-      <c r="F77" s="2">
-        <v>1</v>
-      </c>
-      <c r="G77" s="2">
+      <c r="F77">
+        <v>1</v>
+      </c>
+      <c r="G77">
         <v>1</v>
       </c>
       <c r="H77">
@@ -6662,99 +6691,99 @@
       <c r="I77">
         <v>0</v>
       </c>
-      <c r="J77" s="3" t="s">
+      <c r="J77" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K77" s="3" t="s">
+      <c r="K77" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L77" s="3" t="s">
+      <c r="L77" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M77" s="2" t="s">
+      <c r="M77" t="s">
+        <v>145</v>
+      </c>
+      <c r="N77" t="s">
+        <v>145</v>
+      </c>
+      <c r="O77" t="s">
+        <v>145</v>
+      </c>
+      <c r="P77" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>34</v>
+      </c>
+      <c r="R77">
+        <v>25</v>
+      </c>
+      <c r="S77">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="C78" s="2">
+        <v>1</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E78" s="2">
+        <v>3</v>
+      </c>
+      <c r="F78" s="2">
+        <v>1</v>
+      </c>
+      <c r="G78" s="2">
+        <v>1</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L78" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="M78" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="N77" s="2" t="s">
+      <c r="N78" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="O77" s="2" t="s">
+      <c r="O78" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="P77" s="2" t="s">
+      <c r="P78" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="Q77" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="R77" s="2">
+      <c r="Q78" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R78" s="2">
         <v>25</v>
       </c>
-      <c r="S77" s="2">
+      <c r="S78" s="2">
         <v>160</v>
-      </c>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
-        <v>99</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="C78">
-        <v>1</v>
-      </c>
-      <c r="D78" t="s">
-        <v>98</v>
-      </c>
-      <c r="E78">
-        <v>2</v>
-      </c>
-      <c r="F78">
-        <v>1</v>
-      </c>
-      <c r="G78">
-        <v>1</v>
-      </c>
-      <c r="H78">
-        <v>0</v>
-      </c>
-      <c r="I78">
-        <v>0</v>
-      </c>
-      <c r="J78" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K78" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="L78" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M78" t="s">
-        <v>149</v>
-      </c>
-      <c r="N78" t="s">
-        <v>149</v>
-      </c>
-      <c r="O78" t="s">
-        <v>150</v>
-      </c>
-      <c r="P78" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q78" t="s">
-        <v>34</v>
-      </c>
-      <c r="R78">
-        <v>60.4</v>
-      </c>
-      <c r="S78">
-        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>305</v>
@@ -6790,10 +6819,10 @@
         <v>10</v>
       </c>
       <c r="M79" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="N79" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="O79" t="s">
         <v>150</v>
@@ -6813,7 +6842,7 @@
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>305</v>
@@ -6849,10 +6878,10 @@
         <v>10</v>
       </c>
       <c r="M80" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N80" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O80" t="s">
         <v>150</v>
@@ -6872,10 +6901,10 @@
     </row>
     <row r="81" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -6908,16 +6937,16 @@
         <v>10</v>
       </c>
       <c r="M81" t="s">
-        <v>257</v>
+        <v>153</v>
       </c>
       <c r="N81" t="s">
-        <v>257</v>
+        <v>153</v>
       </c>
       <c r="O81" t="s">
-        <v>275</v>
+        <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>280</v>
+        <v>151</v>
       </c>
       <c r="Q81" t="s">
         <v>34</v>
@@ -6931,7 +6960,7 @@
     </row>
     <row r="82" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>303</v>
@@ -6967,10 +6996,10 @@
         <v>10</v>
       </c>
       <c r="M82" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N82" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O82" t="s">
         <v>275</v>
@@ -6990,7 +7019,7 @@
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>303</v>
@@ -7026,10 +7055,10 @@
         <v>10</v>
       </c>
       <c r="M83" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N83" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O83" t="s">
         <v>275</v>
@@ -7049,7 +7078,7 @@
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>303</v>
@@ -7085,16 +7114,16 @@
         <v>10</v>
       </c>
       <c r="M84" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="N84" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O84" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P84" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q84" t="s">
         <v>34</v>
@@ -7108,7 +7137,7 @@
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>303</v>
@@ -7144,10 +7173,10 @@
         <v>10</v>
       </c>
       <c r="M85" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="N85" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O85" t="s">
         <v>276</v>
@@ -7167,7 +7196,7 @@
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>303</v>
@@ -7203,10 +7232,10 @@
         <v>10</v>
       </c>
       <c r="M86" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N86" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O86" t="s">
         <v>276</v>
@@ -7226,10 +7255,10 @@
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>272</v>
+        <v>107</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -7262,16 +7291,16 @@
         <v>10</v>
       </c>
       <c r="M87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O87" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P87" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q87" t="s">
         <v>34</v>
@@ -7285,7 +7314,7 @@
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>311</v>
@@ -7321,10 +7350,10 @@
         <v>10</v>
       </c>
       <c r="M88" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="N88" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O88" t="s">
         <v>277</v>
@@ -7344,7 +7373,7 @@
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>311</v>
@@ -7380,10 +7409,10 @@
         <v>10</v>
       </c>
       <c r="M89" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N89" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O89" t="s">
         <v>277</v>
@@ -7403,10 +7432,10 @@
     </row>
     <row r="90" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>108</v>
+        <v>274</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="C90">
         <v>1</v>
@@ -7439,16 +7468,16 @@
         <v>10</v>
       </c>
       <c r="M90" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="N90" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O90" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P90" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Q90" t="s">
         <v>34</v>
@@ -7462,7 +7491,7 @@
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>304</v>
@@ -7498,10 +7527,10 @@
         <v>10</v>
       </c>
       <c r="M91" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N91" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O91" t="s">
         <v>278</v>
@@ -7521,7 +7550,7 @@
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>304</v>
@@ -7557,10 +7586,10 @@
         <v>10</v>
       </c>
       <c r="M92" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="N92" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O92" t="s">
         <v>278</v>
@@ -7580,10 +7609,10 @@
     </row>
     <row r="93" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C93">
         <v>1</v>
@@ -7616,16 +7645,16 @@
         <v>10</v>
       </c>
       <c r="M93" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="N93" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="O93" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P93" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q93" t="s">
         <v>34</v>
@@ -7639,7 +7668,7 @@
     </row>
     <row r="94" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>302</v>
@@ -7675,10 +7704,10 @@
         <v>10</v>
       </c>
       <c r="M94" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="N94" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O94" t="s">
         <v>279</v>
@@ -7696,26 +7725,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="2" t="s">
-        <v>113</v>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>112</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="C95" s="2">
-        <v>1</v>
-      </c>
-      <c r="D95" s="2" t="s">
+      <c r="C95">
+        <v>1</v>
+      </c>
+      <c r="D95" t="s">
         <v>98</v>
       </c>
-      <c r="E95" s="2">
-        <v>2</v>
-      </c>
-      <c r="F95" s="2">
-        <v>1</v>
-      </c>
-      <c r="G95" s="2">
+      <c r="E95">
+        <v>2</v>
+      </c>
+      <c r="F95">
+        <v>1</v>
+      </c>
+      <c r="G95">
         <v>1</v>
       </c>
       <c r="H95">
@@ -7724,217 +7753,217 @@
       <c r="I95">
         <v>0</v>
       </c>
-      <c r="J95" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K95" s="3" t="s">
+      <c r="J95" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K95" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L95" s="3" t="s">
+      <c r="L95" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M95" s="2" t="s">
+      <c r="M95" t="s">
+        <v>270</v>
+      </c>
+      <c r="N95" t="s">
+        <v>270</v>
+      </c>
+      <c r="O95" t="s">
+        <v>279</v>
+      </c>
+      <c r="P95" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>34</v>
+      </c>
+      <c r="R95">
+        <v>60.4</v>
+      </c>
+      <c r="S95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C96" s="2">
+        <v>1</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E96" s="2">
+        <v>2</v>
+      </c>
+      <c r="F96" s="2">
+        <v>1</v>
+      </c>
+      <c r="G96" s="2">
+        <v>1</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M96" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="N95" s="2" t="s">
+      <c r="N96" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="O95" s="2" t="s">
+      <c r="O96" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="P95" s="2" t="s">
+      <c r="P96" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="Q95" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="R95" s="2">
+      <c r="Q96" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R96" s="2">
         <v>60.4</v>
       </c>
-      <c r="S95" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A96" t="s">
+      <c r="S96" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
         <v>251</v>
       </c>
-      <c r="B96" s="4" t="s">
+      <c r="B97" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="C96">
-        <v>1</v>
-      </c>
-      <c r="D96" t="s">
+      <c r="C97">
+        <v>1</v>
+      </c>
+      <c r="D97" t="s">
         <v>98</v>
       </c>
-      <c r="E96">
-        <v>2</v>
-      </c>
-      <c r="F96">
-        <v>1</v>
-      </c>
-      <c r="G96">
-        <v>1</v>
-      </c>
-      <c r="H96">
-        <v>0</v>
-      </c>
-      <c r="I96">
-        <v>0</v>
-      </c>
-      <c r="J96" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K96" s="1" t="s">
+      <c r="E97">
+        <v>2</v>
+      </c>
+      <c r="F97">
+        <v>1</v>
+      </c>
+      <c r="G97">
+        <v>1</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K97" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L96" s="1" t="s">
+      <c r="L97" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M96" t="s">
+      <c r="M97" t="s">
         <v>253</v>
       </c>
-      <c r="N96" t="s">
+      <c r="N97" t="s">
         <v>253</v>
       </c>
-      <c r="O96" t="s">
+      <c r="O97" t="s">
         <v>254</v>
       </c>
-      <c r="P96" t="s">
+      <c r="P97" t="s">
         <v>249</v>
       </c>
-      <c r="Q96" t="s">
-        <v>34</v>
-      </c>
-      <c r="R96">
+      <c r="Q97" t="s">
+        <v>34</v>
+      </c>
+      <c r="R97">
         <v>80</v>
       </c>
-      <c r="S96">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="2" t="s">
+      <c r="S97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="B97" s="4" t="s">
+      <c r="B98" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="C97" s="2">
-        <v>1</v>
-      </c>
-      <c r="D97" s="2" t="s">
+      <c r="C98" s="2">
+        <v>1</v>
+      </c>
+      <c r="D98" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E97" s="2">
-        <v>2</v>
-      </c>
-      <c r="F97" s="2">
-        <v>1</v>
-      </c>
-      <c r="G97" s="2">
-        <v>1</v>
-      </c>
-      <c r="H97">
-        <v>0</v>
-      </c>
-      <c r="I97">
-        <v>0</v>
-      </c>
-      <c r="J97" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K97" s="3" t="s">
+      <c r="E98" s="2">
+        <v>2</v>
+      </c>
+      <c r="F98" s="2">
+        <v>1</v>
+      </c>
+      <c r="G98" s="2">
+        <v>1</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K98" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="L97" s="3" t="s">
+      <c r="L98" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M97" s="2" t="s">
+      <c r="M98" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="N97" s="2" t="s">
+      <c r="N98" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="O97" s="2" t="s">
+      <c r="O98" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="P97" s="2" t="s">
+      <c r="P98" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="Q97" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="R97" s="2">
+      <c r="Q98" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R98" s="2">
         <v>80</v>
       </c>
-      <c r="S97" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A98" t="s">
-        <v>285</v>
-      </c>
-      <c r="B98" t="s">
-        <v>302</v>
-      </c>
-      <c r="C98" s="4">
-        <v>1</v>
-      </c>
-      <c r="D98" t="s">
-        <v>98</v>
-      </c>
-      <c r="E98" s="4">
-        <v>2</v>
-      </c>
-      <c r="F98" s="4">
-        <v>1</v>
-      </c>
-      <c r="G98" s="4">
-        <v>1</v>
-      </c>
-      <c r="H98">
-        <v>0</v>
-      </c>
-      <c r="I98">
-        <v>0</v>
-      </c>
-      <c r="J98" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K98" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L98" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M98" t="s">
-        <v>291</v>
-      </c>
-      <c r="N98" t="s">
-        <v>291</v>
-      </c>
-      <c r="O98" t="s">
-        <v>292</v>
-      </c>
-      <c r="P98" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q98" t="s">
-        <v>34</v>
-      </c>
-      <c r="R98" s="4">
-        <v>100</v>
-      </c>
-      <c r="S98" s="4">
+      <c r="S98" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B99" t="s">
         <v>302</v>
@@ -7970,10 +7999,10 @@
         <v>10</v>
       </c>
       <c r="M99" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="N99" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O99" t="s">
         <v>292</v>
@@ -7993,10 +8022,10 @@
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B100" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="C100" s="4">
         <v>1</v>
@@ -8029,13 +8058,13 @@
         <v>10</v>
       </c>
       <c r="M100" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="N100" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O100" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="P100" t="s">
         <v>300</v>
@@ -8052,7 +8081,7 @@
     </row>
     <row r="101" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B101" t="s">
         <v>311</v>
@@ -8088,10 +8117,10 @@
         <v>10</v>
       </c>
       <c r="M101" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="N101" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="O101" t="s">
         <v>295</v>
@@ -8111,10 +8140,10 @@
     </row>
     <row r="102" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B102" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="C102" s="4">
         <v>1</v>
@@ -8147,13 +8176,13 @@
         <v>10</v>
       </c>
       <c r="M102" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="N102" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O102" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="P102" t="s">
         <v>300</v>
@@ -8168,85 +8197,85 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="2" t="s">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>289</v>
+      </c>
+      <c r="B103" t="s">
+        <v>303</v>
+      </c>
+      <c r="C103" s="4">
+        <v>1</v>
+      </c>
+      <c r="D103" t="s">
+        <v>98</v>
+      </c>
+      <c r="E103" s="4">
+        <v>2</v>
+      </c>
+      <c r="F103" s="4">
+        <v>1</v>
+      </c>
+      <c r="G103" s="4">
+        <v>1</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L103" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M103" t="s">
+        <v>297</v>
+      </c>
+      <c r="N103" t="s">
+        <v>297</v>
+      </c>
+      <c r="O103" t="s">
+        <v>298</v>
+      </c>
+      <c r="P103" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>34</v>
+      </c>
+      <c r="R103" s="4">
+        <v>100</v>
+      </c>
+      <c r="S103" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="B103" s="2" t="s">
+      <c r="B104" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="C103" s="5">
-        <v>1</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E103" s="5">
-        <v>2</v>
-      </c>
-      <c r="F103" s="5">
-        <v>1</v>
-      </c>
-      <c r="G103" s="5">
-        <v>1</v>
-      </c>
-      <c r="H103">
-        <v>0</v>
-      </c>
-      <c r="I103">
-        <v>0</v>
-      </c>
-      <c r="J103" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K103" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L103" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M103" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="N103" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="O103" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="P103" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q103" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="R103" s="5">
-        <v>100</v>
-      </c>
-      <c r="S103" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A104" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="B104" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="C104" s="4">
+      <c r="C104" s="5">
         <v>1</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E104" s="16">
-        <v>3</v>
-      </c>
-      <c r="F104" s="4">
-        <v>1</v>
-      </c>
-      <c r="G104" s="4">
+      <c r="E104" s="5">
+        <v>2</v>
+      </c>
+      <c r="F104" s="5">
+        <v>1</v>
+      </c>
+      <c r="G104" s="5">
         <v>1</v>
       </c>
       <c r="H104">
@@ -8255,40 +8284,40 @@
       <c r="I104">
         <v>0</v>
       </c>
-      <c r="J104" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="K104" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="L104" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M104" t="s">
-        <v>321</v>
-      </c>
-      <c r="N104" t="s">
-        <v>321</v>
-      </c>
-      <c r="O104" t="s">
-        <v>322</v>
-      </c>
-      <c r="P104" t="s">
-        <v>329</v>
-      </c>
-      <c r="Q104" t="s">
-        <v>34</v>
-      </c>
-      <c r="R104" s="4">
-        <v>61.18</v>
-      </c>
-      <c r="S104" s="4">
-        <v>135</v>
+      <c r="J104" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K104" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L104" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M104" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="N104" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="O104" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="P104" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q104" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R104" s="5">
+        <v>100</v>
+      </c>
+      <c r="S104" s="5">
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>303</v>
@@ -8324,10 +8353,10 @@
         <v>9</v>
       </c>
       <c r="M105" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="N105" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="O105" t="s">
         <v>322</v>
@@ -8347,10 +8376,10 @@
     </row>
     <row r="106" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A106" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C106" s="4">
         <v>1</v>
@@ -8374,25 +8403,25 @@
         <v>0</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>423</v>
+        <v>334</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>423</v>
+        <v>334</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>320</v>
+        <v>9</v>
       </c>
       <c r="M106" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N106" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O106" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="P106" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q106" t="s">
         <v>34</v>
@@ -8406,7 +8435,7 @@
     </row>
     <row r="107" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>304</v>
@@ -8442,10 +8471,10 @@
         <v>320</v>
       </c>
       <c r="M107" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="N107" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="O107" t="s">
         <v>325</v>
@@ -8465,10 +8494,10 @@
     </row>
     <row r="108" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C108" s="4">
         <v>1</v>
@@ -8492,25 +8521,25 @@
         <v>0</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L108" s="1" t="s">
         <v>320</v>
       </c>
       <c r="M108" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="N108" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O108" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="P108" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q108" t="s">
         <v>34</v>
@@ -8524,7 +8553,7 @@
     </row>
     <row r="109" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A109" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>302</v>
@@ -8548,7 +8577,7 @@
         <v>0</v>
       </c>
       <c r="I109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J109" s="1" t="s">
         <v>424</v>
@@ -8560,16 +8589,16 @@
         <v>320</v>
       </c>
       <c r="M109" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="N109" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="O109" t="s">
         <v>328</v>
       </c>
       <c r="P109" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="Q109" t="s">
         <v>34</v>
@@ -8581,165 +8610,229 @@
         <v>135</v>
       </c>
     </row>
+    <row r="110" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A110" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C110" s="4">
+        <v>1</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E110" s="16">
+        <v>3</v>
+      </c>
+      <c r="F110" s="4">
+        <v>1</v>
+      </c>
+      <c r="G110" s="4">
+        <v>1</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+      <c r="I110">
+        <v>1</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="K110" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="L110" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="M110" t="s">
+        <v>332</v>
+      </c>
+      <c r="N110" t="s">
+        <v>332</v>
+      </c>
+      <c r="O110" t="s">
+        <v>328</v>
+      </c>
+      <c r="P110" t="s">
+        <v>333</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>34</v>
+      </c>
+      <c r="R110" s="4">
+        <v>61.18</v>
+      </c>
+      <c r="S110" s="4">
+        <v>135</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C1 C11 C47:C54 C78:C86 C90:C95 C98:C1048576 C57:C67">
-    <cfRule type="cellIs" dxfId="33" priority="37" operator="equal">
+  <conditionalFormatting sqref="C1 C11 C47:C54 C79:C87 C91:C96 C99:C1048576 C58:C68">
+    <cfRule type="cellIs" dxfId="34" priority="38" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2">
+    <cfRule type="cellIs" dxfId="33" priority="35" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3">
     <cfRule type="cellIs" dxfId="32" priority="34" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3">
+  <conditionalFormatting sqref="C4">
     <cfRule type="cellIs" dxfId="31" priority="33" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4">
+  <conditionalFormatting sqref="C5">
     <cfRule type="cellIs" dxfId="30" priority="32" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C5">
+  <conditionalFormatting sqref="C6">
     <cfRule type="cellIs" dxfId="29" priority="31" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C6">
+  <conditionalFormatting sqref="C7">
     <cfRule type="cellIs" dxfId="28" priority="30" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C7">
+  <conditionalFormatting sqref="C8">
     <cfRule type="cellIs" dxfId="27" priority="29" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C8">
+  <conditionalFormatting sqref="C9">
     <cfRule type="cellIs" dxfId="26" priority="28" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C9">
+  <conditionalFormatting sqref="C10">
     <cfRule type="cellIs" dxfId="25" priority="27" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C10">
+  <conditionalFormatting sqref="C12">
     <cfRule type="cellIs" dxfId="24" priority="26" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C12">
+  <conditionalFormatting sqref="C13">
     <cfRule type="cellIs" dxfId="23" priority="25" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C13">
+  <conditionalFormatting sqref="C14">
     <cfRule type="cellIs" dxfId="22" priority="24" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14">
+  <conditionalFormatting sqref="C15">
     <cfRule type="cellIs" dxfId="21" priority="23" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C15">
+  <conditionalFormatting sqref="C16">
     <cfRule type="cellIs" dxfId="20" priority="22" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16">
+  <conditionalFormatting sqref="C17">
     <cfRule type="cellIs" dxfId="19" priority="21" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17">
+  <conditionalFormatting sqref="C18">
     <cfRule type="cellIs" dxfId="18" priority="20" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18">
+  <conditionalFormatting sqref="C19:C20">
     <cfRule type="cellIs" dxfId="17" priority="19" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C19:C20">
+  <conditionalFormatting sqref="C21">
     <cfRule type="cellIs" dxfId="16" priority="18" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21">
+  <conditionalFormatting sqref="C22">
     <cfRule type="cellIs" dxfId="15" priority="17" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22">
+  <conditionalFormatting sqref="C23">
     <cfRule type="cellIs" dxfId="14" priority="16" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C23">
+  <conditionalFormatting sqref="C24">
     <cfRule type="cellIs" dxfId="13" priority="15" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24">
+  <conditionalFormatting sqref="C25">
     <cfRule type="cellIs" dxfId="12" priority="14" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C25">
+  <conditionalFormatting sqref="C26">
     <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C26">
+  <conditionalFormatting sqref="C27">
     <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C27">
+  <conditionalFormatting sqref="C28">
     <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C28">
+  <conditionalFormatting sqref="C29:C46">
     <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C29:C46">
+  <conditionalFormatting sqref="C70:C78">
     <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C69:C77">
+  <conditionalFormatting sqref="C69">
     <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C68">
+  <conditionalFormatting sqref="C97">
     <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C96">
+  <conditionalFormatting sqref="C98">
     <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C97">
+  <conditionalFormatting sqref="C88:C90">
     <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C87:C89">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+  <conditionalFormatting sqref="C57">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
